--- a/templates/25-pareto-and-distribution.xlsx
+++ b/templates/25-pareto-and-distribution.xlsx
@@ -880,11 +880,11 @@
         <v>412</v>
       </c>
       <c r="C5" s="8">
-        <f>IFERROR(B5/SUM($B$5:$B$24),"")</f>
+        <f>IF(OR(B5="",SUM($B$5:$B$24)=0),"",B5/SUM($B$5:$B$24))</f>
         <v/>
       </c>
       <c r="D5" s="8">
-        <f>IFERROR(SUM($B$5:B5)/SUM($B$5:$B$24),"")</f>
+        <f>IF(OR(B5="",SUM($B$5:$B$24)=0),"",SUM($B$5:B5)/SUM($B$5:$B$24))</f>
         <v/>
       </c>
       <c r="E5" s="7" t="n"/>
@@ -899,11 +899,11 @@
         <v>233</v>
       </c>
       <c r="C6" s="10">
-        <f>IFERROR(B6/SUM($B$5:$B$24),"")</f>
+        <f>IF(OR(B6="",SUM($B$5:$B$24)=0),"",B6/SUM($B$5:$B$24))</f>
         <v/>
       </c>
       <c r="D6" s="10">
-        <f>IFERROR(SUM($B$5:B6)/SUM($B$5:$B$24),"")</f>
+        <f>IF(OR(B6="",SUM($B$5:$B$24)=0),"",SUM($B$5:B6)/SUM($B$5:$B$24))</f>
         <v/>
       </c>
       <c r="E6" s="9" t="n"/>
@@ -918,11 +918,11 @@
         <v>151</v>
       </c>
       <c r="C7" s="10">
-        <f>IFERROR(B7/SUM($B$5:$B$24),"")</f>
+        <f>IF(OR(B7="",SUM($B$5:$B$24)=0),"",B7/SUM($B$5:$B$24))</f>
         <v/>
       </c>
       <c r="D7" s="10">
-        <f>IFERROR(SUM($B$5:B7)/SUM($B$5:$B$24),"")</f>
+        <f>IF(OR(B7="",SUM($B$5:$B$24)=0),"",SUM($B$5:B7)/SUM($B$5:$B$24))</f>
         <v/>
       </c>
       <c r="E7" s="9" t="n"/>
@@ -937,11 +937,11 @@
         <v>96</v>
       </c>
       <c r="C8" s="10">
-        <f>IFERROR(B8/SUM($B$5:$B$24),"")</f>
+        <f>IF(OR(B8="",SUM($B$5:$B$24)=0),"",B8/SUM($B$5:$B$24))</f>
         <v/>
       </c>
       <c r="D8" s="10">
-        <f>IFERROR(SUM($B$5:B8)/SUM($B$5:$B$24),"")</f>
+        <f>IF(OR(B8="",SUM($B$5:$B$24)=0),"",SUM($B$5:B8)/SUM($B$5:$B$24))</f>
         <v/>
       </c>
       <c r="E8" s="9" t="n"/>
@@ -956,11 +956,11 @@
         <v>74</v>
       </c>
       <c r="C9" s="10">
-        <f>IFERROR(B9/SUM($B$5:$B$24),"")</f>
+        <f>IF(OR(B9="",SUM($B$5:$B$24)=0),"",B9/SUM($B$5:$B$24))</f>
         <v/>
       </c>
       <c r="D9" s="10">
-        <f>IFERROR(SUM($B$5:B9)/SUM($B$5:$B$24),"")</f>
+        <f>IF(OR(B9="",SUM($B$5:$B$24)=0),"",SUM($B$5:B9)/SUM($B$5:$B$24))</f>
         <v/>
       </c>
       <c r="E9" s="9" t="n"/>
@@ -969,11 +969,11 @@
       <c r="A10" s="9" t="n"/>
       <c r="B10" s="9" t="n"/>
       <c r="C10" s="10">
-        <f>IFERROR(B10/SUM($B$5:$B$24),"")</f>
+        <f>IF(OR(B10="",SUM($B$5:$B$24)=0),"",B10/SUM($B$5:$B$24))</f>
         <v/>
       </c>
       <c r="D10" s="10">
-        <f>IFERROR(SUM($B$5:B10)/SUM($B$5:$B$24),"")</f>
+        <f>IF(OR(B10="",SUM($B$5:$B$24)=0),"",SUM($B$5:B10)/SUM($B$5:$B$24))</f>
         <v/>
       </c>
       <c r="E10" s="9" t="n"/>
@@ -982,11 +982,11 @@
       <c r="A11" s="9" t="n"/>
       <c r="B11" s="9" t="n"/>
       <c r="C11" s="10">
-        <f>IFERROR(B11/SUM($B$5:$B$24),"")</f>
+        <f>IF(OR(B11="",SUM($B$5:$B$24)=0),"",B11/SUM($B$5:$B$24))</f>
         <v/>
       </c>
       <c r="D11" s="10">
-        <f>IFERROR(SUM($B$5:B11)/SUM($B$5:$B$24),"")</f>
+        <f>IF(OR(B11="",SUM($B$5:$B$24)=0),"",SUM($B$5:B11)/SUM($B$5:$B$24))</f>
         <v/>
       </c>
       <c r="E11" s="9" t="n"/>
@@ -995,11 +995,11 @@
       <c r="A12" s="9" t="n"/>
       <c r="B12" s="9" t="n"/>
       <c r="C12" s="10">
-        <f>IFERROR(B12/SUM($B$5:$B$24),"")</f>
+        <f>IF(OR(B12="",SUM($B$5:$B$24)=0),"",B12/SUM($B$5:$B$24))</f>
         <v/>
       </c>
       <c r="D12" s="10">
-        <f>IFERROR(SUM($B$5:B12)/SUM($B$5:$B$24),"")</f>
+        <f>IF(OR(B12="",SUM($B$5:$B$24)=0),"",SUM($B$5:B12)/SUM($B$5:$B$24))</f>
         <v/>
       </c>
       <c r="E12" s="9" t="n"/>
@@ -1008,11 +1008,11 @@
       <c r="A13" s="9" t="n"/>
       <c r="B13" s="9" t="n"/>
       <c r="C13" s="10">
-        <f>IFERROR(B13/SUM($B$5:$B$24),"")</f>
+        <f>IF(OR(B13="",SUM($B$5:$B$24)=0),"",B13/SUM($B$5:$B$24))</f>
         <v/>
       </c>
       <c r="D13" s="10">
-        <f>IFERROR(SUM($B$5:B13)/SUM($B$5:$B$24),"")</f>
+        <f>IF(OR(B13="",SUM($B$5:$B$24)=0),"",SUM($B$5:B13)/SUM($B$5:$B$24))</f>
         <v/>
       </c>
       <c r="E13" s="9" t="n"/>
@@ -1021,11 +1021,11 @@
       <c r="A14" s="9" t="n"/>
       <c r="B14" s="9" t="n"/>
       <c r="C14" s="10">
-        <f>IFERROR(B14/SUM($B$5:$B$24),"")</f>
+        <f>IF(OR(B14="",SUM($B$5:$B$24)=0),"",B14/SUM($B$5:$B$24))</f>
         <v/>
       </c>
       <c r="D14" s="10">
-        <f>IFERROR(SUM($B$5:B14)/SUM($B$5:$B$24),"")</f>
+        <f>IF(OR(B14="",SUM($B$5:$B$24)=0),"",SUM($B$5:B14)/SUM($B$5:$B$24))</f>
         <v/>
       </c>
       <c r="E14" s="9" t="n"/>
@@ -1034,11 +1034,11 @@
       <c r="A15" s="9" t="n"/>
       <c r="B15" s="9" t="n"/>
       <c r="C15" s="10">
-        <f>IFERROR(B15/SUM($B$5:$B$24),"")</f>
+        <f>IF(OR(B15="",SUM($B$5:$B$24)=0),"",B15/SUM($B$5:$B$24))</f>
         <v/>
       </c>
       <c r="D15" s="10">
-        <f>IFERROR(SUM($B$5:B15)/SUM($B$5:$B$24),"")</f>
+        <f>IF(OR(B15="",SUM($B$5:$B$24)=0),"",SUM($B$5:B15)/SUM($B$5:$B$24))</f>
         <v/>
       </c>
       <c r="E15" s="9" t="n"/>
@@ -1047,11 +1047,11 @@
       <c r="A16" s="9" t="n"/>
       <c r="B16" s="9" t="n"/>
       <c r="C16" s="10">
-        <f>IFERROR(B16/SUM($B$5:$B$24),"")</f>
+        <f>IF(OR(B16="",SUM($B$5:$B$24)=0),"",B16/SUM($B$5:$B$24))</f>
         <v/>
       </c>
       <c r="D16" s="10">
-        <f>IFERROR(SUM($B$5:B16)/SUM($B$5:$B$24),"")</f>
+        <f>IF(OR(B16="",SUM($B$5:$B$24)=0),"",SUM($B$5:B16)/SUM($B$5:$B$24))</f>
         <v/>
       </c>
       <c r="E16" s="9" t="n"/>
@@ -1060,11 +1060,11 @@
       <c r="A17" s="9" t="n"/>
       <c r="B17" s="9" t="n"/>
       <c r="C17" s="10">
-        <f>IFERROR(B17/SUM($B$5:$B$24),"")</f>
+        <f>IF(OR(B17="",SUM($B$5:$B$24)=0),"",B17/SUM($B$5:$B$24))</f>
         <v/>
       </c>
       <c r="D17" s="10">
-        <f>IFERROR(SUM($B$5:B17)/SUM($B$5:$B$24),"")</f>
+        <f>IF(OR(B17="",SUM($B$5:$B$24)=0),"",SUM($B$5:B17)/SUM($B$5:$B$24))</f>
         <v/>
       </c>
       <c r="E17" s="9" t="n"/>
@@ -1073,11 +1073,11 @@
       <c r="A18" s="9" t="n"/>
       <c r="B18" s="9" t="n"/>
       <c r="C18" s="10">
-        <f>IFERROR(B18/SUM($B$5:$B$24),"")</f>
+        <f>IF(OR(B18="",SUM($B$5:$B$24)=0),"",B18/SUM($B$5:$B$24))</f>
         <v/>
       </c>
       <c r="D18" s="10">
-        <f>IFERROR(SUM($B$5:B18)/SUM($B$5:$B$24),"")</f>
+        <f>IF(OR(B18="",SUM($B$5:$B$24)=0),"",SUM($B$5:B18)/SUM($B$5:$B$24))</f>
         <v/>
       </c>
       <c r="E18" s="9" t="n"/>
@@ -1086,11 +1086,11 @@
       <c r="A19" s="9" t="n"/>
       <c r="B19" s="9" t="n"/>
       <c r="C19" s="10">
-        <f>IFERROR(B19/SUM($B$5:$B$24),"")</f>
+        <f>IF(OR(B19="",SUM($B$5:$B$24)=0),"",B19/SUM($B$5:$B$24))</f>
         <v/>
       </c>
       <c r="D19" s="10">
-        <f>IFERROR(SUM($B$5:B19)/SUM($B$5:$B$24),"")</f>
+        <f>IF(OR(B19="",SUM($B$5:$B$24)=0),"",SUM($B$5:B19)/SUM($B$5:$B$24))</f>
         <v/>
       </c>
       <c r="E19" s="9" t="n"/>
@@ -1099,11 +1099,11 @@
       <c r="A20" s="9" t="n"/>
       <c r="B20" s="9" t="n"/>
       <c r="C20" s="10">
-        <f>IFERROR(B20/SUM($B$5:$B$24),"")</f>
+        <f>IF(OR(B20="",SUM($B$5:$B$24)=0),"",B20/SUM($B$5:$B$24))</f>
         <v/>
       </c>
       <c r="D20" s="10">
-        <f>IFERROR(SUM($B$5:B20)/SUM($B$5:$B$24),"")</f>
+        <f>IF(OR(B20="",SUM($B$5:$B$24)=0),"",SUM($B$5:B20)/SUM($B$5:$B$24))</f>
         <v/>
       </c>
       <c r="E20" s="9" t="n"/>
@@ -1112,11 +1112,11 @@
       <c r="A21" s="9" t="n"/>
       <c r="B21" s="9" t="n"/>
       <c r="C21" s="10">
-        <f>IFERROR(B21/SUM($B$5:$B$24),"")</f>
+        <f>IF(OR(B21="",SUM($B$5:$B$24)=0),"",B21/SUM($B$5:$B$24))</f>
         <v/>
       </c>
       <c r="D21" s="10">
-        <f>IFERROR(SUM($B$5:B21)/SUM($B$5:$B$24),"")</f>
+        <f>IF(OR(B21="",SUM($B$5:$B$24)=0),"",SUM($B$5:B21)/SUM($B$5:$B$24))</f>
         <v/>
       </c>
       <c r="E21" s="9" t="n"/>
@@ -1125,11 +1125,11 @@
       <c r="A22" s="9" t="n"/>
       <c r="B22" s="9" t="n"/>
       <c r="C22" s="10">
-        <f>IFERROR(B22/SUM($B$5:$B$24),"")</f>
+        <f>IF(OR(B22="",SUM($B$5:$B$24)=0),"",B22/SUM($B$5:$B$24))</f>
         <v/>
       </c>
       <c r="D22" s="10">
-        <f>IFERROR(SUM($B$5:B22)/SUM($B$5:$B$24),"")</f>
+        <f>IF(OR(B22="",SUM($B$5:$B$24)=0),"",SUM($B$5:B22)/SUM($B$5:$B$24))</f>
         <v/>
       </c>
       <c r="E22" s="9" t="n"/>
@@ -1138,11 +1138,11 @@
       <c r="A23" s="9" t="n"/>
       <c r="B23" s="9" t="n"/>
       <c r="C23" s="10">
-        <f>IFERROR(B23/SUM($B$5:$B$24),"")</f>
+        <f>IF(OR(B23="",SUM($B$5:$B$24)=0),"",B23/SUM($B$5:$B$24))</f>
         <v/>
       </c>
       <c r="D23" s="10">
-        <f>IFERROR(SUM($B$5:B23)/SUM($B$5:$B$24),"")</f>
+        <f>IF(OR(B23="",SUM($B$5:$B$24)=0),"",SUM($B$5:B23)/SUM($B$5:$B$24))</f>
         <v/>
       </c>
       <c r="E23" s="9" t="n"/>
@@ -1151,11 +1151,11 @@
       <c r="A24" s="9" t="n"/>
       <c r="B24" s="9" t="n"/>
       <c r="C24" s="10">
-        <f>IFERROR(B24/SUM($B$5:$B$24),"")</f>
+        <f>IF(OR(B24="",SUM($B$5:$B$24)=0),"",B24/SUM($B$5:$B$24))</f>
         <v/>
       </c>
       <c r="D24" s="10">
-        <f>IFERROR(SUM($B$5:B24)/SUM($B$5:$B$24),"")</f>
+        <f>IF(OR(B24="",SUM($B$5:$B$24)=0),"",SUM($B$5:B24)/SUM($B$5:$B$24))</f>
         <v/>
       </c>
       <c r="E24" s="9" t="n"/>

--- a/templates/25-pareto-and-distribution.xlsx
+++ b/templates/25-pareto-and-distribution.xlsx
@@ -242,10 +242,14 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
+            <a:solidFill>
+              <a:srgbClr val="1F4E79"/>
+            </a:solidFill>
             <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
+          <invertIfNegative val="0"/>
           <cat>
             <numRef>
               <f>'Pareto'!$A$5:$A$14</f>

--- a/templates/25-pareto-and-distribution.xlsx
+++ b/templates/25-pareto-and-distribution.xlsx
@@ -111,7 +111,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -127,6 +127,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -241,6 +242,9 @@
         <ser>
           <idx val="0"/>
           <order val="0"/>
+          <tx>
+            <v>Count</v>
+          </tx>
           <spPr>
             <a:solidFill>
               <a:srgbClr val="1F4E79"/>
@@ -270,8 +274,14 @@
         <ser>
           <idx val="1"/>
           <order val="1"/>
+          <tx>
+            <v>Cumulative share</v>
+          </tx>
           <spPr>
-            <a:ln>
+            <a:ln w="24000">
+              <a:solidFill>
+                <a:srgbClr val="B45309"/>
+              </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -286,6 +296,34 @@
           <val>
             <numRef>
               <f>'Pareto'!$D$5:$D$14</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <v>80% — the vital few are left of here</v>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="C0392B"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <val>
+            <numRef>
+              <f>'Pareto'!$F$5:$F$14</f>
             </numRef>
           </val>
         </ser>
@@ -340,6 +378,7 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
         <title>
@@ -364,6 +403,9 @@
         <crosses val="max"/>
       </valAx>
     </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
@@ -818,7 +860,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -873,6 +915,11 @@
           <t>Validated by reading tickets?</t>
         </is>
       </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>80% line</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
@@ -892,318 +939,358 @@
         <v/>
       </c>
       <c r="E5" s="7" t="n"/>
+      <c r="F5" s="9">
+        <f>IF(B5="","",0.8)</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Wrong plan applied</t>
         </is>
       </c>
-      <c r="B6" s="9" t="n">
+      <c r="B6" s="10" t="n">
         <v>233</v>
       </c>
-      <c r="C6" s="10">
+      <c r="C6" s="11">
         <f>IF(OR(B6="",SUM($B$5:$B$24)=0),"",B6/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D6" s="10">
+      <c r="D6" s="11">
         <f>IF(OR(B6="",SUM($B$5:$B$24)=0),"",SUM($B$5:B6)/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="E6" s="9" t="n"/>
+      <c r="E6" s="10" t="n"/>
+      <c r="F6" s="9">
+        <f>IF(B6="","",0.8)</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>Duplicate charge</t>
         </is>
       </c>
-      <c r="B7" s="9" t="n">
+      <c r="B7" s="10" t="n">
         <v>151</v>
       </c>
-      <c r="C7" s="10">
+      <c r="C7" s="11">
         <f>IF(OR(B7="",SUM($B$5:$B$24)=0),"",B7/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D7" s="10">
+      <c r="D7" s="11">
         <f>IF(OR(B7="",SUM($B$5:$B$24)=0),"",SUM($B$5:B7)/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="E7" s="9" t="n"/>
+      <c r="E7" s="10" t="n"/>
+      <c r="F7" s="9">
+        <f>IF(B7="","",0.8)</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>Proration misunderstood</t>
         </is>
       </c>
-      <c r="B8" s="9" t="n">
+      <c r="B8" s="10" t="n">
         <v>96</v>
       </c>
-      <c r="C8" s="10">
+      <c r="C8" s="11">
         <f>IF(OR(B8="",SUM($B$5:$B$24)=0),"",B8/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D8" s="10">
+      <c r="D8" s="11">
         <f>IF(OR(B8="",SUM($B$5:$B$24)=0),"",SUM($B$5:B8)/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="E8" s="9" t="n"/>
+      <c r="E8" s="10" t="n"/>
+      <c r="F8" s="9">
+        <f>IF(B8="","",0.8)</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>Refund timing</t>
         </is>
       </c>
-      <c r="B9" s="9" t="n">
+      <c r="B9" s="10" t="n">
         <v>74</v>
       </c>
-      <c r="C9" s="10">
+      <c r="C9" s="11">
         <f>IF(OR(B9="",SUM($B$5:$B$24)=0),"",B9/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D9" s="10">
+      <c r="D9" s="11">
         <f>IF(OR(B9="",SUM($B$5:$B$24)=0),"",SUM($B$5:B9)/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="E9" s="9" t="n"/>
+      <c r="E9" s="10" t="n"/>
+      <c r="F9" s="9">
+        <f>IF(B9="","",0.8)</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="n"/>
-      <c r="B10" s="9" t="n"/>
-      <c r="C10" s="10">
+      <c r="A10" s="10" t="n"/>
+      <c r="B10" s="10" t="n"/>
+      <c r="C10" s="11">
         <f>IF(OR(B10="",SUM($B$5:$B$24)=0),"",B10/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D10" s="10">
+      <c r="D10" s="11">
         <f>IF(OR(B10="",SUM($B$5:$B$24)=0),"",SUM($B$5:B10)/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="E10" s="9" t="n"/>
+      <c r="E10" s="10" t="n"/>
+      <c r="F10" s="9">
+        <f>IF(B10="","",0.8)</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="n"/>
-      <c r="B11" s="9" t="n"/>
-      <c r="C11" s="10">
+      <c r="A11" s="10" t="n"/>
+      <c r="B11" s="10" t="n"/>
+      <c r="C11" s="11">
         <f>IF(OR(B11="",SUM($B$5:$B$24)=0),"",B11/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D11" s="10">
+      <c r="D11" s="11">
         <f>IF(OR(B11="",SUM($B$5:$B$24)=0),"",SUM($B$5:B11)/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="E11" s="9" t="n"/>
+      <c r="E11" s="10" t="n"/>
+      <c r="F11" s="9">
+        <f>IF(B11="","",0.8)</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="n"/>
-      <c r="B12" s="9" t="n"/>
-      <c r="C12" s="10">
+      <c r="A12" s="10" t="n"/>
+      <c r="B12" s="10" t="n"/>
+      <c r="C12" s="11">
         <f>IF(OR(B12="",SUM($B$5:$B$24)=0),"",B12/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D12" s="10">
+      <c r="D12" s="11">
         <f>IF(OR(B12="",SUM($B$5:$B$24)=0),"",SUM($B$5:B12)/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="E12" s="9" t="n"/>
+      <c r="E12" s="10" t="n"/>
+      <c r="F12" s="9">
+        <f>IF(B12="","",0.8)</f>
+        <v/>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="n"/>
-      <c r="B13" s="9" t="n"/>
-      <c r="C13" s="10">
+      <c r="A13" s="10" t="n"/>
+      <c r="B13" s="10" t="n"/>
+      <c r="C13" s="11">
         <f>IF(OR(B13="",SUM($B$5:$B$24)=0),"",B13/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D13" s="10">
+      <c r="D13" s="11">
         <f>IF(OR(B13="",SUM($B$5:$B$24)=0),"",SUM($B$5:B13)/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="E13" s="9" t="n"/>
+      <c r="E13" s="10" t="n"/>
+      <c r="F13" s="9">
+        <f>IF(B13="","",0.8)</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="n"/>
-      <c r="B14" s="9" t="n"/>
-      <c r="C14" s="10">
+      <c r="A14" s="10" t="n"/>
+      <c r="B14" s="10" t="n"/>
+      <c r="C14" s="11">
         <f>IF(OR(B14="",SUM($B$5:$B$24)=0),"",B14/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D14" s="10">
+      <c r="D14" s="11">
         <f>IF(OR(B14="",SUM($B$5:$B$24)=0),"",SUM($B$5:B14)/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="E14" s="9" t="n"/>
+      <c r="E14" s="10" t="n"/>
+      <c r="F14" s="9">
+        <f>IF(B14="","",0.8)</f>
+        <v/>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="n"/>
-      <c r="B15" s="9" t="n"/>
-      <c r="C15" s="10">
+      <c r="A15" s="10" t="n"/>
+      <c r="B15" s="10" t="n"/>
+      <c r="C15" s="11">
         <f>IF(OR(B15="",SUM($B$5:$B$24)=0),"",B15/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D15" s="10">
+      <c r="D15" s="11">
         <f>IF(OR(B15="",SUM($B$5:$B$24)=0),"",SUM($B$5:B15)/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="E15" s="9" t="n"/>
+      <c r="E15" s="10" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="n"/>
-      <c r="B16" s="9" t="n"/>
-      <c r="C16" s="10">
+      <c r="A16" s="10" t="n"/>
+      <c r="B16" s="10" t="n"/>
+      <c r="C16" s="11">
         <f>IF(OR(B16="",SUM($B$5:$B$24)=0),"",B16/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D16" s="10">
+      <c r="D16" s="11">
         <f>IF(OR(B16="",SUM($B$5:$B$24)=0),"",SUM($B$5:B16)/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="E16" s="9" t="n"/>
+      <c r="E16" s="10" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="n"/>
-      <c r="B17" s="9" t="n"/>
-      <c r="C17" s="10">
+      <c r="A17" s="10" t="n"/>
+      <c r="B17" s="10" t="n"/>
+      <c r="C17" s="11">
         <f>IF(OR(B17="",SUM($B$5:$B$24)=0),"",B17/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D17" s="10">
+      <c r="D17" s="11">
         <f>IF(OR(B17="",SUM($B$5:$B$24)=0),"",SUM($B$5:B17)/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="E17" s="9" t="n"/>
+      <c r="E17" s="10" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="n"/>
-      <c r="B18" s="9" t="n"/>
-      <c r="C18" s="10">
+      <c r="A18" s="10" t="n"/>
+      <c r="B18" s="10" t="n"/>
+      <c r="C18" s="11">
         <f>IF(OR(B18="",SUM($B$5:$B$24)=0),"",B18/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D18" s="10">
+      <c r="D18" s="11">
         <f>IF(OR(B18="",SUM($B$5:$B$24)=0),"",SUM($B$5:B18)/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="E18" s="9" t="n"/>
+      <c r="E18" s="10" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="9" t="n"/>
-      <c r="B19" s="9" t="n"/>
-      <c r="C19" s="10">
+      <c r="A19" s="10" t="n"/>
+      <c r="B19" s="10" t="n"/>
+      <c r="C19" s="11">
         <f>IF(OR(B19="",SUM($B$5:$B$24)=0),"",B19/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D19" s="10">
+      <c r="D19" s="11">
         <f>IF(OR(B19="",SUM($B$5:$B$24)=0),"",SUM($B$5:B19)/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="E19" s="9" t="n"/>
+      <c r="E19" s="10" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="n"/>
-      <c r="B20" s="9" t="n"/>
-      <c r="C20" s="10">
+      <c r="A20" s="10" t="n"/>
+      <c r="B20" s="10" t="n"/>
+      <c r="C20" s="11">
         <f>IF(OR(B20="",SUM($B$5:$B$24)=0),"",B20/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D20" s="10">
+      <c r="D20" s="11">
         <f>IF(OR(B20="",SUM($B$5:$B$24)=0),"",SUM($B$5:B20)/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="E20" s="9" t="n"/>
+      <c r="E20" s="10" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="n"/>
-      <c r="B21" s="9" t="n"/>
-      <c r="C21" s="10">
+      <c r="A21" s="10" t="n"/>
+      <c r="B21" s="10" t="n"/>
+      <c r="C21" s="11">
         <f>IF(OR(B21="",SUM($B$5:$B$24)=0),"",B21/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D21" s="10">
+      <c r="D21" s="11">
         <f>IF(OR(B21="",SUM($B$5:$B$24)=0),"",SUM($B$5:B21)/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="E21" s="9" t="n"/>
+      <c r="E21" s="10" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="n"/>
-      <c r="B22" s="9" t="n"/>
-      <c r="C22" s="10">
+      <c r="A22" s="10" t="n"/>
+      <c r="B22" s="10" t="n"/>
+      <c r="C22" s="11">
         <f>IF(OR(B22="",SUM($B$5:$B$24)=0),"",B22/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D22" s="10">
+      <c r="D22" s="11">
         <f>IF(OR(B22="",SUM($B$5:$B$24)=0),"",SUM($B$5:B22)/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="E22" s="9" t="n"/>
+      <c r="E22" s="10" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="9" t="n"/>
-      <c r="B23" s="9" t="n"/>
-      <c r="C23" s="10">
+      <c r="A23" s="10" t="n"/>
+      <c r="B23" s="10" t="n"/>
+      <c r="C23" s="11">
         <f>IF(OR(B23="",SUM($B$5:$B$24)=0),"",B23/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D23" s="10">
+      <c r="D23" s="11">
         <f>IF(OR(B23="",SUM($B$5:$B$24)=0),"",SUM($B$5:B23)/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="E23" s="9" t="n"/>
+      <c r="E23" s="10" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="9" t="n"/>
-      <c r="B24" s="9" t="n"/>
-      <c r="C24" s="10">
+      <c r="A24" s="10" t="n"/>
+      <c r="B24" s="10" t="n"/>
+      <c r="C24" s="11">
         <f>IF(OR(B24="",SUM($B$5:$B$24)=0),"",B24/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D24" s="10">
+      <c r="D24" s="11">
         <f>IF(OR(B24="",SUM($B$5:$B$24)=0),"",SUM($B$5:B24)/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="E24" s="9" t="n"/>
+      <c r="E24" s="10" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="11" t="inlineStr">
+      <c r="A26" s="12" t="inlineStr">
         <is>
           <t>SUMMARY</t>
         </is>
       </c>
-      <c r="B26" s="12" t="n"/>
-      <c r="C26" s="12" t="n"/>
-      <c r="D26" s="12" t="n"/>
-      <c r="E26" s="12" t="n"/>
+      <c r="B26" s="13" t="n"/>
+      <c r="C26" s="13" t="n"/>
+      <c r="D26" s="13" t="n"/>
+      <c r="E26" s="13" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="13" t="inlineStr">
+      <c r="A27" s="14" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C27" s="14">
+      <c r="C27" s="15">
         <f>SUM(B5:B24)</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="13" t="inlineStr">
+      <c r="A28" s="14" t="inlineStr">
         <is>
           <t>Categories</t>
         </is>
       </c>
-      <c r="C28" s="14">
+      <c r="C28" s="15">
         <f>COUNTA(A5:A24)</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="13" t="inlineStr">
+      <c r="A29" s="14" t="inlineStr">
         <is>
           <t>Share explained by the top three</t>
         </is>
       </c>
-      <c r="C29" s="10">
+      <c r="C29" s="11">
         <f>IFERROR(SUM(B5:B7)/SUM(B5:B24),"")</f>
         <v/>
       </c>
@@ -1296,135 +1383,135 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
-      <c r="B6" s="15">
+      <c r="B6" s="16">
         <f>COUNT($B$20:$B$1000)</f>
         <v/>
       </c>
-      <c r="D6" s="16" t="inlineStr">
+      <c r="D6" s="17" t="inlineStr">
         <is>
           <t>How many values you pasted.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>Mean</t>
         </is>
       </c>
-      <c r="B7" s="15">
+      <c r="B7" s="16">
         <f>IFERROR(AVERAGE($B$20:$B$1000),"")</f>
         <v/>
       </c>
-      <c r="D7" s="16" t="inlineStr">
+      <c r="D7" s="17" t="inlineStr">
         <is>
           <t>Dragged upward by the long tail. Rarely the number to quote.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>Median (p50)</t>
         </is>
       </c>
-      <c r="B8" s="15">
+      <c r="B8" s="16">
         <f>IFERROR(MEDIAN($B$20:$B$1000),"")</f>
         <v/>
       </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="D8" s="17" t="inlineStr">
         <is>
           <t>The typical experience. Quote this.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>p90</t>
         </is>
       </c>
-      <c r="B9" s="15">
+      <c r="B9" s="16">
         <f>IFERROR(PERCENTILE($B$20:$B$1000,0.9),"")</f>
         <v/>
       </c>
-      <c r="D9" s="16" t="inlineStr">
+      <c r="D9" s="17" t="inlineStr">
         <is>
           <t>What your worst-served customers get. This is what generates complaints.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="13" t="inlineStr">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>Standard deviation</t>
         </is>
       </c>
-      <c r="B10" s="15">
+      <c r="B10" s="16">
         <f>IFERROR(STDEV($B$20:$B$1000),"")</f>
         <v/>
       </c>
-      <c r="D10" s="16" t="inlineStr">
+      <c r="D10" s="17" t="inlineStr">
         <is>
           <t>Assumes symmetry, so it describes skewed data poorly.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="13" t="inlineStr">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>Interquartile range</t>
         </is>
       </c>
-      <c r="B11" s="15">
+      <c r="B11" s="16">
         <f>IFERROR(QUARTILE($B$20:$B$1000,3)-QUARTILE($B$20:$B$1000,1),"")</f>
         <v/>
       </c>
-      <c r="D11" s="16" t="inlineStr">
+      <c r="D11" s="17" t="inlineStr">
         <is>
           <t>The middle half. A better spread measure for this data.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="13" t="inlineStr">
+      <c r="A12" s="14" t="inlineStr">
         <is>
           <t>Mean ÷ median</t>
         </is>
       </c>
-      <c r="B12" s="15">
+      <c r="B12" s="16">
         <f>IFERROR(AVERAGE($B$20:$B$1000)/MEDIAN($B$20:$B$1000),"")</f>
         <v/>
       </c>
-      <c r="D12" s="16" t="inlineStr">
+      <c r="D12" s="17" t="inlineStr">
         <is>
           <t>Above about 1.2 means meaningful right skew — use non-parametric tests and quote percentiles.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="14" t="inlineStr">
+      <c r="A14" s="15" t="inlineStr">
         <is>
           <t>VERDICT</t>
         </is>
       </c>
-      <c r="B14" s="12" t="n"/>
-      <c r="C14" s="12" t="n"/>
-      <c r="D14" s="12" t="n"/>
+      <c r="B14" s="13" t="n"/>
+      <c r="C14" s="13" t="n"/>
+      <c r="D14" s="13" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="17">
+      <c r="A15" s="18">
         <f>IF(COUNT($B$20:$B$1000)=0,"Paste your data into column B below.",IF(AVERAGE($B$20:$B$1000)/MEDIAN($B$20:$B$1000)&gt;1.2,"RIGHT-SKEWED — quote the median and p90, and prefer non-parametric tests.","ROUGHLY SYMMETRIC — the mean and a parametric test are defensible."))</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="13" t="inlineStr">
+      <c r="A18" s="14" t="inlineStr">
         <is>
           <t>Your data</t>
         </is>
@@ -1438,124 +1525,124 @@
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="9" t="n"/>
+      <c r="B20" s="10" t="n"/>
     </row>
     <row r="21">
-      <c r="B21" s="9" t="n"/>
+      <c r="B21" s="10" t="n"/>
     </row>
     <row r="22">
-      <c r="B22" s="9" t="n"/>
+      <c r="B22" s="10" t="n"/>
     </row>
     <row r="23">
-      <c r="B23" s="9" t="n"/>
+      <c r="B23" s="10" t="n"/>
     </row>
     <row r="24">
-      <c r="B24" s="9" t="n"/>
+      <c r="B24" s="10" t="n"/>
     </row>
     <row r="25">
-      <c r="B25" s="9" t="n"/>
+      <c r="B25" s="10" t="n"/>
     </row>
     <row r="26">
-      <c r="B26" s="9" t="n"/>
+      <c r="B26" s="10" t="n"/>
     </row>
     <row r="27">
-      <c r="B27" s="9" t="n"/>
+      <c r="B27" s="10" t="n"/>
     </row>
     <row r="28">
-      <c r="B28" s="9" t="n"/>
+      <c r="B28" s="10" t="n"/>
     </row>
     <row r="29">
-      <c r="B29" s="9" t="n"/>
+      <c r="B29" s="10" t="n"/>
     </row>
     <row r="30">
-      <c r="B30" s="9" t="n"/>
+      <c r="B30" s="10" t="n"/>
     </row>
     <row r="31">
-      <c r="B31" s="9" t="n"/>
+      <c r="B31" s="10" t="n"/>
     </row>
     <row r="32">
-      <c r="B32" s="9" t="n"/>
+      <c r="B32" s="10" t="n"/>
     </row>
     <row r="33">
-      <c r="B33" s="9" t="n"/>
+      <c r="B33" s="10" t="n"/>
     </row>
     <row r="34">
-      <c r="B34" s="9" t="n"/>
+      <c r="B34" s="10" t="n"/>
     </row>
     <row r="35">
-      <c r="B35" s="9" t="n"/>
+      <c r="B35" s="10" t="n"/>
     </row>
     <row r="36">
-      <c r="B36" s="9" t="n"/>
+      <c r="B36" s="10" t="n"/>
     </row>
     <row r="37">
-      <c r="B37" s="9" t="n"/>
+      <c r="B37" s="10" t="n"/>
     </row>
     <row r="38">
-      <c r="B38" s="9" t="n"/>
+      <c r="B38" s="10" t="n"/>
     </row>
     <row r="39">
-      <c r="B39" s="9" t="n"/>
+      <c r="B39" s="10" t="n"/>
     </row>
     <row r="40">
-      <c r="B40" s="9" t="n"/>
+      <c r="B40" s="10" t="n"/>
     </row>
     <row r="41">
-      <c r="B41" s="9" t="n"/>
+      <c r="B41" s="10" t="n"/>
     </row>
     <row r="42">
-      <c r="B42" s="9" t="n"/>
+      <c r="B42" s="10" t="n"/>
     </row>
     <row r="43">
-      <c r="B43" s="9" t="n"/>
+      <c r="B43" s="10" t="n"/>
     </row>
     <row r="44">
-      <c r="B44" s="9" t="n"/>
+      <c r="B44" s="10" t="n"/>
     </row>
     <row r="45">
-      <c r="B45" s="9" t="n"/>
+      <c r="B45" s="10" t="n"/>
     </row>
     <row r="46">
-      <c r="B46" s="9" t="n"/>
+      <c r="B46" s="10" t="n"/>
     </row>
     <row r="47">
-      <c r="B47" s="9" t="n"/>
+      <c r="B47" s="10" t="n"/>
     </row>
     <row r="48">
-      <c r="B48" s="9" t="n"/>
+      <c r="B48" s="10" t="n"/>
     </row>
     <row r="49">
-      <c r="B49" s="9" t="n"/>
+      <c r="B49" s="10" t="n"/>
     </row>
     <row r="50">
-      <c r="B50" s="9" t="n"/>
+      <c r="B50" s="10" t="n"/>
     </row>
     <row r="51">
-      <c r="B51" s="9" t="n"/>
+      <c r="B51" s="10" t="n"/>
     </row>
     <row r="52">
-      <c r="B52" s="9" t="n"/>
+      <c r="B52" s="10" t="n"/>
     </row>
     <row r="53">
-      <c r="B53" s="9" t="n"/>
+      <c r="B53" s="10" t="n"/>
     </row>
     <row r="54">
-      <c r="B54" s="9" t="n"/>
+      <c r="B54" s="10" t="n"/>
     </row>
     <row r="55">
-      <c r="B55" s="9" t="n"/>
+      <c r="B55" s="10" t="n"/>
     </row>
     <row r="56">
-      <c r="B56" s="9" t="n"/>
+      <c r="B56" s="10" t="n"/>
     </row>
     <row r="57">
-      <c r="B57" s="9" t="n"/>
+      <c r="B57" s="10" t="n"/>
     </row>
     <row r="58">
-      <c r="B58" s="9" t="n"/>
+      <c r="B58" s="10" t="n"/>
     </row>
     <row r="59">
-      <c r="B59" s="9" t="n"/>
+      <c r="B59" s="10" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="4">

--- a/templates/25-pareto-and-distribution.xlsx
+++ b/templates/25-pareto-and-distribution.xlsx
@@ -111,7 +111,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -122,18 +122,21 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -256,12 +259,12 @@
           <invertIfNegative val="0"/>
           <cat>
             <numRef>
-              <f>'Pareto'!$A$5:$A$14</f>
+              <f>'Pareto'!$H$5:$H$14</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Pareto'!$B$5:$B$14</f>
+              <f>'Pareto'!$I$5:$I$14</f>
             </numRef>
           </val>
         </ser>
@@ -295,7 +298,7 @@
           </marker>
           <val>
             <numRef>
-              <f>'Pareto'!$D$5:$D$14</f>
+              <f>'Pareto'!$J$5:$J$14</f>
             </numRef>
           </val>
         </ser>
@@ -323,7 +326,7 @@
           </marker>
           <val>
             <numRef>
-              <f>'Pareto'!$F$5:$F$14</f>
+              <f>'Pareto'!$K$5:$K$14</f>
             </numRef>
           </val>
         </ser>
@@ -860,14 +863,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:K31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="3" customWidth="1" min="6" max="6"/>
+    <col width="7" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -888,410 +897,761 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
+    <row r="3">
+      <c r="G3" s="6" t="inlineStr">
+        <is>
+          <t>RANKED — this is what the chart plots. Type above in any order; this sorts itself.</t>
+        </is>
+      </c>
+      <c r="H3" s="7" t="n"/>
+      <c r="I3" s="7" t="n"/>
+      <c r="J3" s="7" t="n"/>
+      <c r="K3" s="7" t="n"/>
+    </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr"/>
+      <c r="B4" s="8" t="inlineStr"/>
+      <c r="C4" s="8" t="inlineStr"/>
+      <c r="D4" s="8" t="inlineStr"/>
+      <c r="E4" s="8" t="inlineStr"/>
+      <c r="F4" s="8" t="inlineStr"/>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="H4" s="8" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="I4" s="8" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>Share</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="J4" s="8" t="inlineStr">
         <is>
           <t>Cumulative</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>Validated by reading tickets?</t>
-        </is>
-      </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="K4" s="8" t="inlineStr">
         <is>
           <t>80% line</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>Adjustment not posted at closure</t>
         </is>
       </c>
-      <c r="B5" s="7" t="n">
+      <c r="B5" s="9" t="n">
         <v>412</v>
       </c>
-      <c r="C5" s="8">
+      <c r="C5" s="10">
         <f>IF(OR(B5="",SUM($B$5:$B$24)=0),"",B5/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D5" s="8">
-        <f>IF(OR(B5="",SUM($B$5:$B$24)=0),"",SUM($B$5:B5)/SUM($B$5:$B$24))</f>
-        <v/>
-      </c>
-      <c r="E5" s="7" t="n"/>
-      <c r="F5" s="9">
-        <f>IF(B5="","",0.8)</f>
+      <c r="D5" s="11">
+        <f>IF(B5="","",RANK(B5,$B$5:$B$24,0)+COUNTIF($B$5:B5,B5)-1)</f>
+        <v/>
+      </c>
+      <c r="E5" s="9" t="n"/>
+      <c r="G5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="12">
+        <f>IFERROR(INDEX($A$5:$A$24,MATCH(G5,$D$5:$D$24,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I5" s="13">
+        <f>IFERROR(INDEX($B$5:$B$24,MATCH(G5,$D$5:$D$24,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J5" s="14">
+        <f>IF(I5="","",SUM($I$5:I5)/SUM($I$5:$I$24))</f>
+        <v/>
+      </c>
+      <c r="K5" s="15">
+        <f>IF(I5="","",0.8)</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>Wrong plan applied</t>
         </is>
       </c>
-      <c r="B6" s="10" t="n">
+      <c r="B6" s="16" t="n">
         <v>233</v>
       </c>
-      <c r="C6" s="11">
+      <c r="C6" s="14">
         <f>IF(OR(B6="",SUM($B$5:$B$24)=0),"",B6/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D6" s="11">
-        <f>IF(OR(B6="",SUM($B$5:$B$24)=0),"",SUM($B$5:B6)/SUM($B$5:$B$24))</f>
-        <v/>
-      </c>
-      <c r="E6" s="10" t="n"/>
-      <c r="F6" s="9">
-        <f>IF(B6="","",0.8)</f>
+      <c r="D6" s="17">
+        <f>IF(B6="","",RANK(B6,$B$5:$B$24,0)+COUNTIF($B$5:B6,B6)-1)</f>
+        <v/>
+      </c>
+      <c r="E6" s="16" t="n"/>
+      <c r="G6" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H6" s="12">
+        <f>IFERROR(INDEX($A$5:$A$24,MATCH(G6,$D$5:$D$24,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I6" s="13">
+        <f>IFERROR(INDEX($B$5:$B$24,MATCH(G6,$D$5:$D$24,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J6" s="14">
+        <f>IF(I6="","",SUM($I$5:I6)/SUM($I$5:$I$24))</f>
+        <v/>
+      </c>
+      <c r="K6" s="15">
+        <f>IF(I6="","",0.8)</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>Duplicate charge</t>
         </is>
       </c>
-      <c r="B7" s="10" t="n">
+      <c r="B7" s="16" t="n">
         <v>151</v>
       </c>
-      <c r="C7" s="11">
+      <c r="C7" s="14">
         <f>IF(OR(B7="",SUM($B$5:$B$24)=0),"",B7/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D7" s="11">
-        <f>IF(OR(B7="",SUM($B$5:$B$24)=0),"",SUM($B$5:B7)/SUM($B$5:$B$24))</f>
-        <v/>
-      </c>
-      <c r="E7" s="10" t="n"/>
-      <c r="F7" s="9">
-        <f>IF(B7="","",0.8)</f>
+      <c r="D7" s="17">
+        <f>IF(B7="","",RANK(B7,$B$5:$B$24,0)+COUNTIF($B$5:B7,B7)-1)</f>
+        <v/>
+      </c>
+      <c r="E7" s="16" t="n"/>
+      <c r="G7" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H7" s="12">
+        <f>IFERROR(INDEX($A$5:$A$24,MATCH(G7,$D$5:$D$24,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I7" s="13">
+        <f>IFERROR(INDEX($B$5:$B$24,MATCH(G7,$D$5:$D$24,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J7" s="14">
+        <f>IF(I7="","",SUM($I$5:I7)/SUM($I$5:$I$24))</f>
+        <v/>
+      </c>
+      <c r="K7" s="15">
+        <f>IF(I7="","",0.8)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>Proration misunderstood</t>
         </is>
       </c>
-      <c r="B8" s="10" t="n">
+      <c r="B8" s="16" t="n">
         <v>96</v>
       </c>
-      <c r="C8" s="11">
+      <c r="C8" s="14">
         <f>IF(OR(B8="",SUM($B$5:$B$24)=0),"",B8/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D8" s="11">
-        <f>IF(OR(B8="",SUM($B$5:$B$24)=0),"",SUM($B$5:B8)/SUM($B$5:$B$24))</f>
-        <v/>
-      </c>
-      <c r="E8" s="10" t="n"/>
-      <c r="F8" s="9">
-        <f>IF(B8="","",0.8)</f>
+      <c r="D8" s="17">
+        <f>IF(B8="","",RANK(B8,$B$5:$B$24,0)+COUNTIF($B$5:B8,B8)-1)</f>
+        <v/>
+      </c>
+      <c r="E8" s="16" t="n"/>
+      <c r="G8" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="H8" s="12">
+        <f>IFERROR(INDEX($A$5:$A$24,MATCH(G8,$D$5:$D$24,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I8" s="13">
+        <f>IFERROR(INDEX($B$5:$B$24,MATCH(G8,$D$5:$D$24,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J8" s="14">
+        <f>IF(I8="","",SUM($I$5:I8)/SUM($I$5:$I$24))</f>
+        <v/>
+      </c>
+      <c r="K8" s="15">
+        <f>IF(I8="","",0.8)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>Refund timing</t>
         </is>
       </c>
-      <c r="B9" s="10" t="n">
+      <c r="B9" s="16" t="n">
         <v>74</v>
       </c>
-      <c r="C9" s="11">
+      <c r="C9" s="14">
         <f>IF(OR(B9="",SUM($B$5:$B$24)=0),"",B9/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D9" s="11">
-        <f>IF(OR(B9="",SUM($B$5:$B$24)=0),"",SUM($B$5:B9)/SUM($B$5:$B$24))</f>
-        <v/>
-      </c>
-      <c r="E9" s="10" t="n"/>
-      <c r="F9" s="9">
-        <f>IF(B9="","",0.8)</f>
+      <c r="D9" s="17">
+        <f>IF(B9="","",RANK(B9,$B$5:$B$24,0)+COUNTIF($B$5:B9,B9)-1)</f>
+        <v/>
+      </c>
+      <c r="E9" s="16" t="n"/>
+      <c r="G9" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="H9" s="12">
+        <f>IFERROR(INDEX($A$5:$A$24,MATCH(G9,$D$5:$D$24,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I9" s="13">
+        <f>IFERROR(INDEX($B$5:$B$24,MATCH(G9,$D$5:$D$24,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J9" s="14">
+        <f>IF(I9="","",SUM($I$5:I9)/SUM($I$5:$I$24))</f>
+        <v/>
+      </c>
+      <c r="K9" s="15">
+        <f>IF(I9="","",0.8)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="n"/>
-      <c r="B10" s="10" t="n"/>
-      <c r="C10" s="11">
+      <c r="A10" s="16" t="n"/>
+      <c r="B10" s="16" t="n"/>
+      <c r="C10" s="14">
         <f>IF(OR(B10="",SUM($B$5:$B$24)=0),"",B10/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D10" s="11">
-        <f>IF(OR(B10="",SUM($B$5:$B$24)=0),"",SUM($B$5:B10)/SUM($B$5:$B$24))</f>
-        <v/>
-      </c>
-      <c r="E10" s="10" t="n"/>
-      <c r="F10" s="9">
-        <f>IF(B10="","",0.8)</f>
+      <c r="D10" s="17">
+        <f>IF(B10="","",RANK(B10,$B$5:$B$24,0)+COUNTIF($B$5:B10,B10)-1)</f>
+        <v/>
+      </c>
+      <c r="E10" s="16" t="n"/>
+      <c r="G10" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H10" s="12">
+        <f>IFERROR(INDEX($A$5:$A$24,MATCH(G10,$D$5:$D$24,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I10" s="13">
+        <f>IFERROR(INDEX($B$5:$B$24,MATCH(G10,$D$5:$D$24,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J10" s="14">
+        <f>IF(I10="","",SUM($I$5:I10)/SUM($I$5:$I$24))</f>
+        <v/>
+      </c>
+      <c r="K10" s="15">
+        <f>IF(I10="","",0.8)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="n"/>
-      <c r="B11" s="10" t="n"/>
-      <c r="C11" s="11">
+      <c r="A11" s="16" t="n"/>
+      <c r="B11" s="16" t="n"/>
+      <c r="C11" s="14">
         <f>IF(OR(B11="",SUM($B$5:$B$24)=0),"",B11/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D11" s="11">
-        <f>IF(OR(B11="",SUM($B$5:$B$24)=0),"",SUM($B$5:B11)/SUM($B$5:$B$24))</f>
-        <v/>
-      </c>
-      <c r="E11" s="10" t="n"/>
-      <c r="F11" s="9">
-        <f>IF(B11="","",0.8)</f>
+      <c r="D11" s="17">
+        <f>IF(B11="","",RANK(B11,$B$5:$B$24,0)+COUNTIF($B$5:B11,B11)-1)</f>
+        <v/>
+      </c>
+      <c r="E11" s="16" t="n"/>
+      <c r="G11" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="H11" s="12">
+        <f>IFERROR(INDEX($A$5:$A$24,MATCH(G11,$D$5:$D$24,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I11" s="13">
+        <f>IFERROR(INDEX($B$5:$B$24,MATCH(G11,$D$5:$D$24,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J11" s="14">
+        <f>IF(I11="","",SUM($I$5:I11)/SUM($I$5:$I$24))</f>
+        <v/>
+      </c>
+      <c r="K11" s="15">
+        <f>IF(I11="","",0.8)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="10" t="n"/>
-      <c r="B12" s="10" t="n"/>
-      <c r="C12" s="11">
+      <c r="A12" s="16" t="n"/>
+      <c r="B12" s="16" t="n"/>
+      <c r="C12" s="14">
         <f>IF(OR(B12="",SUM($B$5:$B$24)=0),"",B12/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D12" s="11">
-        <f>IF(OR(B12="",SUM($B$5:$B$24)=0),"",SUM($B$5:B12)/SUM($B$5:$B$24))</f>
-        <v/>
-      </c>
-      <c r="E12" s="10" t="n"/>
-      <c r="F12" s="9">
-        <f>IF(B12="","",0.8)</f>
+      <c r="D12" s="17">
+        <f>IF(B12="","",RANK(B12,$B$5:$B$24,0)+COUNTIF($B$5:B12,B12)-1)</f>
+        <v/>
+      </c>
+      <c r="E12" s="16" t="n"/>
+      <c r="G12" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="H12" s="12">
+        <f>IFERROR(INDEX($A$5:$A$24,MATCH(G12,$D$5:$D$24,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I12" s="13">
+        <f>IFERROR(INDEX($B$5:$B$24,MATCH(G12,$D$5:$D$24,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J12" s="14">
+        <f>IF(I12="","",SUM($I$5:I12)/SUM($I$5:$I$24))</f>
+        <v/>
+      </c>
+      <c r="K12" s="15">
+        <f>IF(I12="","",0.8)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="10" t="n"/>
-      <c r="B13" s="10" t="n"/>
-      <c r="C13" s="11">
+      <c r="A13" s="16" t="n"/>
+      <c r="B13" s="16" t="n"/>
+      <c r="C13" s="14">
         <f>IF(OR(B13="",SUM($B$5:$B$24)=0),"",B13/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D13" s="11">
-        <f>IF(OR(B13="",SUM($B$5:$B$24)=0),"",SUM($B$5:B13)/SUM($B$5:$B$24))</f>
-        <v/>
-      </c>
-      <c r="E13" s="10" t="n"/>
-      <c r="F13" s="9">
-        <f>IF(B13="","",0.8)</f>
+      <c r="D13" s="17">
+        <f>IF(B13="","",RANK(B13,$B$5:$B$24,0)+COUNTIF($B$5:B13,B13)-1)</f>
+        <v/>
+      </c>
+      <c r="E13" s="16" t="n"/>
+      <c r="G13" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="H13" s="12">
+        <f>IFERROR(INDEX($A$5:$A$24,MATCH(G13,$D$5:$D$24,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I13" s="13">
+        <f>IFERROR(INDEX($B$5:$B$24,MATCH(G13,$D$5:$D$24,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J13" s="14">
+        <f>IF(I13="","",SUM($I$5:I13)/SUM($I$5:$I$24))</f>
+        <v/>
+      </c>
+      <c r="K13" s="15">
+        <f>IF(I13="","",0.8)</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="10" t="n"/>
-      <c r="B14" s="10" t="n"/>
-      <c r="C14" s="11">
+      <c r="A14" s="16" t="n"/>
+      <c r="B14" s="16" t="n"/>
+      <c r="C14" s="14">
         <f>IF(OR(B14="",SUM($B$5:$B$24)=0),"",B14/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D14" s="11">
-        <f>IF(OR(B14="",SUM($B$5:$B$24)=0),"",SUM($B$5:B14)/SUM($B$5:$B$24))</f>
-        <v/>
-      </c>
-      <c r="E14" s="10" t="n"/>
-      <c r="F14" s="9">
-        <f>IF(B14="","",0.8)</f>
+      <c r="D14" s="17">
+        <f>IF(B14="","",RANK(B14,$B$5:$B$24,0)+COUNTIF($B$5:B14,B14)-1)</f>
+        <v/>
+      </c>
+      <c r="E14" s="16" t="n"/>
+      <c r="G14" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="H14" s="12">
+        <f>IFERROR(INDEX($A$5:$A$24,MATCH(G14,$D$5:$D$24,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I14" s="13">
+        <f>IFERROR(INDEX($B$5:$B$24,MATCH(G14,$D$5:$D$24,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J14" s="14">
+        <f>IF(I14="","",SUM($I$5:I14)/SUM($I$5:$I$24))</f>
+        <v/>
+      </c>
+      <c r="K14" s="15">
+        <f>IF(I14="","",0.8)</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="10" t="n"/>
-      <c r="B15" s="10" t="n"/>
-      <c r="C15" s="11">
+      <c r="A15" s="16" t="n"/>
+      <c r="B15" s="16" t="n"/>
+      <c r="C15" s="14">
         <f>IF(OR(B15="",SUM($B$5:$B$24)=0),"",B15/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D15" s="11">
-        <f>IF(OR(B15="",SUM($B$5:$B$24)=0),"",SUM($B$5:B15)/SUM($B$5:$B$24))</f>
-        <v/>
-      </c>
-      <c r="E15" s="10" t="n"/>
+      <c r="D15" s="17">
+        <f>IF(B15="","",RANK(B15,$B$5:$B$24,0)+COUNTIF($B$5:B15,B15)-1)</f>
+        <v/>
+      </c>
+      <c r="E15" s="16" t="n"/>
+      <c r="G15" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="H15" s="12">
+        <f>IFERROR(INDEX($A$5:$A$24,MATCH(G15,$D$5:$D$24,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I15" s="13">
+        <f>IFERROR(INDEX($B$5:$B$24,MATCH(G15,$D$5:$D$24,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J15" s="14">
+        <f>IF(I15="","",SUM($I$5:I15)/SUM($I$5:$I$24))</f>
+        <v/>
+      </c>
+      <c r="K15" s="15">
+        <f>IF(I15="","",0.8)</f>
+        <v/>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="10" t="n"/>
-      <c r="B16" s="10" t="n"/>
-      <c r="C16" s="11">
+      <c r="A16" s="16" t="n"/>
+      <c r="B16" s="16" t="n"/>
+      <c r="C16" s="14">
         <f>IF(OR(B16="",SUM($B$5:$B$24)=0),"",B16/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D16" s="11">
-        <f>IF(OR(B16="",SUM($B$5:$B$24)=0),"",SUM($B$5:B16)/SUM($B$5:$B$24))</f>
-        <v/>
-      </c>
-      <c r="E16" s="10" t="n"/>
+      <c r="D16" s="17">
+        <f>IF(B16="","",RANK(B16,$B$5:$B$24,0)+COUNTIF($B$5:B16,B16)-1)</f>
+        <v/>
+      </c>
+      <c r="E16" s="16" t="n"/>
+      <c r="G16" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="H16" s="12">
+        <f>IFERROR(INDEX($A$5:$A$24,MATCH(G16,$D$5:$D$24,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I16" s="13">
+        <f>IFERROR(INDEX($B$5:$B$24,MATCH(G16,$D$5:$D$24,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J16" s="14">
+        <f>IF(I16="","",SUM($I$5:I16)/SUM($I$5:$I$24))</f>
+        <v/>
+      </c>
+      <c r="K16" s="15">
+        <f>IF(I16="","",0.8)</f>
+        <v/>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="10" t="n"/>
-      <c r="B17" s="10" t="n"/>
-      <c r="C17" s="11">
+      <c r="A17" s="16" t="n"/>
+      <c r="B17" s="16" t="n"/>
+      <c r="C17" s="14">
         <f>IF(OR(B17="",SUM($B$5:$B$24)=0),"",B17/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D17" s="11">
-        <f>IF(OR(B17="",SUM($B$5:$B$24)=0),"",SUM($B$5:B17)/SUM($B$5:$B$24))</f>
-        <v/>
-      </c>
-      <c r="E17" s="10" t="n"/>
+      <c r="D17" s="17">
+        <f>IF(B17="","",RANK(B17,$B$5:$B$24,0)+COUNTIF($B$5:B17,B17)-1)</f>
+        <v/>
+      </c>
+      <c r="E17" s="16" t="n"/>
+      <c r="G17" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="H17" s="12">
+        <f>IFERROR(INDEX($A$5:$A$24,MATCH(G17,$D$5:$D$24,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I17" s="13">
+        <f>IFERROR(INDEX($B$5:$B$24,MATCH(G17,$D$5:$D$24,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J17" s="14">
+        <f>IF(I17="","",SUM($I$5:I17)/SUM($I$5:$I$24))</f>
+        <v/>
+      </c>
+      <c r="K17" s="15">
+        <f>IF(I17="","",0.8)</f>
+        <v/>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="10" t="n"/>
-      <c r="B18" s="10" t="n"/>
-      <c r="C18" s="11">
+      <c r="A18" s="16" t="n"/>
+      <c r="B18" s="16" t="n"/>
+      <c r="C18" s="14">
         <f>IF(OR(B18="",SUM($B$5:$B$24)=0),"",B18/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D18" s="11">
-        <f>IF(OR(B18="",SUM($B$5:$B$24)=0),"",SUM($B$5:B18)/SUM($B$5:$B$24))</f>
-        <v/>
-      </c>
-      <c r="E18" s="10" t="n"/>
+      <c r="D18" s="17">
+        <f>IF(B18="","",RANK(B18,$B$5:$B$24,0)+COUNTIF($B$5:B18,B18)-1)</f>
+        <v/>
+      </c>
+      <c r="E18" s="16" t="n"/>
+      <c r="G18" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="H18" s="12">
+        <f>IFERROR(INDEX($A$5:$A$24,MATCH(G18,$D$5:$D$24,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I18" s="13">
+        <f>IFERROR(INDEX($B$5:$B$24,MATCH(G18,$D$5:$D$24,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J18" s="14">
+        <f>IF(I18="","",SUM($I$5:I18)/SUM($I$5:$I$24))</f>
+        <v/>
+      </c>
+      <c r="K18" s="15">
+        <f>IF(I18="","",0.8)</f>
+        <v/>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="10" t="n"/>
-      <c r="B19" s="10" t="n"/>
-      <c r="C19" s="11">
+      <c r="A19" s="16" t="n"/>
+      <c r="B19" s="16" t="n"/>
+      <c r="C19" s="14">
         <f>IF(OR(B19="",SUM($B$5:$B$24)=0),"",B19/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D19" s="11">
-        <f>IF(OR(B19="",SUM($B$5:$B$24)=0),"",SUM($B$5:B19)/SUM($B$5:$B$24))</f>
-        <v/>
-      </c>
-      <c r="E19" s="10" t="n"/>
+      <c r="D19" s="17">
+        <f>IF(B19="","",RANK(B19,$B$5:$B$24,0)+COUNTIF($B$5:B19,B19)-1)</f>
+        <v/>
+      </c>
+      <c r="E19" s="16" t="n"/>
+      <c r="G19" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="H19" s="12">
+        <f>IFERROR(INDEX($A$5:$A$24,MATCH(G19,$D$5:$D$24,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I19" s="13">
+        <f>IFERROR(INDEX($B$5:$B$24,MATCH(G19,$D$5:$D$24,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J19" s="14">
+        <f>IF(I19="","",SUM($I$5:I19)/SUM($I$5:$I$24))</f>
+        <v/>
+      </c>
+      <c r="K19" s="15">
+        <f>IF(I19="","",0.8)</f>
+        <v/>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="10" t="n"/>
-      <c r="B20" s="10" t="n"/>
-      <c r="C20" s="11">
+      <c r="A20" s="16" t="n"/>
+      <c r="B20" s="16" t="n"/>
+      <c r="C20" s="14">
         <f>IF(OR(B20="",SUM($B$5:$B$24)=0),"",B20/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D20" s="11">
-        <f>IF(OR(B20="",SUM($B$5:$B$24)=0),"",SUM($B$5:B20)/SUM($B$5:$B$24))</f>
-        <v/>
-      </c>
-      <c r="E20" s="10" t="n"/>
+      <c r="D20" s="17">
+        <f>IF(B20="","",RANK(B20,$B$5:$B$24,0)+COUNTIF($B$5:B20,B20)-1)</f>
+        <v/>
+      </c>
+      <c r="E20" s="16" t="n"/>
+      <c r="G20" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="H20" s="12">
+        <f>IFERROR(INDEX($A$5:$A$24,MATCH(G20,$D$5:$D$24,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I20" s="13">
+        <f>IFERROR(INDEX($B$5:$B$24,MATCH(G20,$D$5:$D$24,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J20" s="14">
+        <f>IF(I20="","",SUM($I$5:I20)/SUM($I$5:$I$24))</f>
+        <v/>
+      </c>
+      <c r="K20" s="15">
+        <f>IF(I20="","",0.8)</f>
+        <v/>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="10" t="n"/>
-      <c r="B21" s="10" t="n"/>
-      <c r="C21" s="11">
+      <c r="A21" s="16" t="n"/>
+      <c r="B21" s="16" t="n"/>
+      <c r="C21" s="14">
         <f>IF(OR(B21="",SUM($B$5:$B$24)=0),"",B21/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D21" s="11">
-        <f>IF(OR(B21="",SUM($B$5:$B$24)=0),"",SUM($B$5:B21)/SUM($B$5:$B$24))</f>
-        <v/>
-      </c>
-      <c r="E21" s="10" t="n"/>
+      <c r="D21" s="17">
+        <f>IF(B21="","",RANK(B21,$B$5:$B$24,0)+COUNTIF($B$5:B21,B21)-1)</f>
+        <v/>
+      </c>
+      <c r="E21" s="16" t="n"/>
+      <c r="G21" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="H21" s="12">
+        <f>IFERROR(INDEX($A$5:$A$24,MATCH(G21,$D$5:$D$24,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I21" s="13">
+        <f>IFERROR(INDEX($B$5:$B$24,MATCH(G21,$D$5:$D$24,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J21" s="14">
+        <f>IF(I21="","",SUM($I$5:I21)/SUM($I$5:$I$24))</f>
+        <v/>
+      </c>
+      <c r="K21" s="15">
+        <f>IF(I21="","",0.8)</f>
+        <v/>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="10" t="n"/>
-      <c r="B22" s="10" t="n"/>
-      <c r="C22" s="11">
+      <c r="A22" s="16" t="n"/>
+      <c r="B22" s="16" t="n"/>
+      <c r="C22" s="14">
         <f>IF(OR(B22="",SUM($B$5:$B$24)=0),"",B22/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D22" s="11">
-        <f>IF(OR(B22="",SUM($B$5:$B$24)=0),"",SUM($B$5:B22)/SUM($B$5:$B$24))</f>
-        <v/>
-      </c>
-      <c r="E22" s="10" t="n"/>
+      <c r="D22" s="17">
+        <f>IF(B22="","",RANK(B22,$B$5:$B$24,0)+COUNTIF($B$5:B22,B22)-1)</f>
+        <v/>
+      </c>
+      <c r="E22" s="16" t="n"/>
+      <c r="G22" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="H22" s="12">
+        <f>IFERROR(INDEX($A$5:$A$24,MATCH(G22,$D$5:$D$24,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I22" s="13">
+        <f>IFERROR(INDEX($B$5:$B$24,MATCH(G22,$D$5:$D$24,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J22" s="14">
+        <f>IF(I22="","",SUM($I$5:I22)/SUM($I$5:$I$24))</f>
+        <v/>
+      </c>
+      <c r="K22" s="15">
+        <f>IF(I22="","",0.8)</f>
+        <v/>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="10" t="n"/>
-      <c r="B23" s="10" t="n"/>
-      <c r="C23" s="11">
+      <c r="A23" s="16" t="n"/>
+      <c r="B23" s="16" t="n"/>
+      <c r="C23" s="14">
         <f>IF(OR(B23="",SUM($B$5:$B$24)=0),"",B23/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D23" s="11">
-        <f>IF(OR(B23="",SUM($B$5:$B$24)=0),"",SUM($B$5:B23)/SUM($B$5:$B$24))</f>
-        <v/>
-      </c>
-      <c r="E23" s="10" t="n"/>
+      <c r="D23" s="17">
+        <f>IF(B23="","",RANK(B23,$B$5:$B$24,0)+COUNTIF($B$5:B23,B23)-1)</f>
+        <v/>
+      </c>
+      <c r="E23" s="16" t="n"/>
+      <c r="G23" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="H23" s="12">
+        <f>IFERROR(INDEX($A$5:$A$24,MATCH(G23,$D$5:$D$24,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I23" s="13">
+        <f>IFERROR(INDEX($B$5:$B$24,MATCH(G23,$D$5:$D$24,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J23" s="14">
+        <f>IF(I23="","",SUM($I$5:I23)/SUM($I$5:$I$24))</f>
+        <v/>
+      </c>
+      <c r="K23" s="15">
+        <f>IF(I23="","",0.8)</f>
+        <v/>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="10" t="n"/>
-      <c r="B24" s="10" t="n"/>
-      <c r="C24" s="11">
+      <c r="A24" s="16" t="n"/>
+      <c r="B24" s="16" t="n"/>
+      <c r="C24" s="14">
         <f>IF(OR(B24="",SUM($B$5:$B$24)=0),"",B24/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D24" s="11">
-        <f>IF(OR(B24="",SUM($B$5:$B$24)=0),"",SUM($B$5:B24)/SUM($B$5:$B$24))</f>
-        <v/>
-      </c>
-      <c r="E24" s="10" t="n"/>
+      <c r="D24" s="17">
+        <f>IF(B24="","",RANK(B24,$B$5:$B$24,0)+COUNTIF($B$5:B24,B24)-1)</f>
+        <v/>
+      </c>
+      <c r="E24" s="16" t="n"/>
+      <c r="G24" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="H24" s="12">
+        <f>IFERROR(INDEX($A$5:$A$24,MATCH(G24,$D$5:$D$24,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I24" s="13">
+        <f>IFERROR(INDEX($B$5:$B$24,MATCH(G24,$D$5:$D$24,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J24" s="14">
+        <f>IF(I24="","",SUM($I$5:I24)/SUM($I$5:$I$24))</f>
+        <v/>
+      </c>
+      <c r="K24" s="15">
+        <f>IF(I24="","",0.8)</f>
+        <v/>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="12" t="inlineStr">
+      <c r="A26" s="6" t="inlineStr">
         <is>
           <t>SUMMARY</t>
         </is>
       </c>
-      <c r="B26" s="13" t="n"/>
-      <c r="C26" s="13" t="n"/>
-      <c r="D26" s="13" t="n"/>
-      <c r="E26" s="13" t="n"/>
+      <c r="B26" s="7" t="n"/>
+      <c r="C26" s="7" t="n"/>
+      <c r="D26" s="7" t="n"/>
+      <c r="E26" s="7" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="14" t="inlineStr">
+      <c r="A27" s="18" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C27" s="15">
+      <c r="C27" s="12">
         <f>SUM(B5:B24)</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="14" t="inlineStr">
+      <c r="A28" s="18" t="inlineStr">
         <is>
           <t>Categories</t>
         </is>
       </c>
-      <c r="C28" s="15">
+      <c r="C28" s="12">
         <f>COUNTA(A5:A24)</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="14" t="inlineStr">
+      <c r="A29" s="18" t="inlineStr">
         <is>
           <t>Share explained by the top three</t>
         </is>
       </c>
-      <c r="C29" s="11">
-        <f>IFERROR(SUM(B5:B7)/SUM(B5:B24),"")</f>
+      <c r="C29" s="14">
+        <f>IFERROR(SUM(I5:I7)/SUM(I5:I24),"")</f>
         <v/>
       </c>
     </row>
@@ -1365,153 +1725,153 @@
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>Statistic</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr"/>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr"/>
+      <c r="D5" s="8" t="inlineStr">
         <is>
           <t>What it tells you</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="A6" s="18" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
-      <c r="B6" s="16">
+      <c r="B6" s="19">
         <f>COUNT($B$20:$B$1000)</f>
         <v/>
       </c>
-      <c r="D6" s="17" t="inlineStr">
+      <c r="D6" s="20" t="inlineStr">
         <is>
           <t>How many values you pasted.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="14" t="inlineStr">
+      <c r="A7" s="18" t="inlineStr">
         <is>
           <t>Mean</t>
         </is>
       </c>
-      <c r="B7" s="16">
+      <c r="B7" s="19">
         <f>IFERROR(AVERAGE($B$20:$B$1000),"")</f>
         <v/>
       </c>
-      <c r="D7" s="17" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>Dragged upward by the long tail. Rarely the number to quote.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="14" t="inlineStr">
+      <c r="A8" s="18" t="inlineStr">
         <is>
           <t>Median (p50)</t>
         </is>
       </c>
-      <c r="B8" s="16">
+      <c r="B8" s="19">
         <f>IFERROR(MEDIAN($B$20:$B$1000),"")</f>
         <v/>
       </c>
-      <c r="D8" s="17" t="inlineStr">
+      <c r="D8" s="20" t="inlineStr">
         <is>
           <t>The typical experience. Quote this.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="14" t="inlineStr">
+      <c r="A9" s="18" t="inlineStr">
         <is>
           <t>p90</t>
         </is>
       </c>
-      <c r="B9" s="16">
+      <c r="B9" s="19">
         <f>IFERROR(PERCENTILE($B$20:$B$1000,0.9),"")</f>
         <v/>
       </c>
-      <c r="D9" s="17" t="inlineStr">
+      <c r="D9" s="20" t="inlineStr">
         <is>
           <t>What your worst-served customers get. This is what generates complaints.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="14" t="inlineStr">
+      <c r="A10" s="18" t="inlineStr">
         <is>
           <t>Standard deviation</t>
         </is>
       </c>
-      <c r="B10" s="16">
+      <c r="B10" s="19">
         <f>IFERROR(STDEV($B$20:$B$1000),"")</f>
         <v/>
       </c>
-      <c r="D10" s="17" t="inlineStr">
+      <c r="D10" s="20" t="inlineStr">
         <is>
           <t>Assumes symmetry, so it describes skewed data poorly.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="14" t="inlineStr">
+      <c r="A11" s="18" t="inlineStr">
         <is>
           <t>Interquartile range</t>
         </is>
       </c>
-      <c r="B11" s="16">
+      <c r="B11" s="19">
         <f>IFERROR(QUARTILE($B$20:$B$1000,3)-QUARTILE($B$20:$B$1000,1),"")</f>
         <v/>
       </c>
-      <c r="D11" s="17" t="inlineStr">
+      <c r="D11" s="20" t="inlineStr">
         <is>
           <t>The middle half. A better spread measure for this data.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="14" t="inlineStr">
+      <c r="A12" s="18" t="inlineStr">
         <is>
           <t>Mean ÷ median</t>
         </is>
       </c>
-      <c r="B12" s="16">
+      <c r="B12" s="19">
         <f>IFERROR(AVERAGE($B$20:$B$1000)/MEDIAN($B$20:$B$1000),"")</f>
         <v/>
       </c>
-      <c r="D12" s="17" t="inlineStr">
+      <c r="D12" s="20" t="inlineStr">
         <is>
           <t>Above about 1.2 means meaningful right skew — use non-parametric tests and quote percentiles.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="inlineStr">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t>VERDICT</t>
         </is>
       </c>
-      <c r="B14" s="13" t="n"/>
-      <c r="C14" s="13" t="n"/>
-      <c r="D14" s="13" t="n"/>
+      <c r="B14" s="7" t="n"/>
+      <c r="C14" s="7" t="n"/>
+      <c r="D14" s="7" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="18">
+      <c r="A15" s="21">
         <f>IF(COUNT($B$20:$B$1000)=0,"Paste your data into column B below.",IF(AVERAGE($B$20:$B$1000)/MEDIAN($B$20:$B$1000)&gt;1.2,"RIGHT-SKEWED — quote the median and p90, and prefer non-parametric tests.","ROUGHLY SYMMETRIC — the mean and a parametric test are defensible."))</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="14" t="inlineStr">
+      <c r="A18" s="18" t="inlineStr">
         <is>
           <t>Your data</t>
         </is>
@@ -1525,124 +1885,124 @@
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="10" t="n"/>
+      <c r="B20" s="16" t="n"/>
     </row>
     <row r="21">
-      <c r="B21" s="10" t="n"/>
+      <c r="B21" s="16" t="n"/>
     </row>
     <row r="22">
-      <c r="B22" s="10" t="n"/>
+      <c r="B22" s="16" t="n"/>
     </row>
     <row r="23">
-      <c r="B23" s="10" t="n"/>
+      <c r="B23" s="16" t="n"/>
     </row>
     <row r="24">
-      <c r="B24" s="10" t="n"/>
+      <c r="B24" s="16" t="n"/>
     </row>
     <row r="25">
-      <c r="B25" s="10" t="n"/>
+      <c r="B25" s="16" t="n"/>
     </row>
     <row r="26">
-      <c r="B26" s="10" t="n"/>
+      <c r="B26" s="16" t="n"/>
     </row>
     <row r="27">
-      <c r="B27" s="10" t="n"/>
+      <c r="B27" s="16" t="n"/>
     </row>
     <row r="28">
-      <c r="B28" s="10" t="n"/>
+      <c r="B28" s="16" t="n"/>
     </row>
     <row r="29">
-      <c r="B29" s="10" t="n"/>
+      <c r="B29" s="16" t="n"/>
     </row>
     <row r="30">
-      <c r="B30" s="10" t="n"/>
+      <c r="B30" s="16" t="n"/>
     </row>
     <row r="31">
-      <c r="B31" s="10" t="n"/>
+      <c r="B31" s="16" t="n"/>
     </row>
     <row r="32">
-      <c r="B32" s="10" t="n"/>
+      <c r="B32" s="16" t="n"/>
     </row>
     <row r="33">
-      <c r="B33" s="10" t="n"/>
+      <c r="B33" s="16" t="n"/>
     </row>
     <row r="34">
-      <c r="B34" s="10" t="n"/>
+      <c r="B34" s="16" t="n"/>
     </row>
     <row r="35">
-      <c r="B35" s="10" t="n"/>
+      <c r="B35" s="16" t="n"/>
     </row>
     <row r="36">
-      <c r="B36" s="10" t="n"/>
+      <c r="B36" s="16" t="n"/>
     </row>
     <row r="37">
-      <c r="B37" s="10" t="n"/>
+      <c r="B37" s="16" t="n"/>
     </row>
     <row r="38">
-      <c r="B38" s="10" t="n"/>
+      <c r="B38" s="16" t="n"/>
     </row>
     <row r="39">
-      <c r="B39" s="10" t="n"/>
+      <c r="B39" s="16" t="n"/>
     </row>
     <row r="40">
-      <c r="B40" s="10" t="n"/>
+      <c r="B40" s="16" t="n"/>
     </row>
     <row r="41">
-      <c r="B41" s="10" t="n"/>
+      <c r="B41" s="16" t="n"/>
     </row>
     <row r="42">
-      <c r="B42" s="10" t="n"/>
+      <c r="B42" s="16" t="n"/>
     </row>
     <row r="43">
-      <c r="B43" s="10" t="n"/>
+      <c r="B43" s="16" t="n"/>
     </row>
     <row r="44">
-      <c r="B44" s="10" t="n"/>
+      <c r="B44" s="16" t="n"/>
     </row>
     <row r="45">
-      <c r="B45" s="10" t="n"/>
+      <c r="B45" s="16" t="n"/>
     </row>
     <row r="46">
-      <c r="B46" s="10" t="n"/>
+      <c r="B46" s="16" t="n"/>
     </row>
     <row r="47">
-      <c r="B47" s="10" t="n"/>
+      <c r="B47" s="16" t="n"/>
     </row>
     <row r="48">
-      <c r="B48" s="10" t="n"/>
+      <c r="B48" s="16" t="n"/>
     </row>
     <row r="49">
-      <c r="B49" s="10" t="n"/>
+      <c r="B49" s="16" t="n"/>
     </row>
     <row r="50">
-      <c r="B50" s="10" t="n"/>
+      <c r="B50" s="16" t="n"/>
     </row>
     <row r="51">
-      <c r="B51" s="10" t="n"/>
+      <c r="B51" s="16" t="n"/>
     </row>
     <row r="52">
-      <c r="B52" s="10" t="n"/>
+      <c r="B52" s="16" t="n"/>
     </row>
     <row r="53">
-      <c r="B53" s="10" t="n"/>
+      <c r="B53" s="16" t="n"/>
     </row>
     <row r="54">
-      <c r="B54" s="10" t="n"/>
+      <c r="B54" s="16" t="n"/>
     </row>
     <row r="55">
-      <c r="B55" s="10" t="n"/>
+      <c r="B55" s="16" t="n"/>
     </row>
     <row r="56">
-      <c r="B56" s="10" t="n"/>
+      <c r="B56" s="16" t="n"/>
     </row>
     <row r="57">
-      <c r="B57" s="10" t="n"/>
+      <c r="B57" s="16" t="n"/>
     </row>
     <row r="58">
-      <c r="B58" s="10" t="n"/>
+      <c r="B58" s="16" t="n"/>
     </row>
     <row r="59">
-      <c r="B59" s="10" t="n"/>
+      <c r="B59" s="16" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="4">

--- a/templates/25-pareto-and-distribution.xlsx
+++ b/templates/25-pareto-and-distribution.xlsx
@@ -909,12 +909,31 @@
       <c r="K3" s="7" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="8" t="inlineStr"/>
-      <c r="B4" s="8" t="inlineStr"/>
-      <c r="C4" s="8" t="inlineStr"/>
-      <c r="D4" s="8" t="inlineStr"/>
-      <c r="E4" s="8" t="inlineStr"/>
-      <c r="F4" s="8" t="inlineStr"/>
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Share</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>Rank</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>Validated by reading tickets?</t>
+        </is>
+      </c>
       <c r="G4" s="8" t="inlineStr">
         <is>
           <t>#</t>

--- a/templates/25-pareto-and-distribution.xlsx
+++ b/templates/25-pareto-and-distribution.xlsx
@@ -111,7 +111,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -142,6 +142,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -415,6 +416,125 @@
 </chartSpace>
 </file>
 
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <roundedCorners val="0"/>
+  <style val="10"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Mean, median and p90 — quoting the mean hides the tail</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <v>Seconds</v>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <invertIfNegative val="0"/>
+          <dPt>
+            <idx val="0"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="9AA4B2"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="1"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="1F4E79"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="2"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="C0392B"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <cat>
+            <numRef>
+              <f>'Shape and spread'!$F$19:$F$21</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Shape and spread'!$G$19:$G$21</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="60"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="low"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+        <tickLblSkip val="1"/>
+        <tickMarkSkip val="1"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
@@ -425,6 +545,33 @@
       <rowOff>0</rowOff>
     </from>
     <ext cx="6840000" cy="3240000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>22</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="2700000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -1709,13 +1856,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D59"/>
+  <dimension ref="A1:G59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -1895,6 +2044,11 @@
           <t>Your data</t>
         </is>
       </c>
+      <c r="F18" s="18" t="inlineStr">
+        <is>
+          <t>What you would quote</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="B19" s="5" t="inlineStr">
@@ -1902,126 +2056,233 @@
           <t>Values ↓</t>
         </is>
       </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>Mean</t>
+        </is>
+      </c>
+      <c r="G19" s="13">
+        <f>IFERROR(AVERAGE($B$20:$B$1000),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="20">
-      <c r="B20" s="16" t="n"/>
+      <c r="B20" s="22" t="n">
+        <v>182</v>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>Median (p50)</t>
+        </is>
+      </c>
+      <c r="G20" s="13">
+        <f>IFERROR(MEDIAN($B$20:$B$1000),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="21">
-      <c r="B21" s="16" t="n"/>
+      <c r="B21" s="22" t="n">
+        <v>201</v>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>p90</t>
+        </is>
+      </c>
+      <c r="G21" s="13">
+        <f>IFERROR(PERCENTILE($B$20:$B$1000,0.9),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="22">
-      <c r="B22" s="16" t="n"/>
+      <c r="B22" s="22" t="n">
+        <v>214</v>
+      </c>
     </row>
     <row r="23">
-      <c r="B23" s="16" t="n"/>
+      <c r="B23" s="22" t="n">
+        <v>227</v>
+      </c>
     </row>
     <row r="24">
-      <c r="B24" s="16" t="n"/>
+      <c r="B24" s="22" t="n">
+        <v>236</v>
+      </c>
     </row>
     <row r="25">
-      <c r="B25" s="16" t="n"/>
+      <c r="B25" s="22" t="n">
+        <v>241</v>
+      </c>
     </row>
     <row r="26">
-      <c r="B26" s="16" t="n"/>
+      <c r="B26" s="22" t="n">
+        <v>248</v>
+      </c>
     </row>
     <row r="27">
-      <c r="B27" s="16" t="n"/>
+      <c r="B27" s="22" t="n">
+        <v>255</v>
+      </c>
     </row>
     <row r="28">
-      <c r="B28" s="16" t="n"/>
+      <c r="B28" s="22" t="n">
+        <v>259</v>
+      </c>
     </row>
     <row r="29">
-      <c r="B29" s="16" t="n"/>
+      <c r="B29" s="22" t="n">
+        <v>263</v>
+      </c>
     </row>
     <row r="30">
-      <c r="B30" s="16" t="n"/>
+      <c r="B30" s="22" t="n">
+        <v>268</v>
+      </c>
     </row>
     <row r="31">
-      <c r="B31" s="16" t="n"/>
+      <c r="B31" s="22" t="n">
+        <v>272</v>
+      </c>
     </row>
     <row r="32">
-      <c r="B32" s="16" t="n"/>
+      <c r="B32" s="22" t="n">
+        <v>277</v>
+      </c>
     </row>
     <row r="33">
-      <c r="B33" s="16" t="n"/>
+      <c r="B33" s="22" t="n">
+        <v>281</v>
+      </c>
     </row>
     <row r="34">
-      <c r="B34" s="16" t="n"/>
+      <c r="B34" s="22" t="n">
+        <v>286</v>
+      </c>
     </row>
     <row r="35">
-      <c r="B35" s="16" t="n"/>
+      <c r="B35" s="22" t="n">
+        <v>292</v>
+      </c>
     </row>
     <row r="36">
-      <c r="B36" s="16" t="n"/>
+      <c r="B36" s="22" t="n">
+        <v>298</v>
+      </c>
     </row>
     <row r="37">
-      <c r="B37" s="16" t="n"/>
+      <c r="B37" s="22" t="n">
+        <v>305</v>
+      </c>
     </row>
     <row r="38">
-      <c r="B38" s="16" t="n"/>
+      <c r="B38" s="22" t="n">
+        <v>311</v>
+      </c>
     </row>
     <row r="39">
-      <c r="B39" s="16" t="n"/>
+      <c r="B39" s="22" t="n">
+        <v>318</v>
+      </c>
     </row>
     <row r="40">
-      <c r="B40" s="16" t="n"/>
+      <c r="B40" s="22" t="n">
+        <v>326</v>
+      </c>
     </row>
     <row r="41">
-      <c r="B41" s="16" t="n"/>
+      <c r="B41" s="22" t="n">
+        <v>335</v>
+      </c>
     </row>
     <row r="42">
-      <c r="B42" s="16" t="n"/>
+      <c r="B42" s="22" t="n">
+        <v>346</v>
+      </c>
     </row>
     <row r="43">
-      <c r="B43" s="16" t="n"/>
+      <c r="B43" s="22" t="n">
+        <v>358</v>
+      </c>
     </row>
     <row r="44">
-      <c r="B44" s="16" t="n"/>
+      <c r="B44" s="22" t="n">
+        <v>372</v>
+      </c>
     </row>
     <row r="45">
-      <c r="B45" s="16" t="n"/>
+      <c r="B45" s="22" t="n">
+        <v>389</v>
+      </c>
     </row>
     <row r="46">
-      <c r="B46" s="16" t="n"/>
+      <c r="B46" s="22" t="n">
+        <v>408</v>
+      </c>
     </row>
     <row r="47">
-      <c r="B47" s="16" t="n"/>
+      <c r="B47" s="22" t="n">
+        <v>431</v>
+      </c>
     </row>
     <row r="48">
-      <c r="B48" s="16" t="n"/>
+      <c r="B48" s="22" t="n">
+        <v>459</v>
+      </c>
     </row>
     <row r="49">
-      <c r="B49" s="16" t="n"/>
+      <c r="B49" s="22" t="n">
+        <v>494</v>
+      </c>
     </row>
     <row r="50">
-      <c r="B50" s="16" t="n"/>
+      <c r="B50" s="22" t="n">
+        <v>538</v>
+      </c>
     </row>
     <row r="51">
-      <c r="B51" s="16" t="n"/>
+      <c r="B51" s="22" t="n">
+        <v>594</v>
+      </c>
     </row>
     <row r="52">
-      <c r="B52" s="16" t="n"/>
+      <c r="B52" s="22" t="n">
+        <v>668</v>
+      </c>
     </row>
     <row r="53">
-      <c r="B53" s="16" t="n"/>
+      <c r="B53" s="22" t="n">
+        <v>771</v>
+      </c>
     </row>
     <row r="54">
-      <c r="B54" s="16" t="n"/>
+      <c r="B54" s="22" t="n">
+        <v>918</v>
+      </c>
     </row>
     <row r="55">
-      <c r="B55" s="16" t="n"/>
+      <c r="B55" s="22" t="n">
+        <v>1140</v>
+      </c>
     </row>
     <row r="56">
-      <c r="B56" s="16" t="n"/>
+      <c r="B56" s="22" t="n">
+        <v>1502</v>
+      </c>
     </row>
     <row r="57">
-      <c r="B57" s="16" t="n"/>
+      <c r="B57" s="22" t="n">
+        <v>2160</v>
+      </c>
     </row>
     <row r="58">
-      <c r="B58" s="16" t="n"/>
+      <c r="B58" s="22" t="n">
+        <v>3480</v>
+      </c>
     </row>
     <row r="59">
-      <c r="B59" s="16" t="n"/>
+      <c r="B59" s="22" t="n">
+        <v>5220</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -2033,5 +2294,6 @@
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
--- a/templates/25-pareto-and-distribution.xlsx
+++ b/templates/25-pareto-and-distribution.xlsx
@@ -539,12 +539,12 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>6</col>
+      <col>13</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6840000" cy="3240000"/>
+    <ext cx="9360000" cy="3960000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -1137,11 +1137,11 @@
         <v/>
       </c>
       <c r="J5" s="14">
-        <f>IF(I5="","",SUM($I$5:I5)/SUM($I$5:$I$24))</f>
+        <f>IF(I5="",NA(),SUM($I$5:I5)/SUM($I$5:$I$24))</f>
         <v/>
       </c>
       <c r="K5" s="15">
-        <f>IF(I5="","",0.8)</f>
+        <f>IF(I5="",NA(),0.8)</f>
         <v/>
       </c>
     </row>
@@ -1175,11 +1175,11 @@
         <v/>
       </c>
       <c r="J6" s="14">
-        <f>IF(I6="","",SUM($I$5:I6)/SUM($I$5:$I$24))</f>
+        <f>IF(I6="",NA(),SUM($I$5:I6)/SUM($I$5:$I$24))</f>
         <v/>
       </c>
       <c r="K6" s="15">
-        <f>IF(I6="","",0.8)</f>
+        <f>IF(I6="",NA(),0.8)</f>
         <v/>
       </c>
     </row>
@@ -1213,11 +1213,11 @@
         <v/>
       </c>
       <c r="J7" s="14">
-        <f>IF(I7="","",SUM($I$5:I7)/SUM($I$5:$I$24))</f>
+        <f>IF(I7="",NA(),SUM($I$5:I7)/SUM($I$5:$I$24))</f>
         <v/>
       </c>
       <c r="K7" s="15">
-        <f>IF(I7="","",0.8)</f>
+        <f>IF(I7="",NA(),0.8)</f>
         <v/>
       </c>
     </row>
@@ -1251,11 +1251,11 @@
         <v/>
       </c>
       <c r="J8" s="14">
-        <f>IF(I8="","",SUM($I$5:I8)/SUM($I$5:$I$24))</f>
+        <f>IF(I8="",NA(),SUM($I$5:I8)/SUM($I$5:$I$24))</f>
         <v/>
       </c>
       <c r="K8" s="15">
-        <f>IF(I8="","",0.8)</f>
+        <f>IF(I8="",NA(),0.8)</f>
         <v/>
       </c>
     </row>
@@ -1289,11 +1289,11 @@
         <v/>
       </c>
       <c r="J9" s="14">
-        <f>IF(I9="","",SUM($I$5:I9)/SUM($I$5:$I$24))</f>
+        <f>IF(I9="",NA(),SUM($I$5:I9)/SUM($I$5:$I$24))</f>
         <v/>
       </c>
       <c r="K9" s="15">
-        <f>IF(I9="","",0.8)</f>
+        <f>IF(I9="",NA(),0.8)</f>
         <v/>
       </c>
     </row>
@@ -1321,11 +1321,11 @@
         <v/>
       </c>
       <c r="J10" s="14">
-        <f>IF(I10="","",SUM($I$5:I10)/SUM($I$5:$I$24))</f>
+        <f>IF(I10="",NA(),SUM($I$5:I10)/SUM($I$5:$I$24))</f>
         <v/>
       </c>
       <c r="K10" s="15">
-        <f>IF(I10="","",0.8)</f>
+        <f>IF(I10="",NA(),0.8)</f>
         <v/>
       </c>
     </row>
@@ -1353,11 +1353,11 @@
         <v/>
       </c>
       <c r="J11" s="14">
-        <f>IF(I11="","",SUM($I$5:I11)/SUM($I$5:$I$24))</f>
+        <f>IF(I11="",NA(),SUM($I$5:I11)/SUM($I$5:$I$24))</f>
         <v/>
       </c>
       <c r="K11" s="15">
-        <f>IF(I11="","",0.8)</f>
+        <f>IF(I11="",NA(),0.8)</f>
         <v/>
       </c>
     </row>
@@ -1385,11 +1385,11 @@
         <v/>
       </c>
       <c r="J12" s="14">
-        <f>IF(I12="","",SUM($I$5:I12)/SUM($I$5:$I$24))</f>
+        <f>IF(I12="",NA(),SUM($I$5:I12)/SUM($I$5:$I$24))</f>
         <v/>
       </c>
       <c r="K12" s="15">
-        <f>IF(I12="","",0.8)</f>
+        <f>IF(I12="",NA(),0.8)</f>
         <v/>
       </c>
     </row>
@@ -1417,11 +1417,11 @@
         <v/>
       </c>
       <c r="J13" s="14">
-        <f>IF(I13="","",SUM($I$5:I13)/SUM($I$5:$I$24))</f>
+        <f>IF(I13="",NA(),SUM($I$5:I13)/SUM($I$5:$I$24))</f>
         <v/>
       </c>
       <c r="K13" s="15">
-        <f>IF(I13="","",0.8)</f>
+        <f>IF(I13="",NA(),0.8)</f>
         <v/>
       </c>
     </row>
@@ -1449,11 +1449,11 @@
         <v/>
       </c>
       <c r="J14" s="14">
-        <f>IF(I14="","",SUM($I$5:I14)/SUM($I$5:$I$24))</f>
+        <f>IF(I14="",NA(),SUM($I$5:I14)/SUM($I$5:$I$24))</f>
         <v/>
       </c>
       <c r="K14" s="15">
-        <f>IF(I14="","",0.8)</f>
+        <f>IF(I14="",NA(),0.8)</f>
         <v/>
       </c>
     </row>
@@ -1481,11 +1481,11 @@
         <v/>
       </c>
       <c r="J15" s="14">
-        <f>IF(I15="","",SUM($I$5:I15)/SUM($I$5:$I$24))</f>
+        <f>IF(I15="",NA(),SUM($I$5:I15)/SUM($I$5:$I$24))</f>
         <v/>
       </c>
       <c r="K15" s="15">
-        <f>IF(I15="","",0.8)</f>
+        <f>IF(I15="",NA(),0.8)</f>
         <v/>
       </c>
     </row>
@@ -1513,11 +1513,11 @@
         <v/>
       </c>
       <c r="J16" s="14">
-        <f>IF(I16="","",SUM($I$5:I16)/SUM($I$5:$I$24))</f>
+        <f>IF(I16="",NA(),SUM($I$5:I16)/SUM($I$5:$I$24))</f>
         <v/>
       </c>
       <c r="K16" s="15">
-        <f>IF(I16="","",0.8)</f>
+        <f>IF(I16="",NA(),0.8)</f>
         <v/>
       </c>
     </row>
@@ -1545,11 +1545,11 @@
         <v/>
       </c>
       <c r="J17" s="14">
-        <f>IF(I17="","",SUM($I$5:I17)/SUM($I$5:$I$24))</f>
+        <f>IF(I17="",NA(),SUM($I$5:I17)/SUM($I$5:$I$24))</f>
         <v/>
       </c>
       <c r="K17" s="15">
-        <f>IF(I17="","",0.8)</f>
+        <f>IF(I17="",NA(),0.8)</f>
         <v/>
       </c>
     </row>
@@ -1577,11 +1577,11 @@
         <v/>
       </c>
       <c r="J18" s="14">
-        <f>IF(I18="","",SUM($I$5:I18)/SUM($I$5:$I$24))</f>
+        <f>IF(I18="",NA(),SUM($I$5:I18)/SUM($I$5:$I$24))</f>
         <v/>
       </c>
       <c r="K18" s="15">
-        <f>IF(I18="","",0.8)</f>
+        <f>IF(I18="",NA(),0.8)</f>
         <v/>
       </c>
     </row>
@@ -1609,11 +1609,11 @@
         <v/>
       </c>
       <c r="J19" s="14">
-        <f>IF(I19="","",SUM($I$5:I19)/SUM($I$5:$I$24))</f>
+        <f>IF(I19="",NA(),SUM($I$5:I19)/SUM($I$5:$I$24))</f>
         <v/>
       </c>
       <c r="K19" s="15">
-        <f>IF(I19="","",0.8)</f>
+        <f>IF(I19="",NA(),0.8)</f>
         <v/>
       </c>
     </row>
@@ -1641,11 +1641,11 @@
         <v/>
       </c>
       <c r="J20" s="14">
-        <f>IF(I20="","",SUM($I$5:I20)/SUM($I$5:$I$24))</f>
+        <f>IF(I20="",NA(),SUM($I$5:I20)/SUM($I$5:$I$24))</f>
         <v/>
       </c>
       <c r="K20" s="15">
-        <f>IF(I20="","",0.8)</f>
+        <f>IF(I20="",NA(),0.8)</f>
         <v/>
       </c>
     </row>
@@ -1673,11 +1673,11 @@
         <v/>
       </c>
       <c r="J21" s="14">
-        <f>IF(I21="","",SUM($I$5:I21)/SUM($I$5:$I$24))</f>
+        <f>IF(I21="",NA(),SUM($I$5:I21)/SUM($I$5:$I$24))</f>
         <v/>
       </c>
       <c r="K21" s="15">
-        <f>IF(I21="","",0.8)</f>
+        <f>IF(I21="",NA(),0.8)</f>
         <v/>
       </c>
     </row>
@@ -1705,11 +1705,11 @@
         <v/>
       </c>
       <c r="J22" s="14">
-        <f>IF(I22="","",SUM($I$5:I22)/SUM($I$5:$I$24))</f>
+        <f>IF(I22="",NA(),SUM($I$5:I22)/SUM($I$5:$I$24))</f>
         <v/>
       </c>
       <c r="K22" s="15">
-        <f>IF(I22="","",0.8)</f>
+        <f>IF(I22="",NA(),0.8)</f>
         <v/>
       </c>
     </row>
@@ -1737,11 +1737,11 @@
         <v/>
       </c>
       <c r="J23" s="14">
-        <f>IF(I23="","",SUM($I$5:I23)/SUM($I$5:$I$24))</f>
+        <f>IF(I23="",NA(),SUM($I$5:I23)/SUM($I$5:$I$24))</f>
         <v/>
       </c>
       <c r="K23" s="15">
-        <f>IF(I23="","",0.8)</f>
+        <f>IF(I23="",NA(),0.8)</f>
         <v/>
       </c>
     </row>
@@ -1769,11 +1769,11 @@
         <v/>
       </c>
       <c r="J24" s="14">
-        <f>IF(I24="","",SUM($I$5:I24)/SUM($I$5:$I$24))</f>
+        <f>IF(I24="",NA(),SUM($I$5:I24)/SUM($I$5:$I$24))</f>
         <v/>
       </c>
       <c r="K24" s="15">
-        <f>IF(I24="","",0.8)</f>
+        <f>IF(I24="",NA(),0.8)</f>
         <v/>
       </c>
     </row>

--- a/templates/25-pareto-and-distribution.xlsx
+++ b/templates/25-pareto-and-distribution.xlsx
@@ -539,7 +539,7 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>13</col>
+      <col>12</col>
       <colOff>0</colOff>
       <row>2</row>
       <rowOff>0</rowOff>
@@ -566,9 +566,9 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>5</col>
+      <col>8</col>
       <colOff>0</colOff>
-      <row>22</row>
+      <row>2</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5400000" cy="2700000"/>
@@ -1777,6 +1777,7 @@
         <v/>
       </c>
     </row>
+    <row r="25"/>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
@@ -1821,6 +1822,7 @@
         <v/>
       </c>
     </row>
+    <row r="30"/>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
@@ -2022,6 +2024,7 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
@@ -2038,6 +2041,8 @@
         <v/>
       </c>
     </row>
+    <row r="16"/>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="18" t="inlineStr">
         <is>

--- a/templates/25-pareto-and-distribution.xlsx
+++ b/templates/25-pareto-and-distribution.xlsx
@@ -111,7 +111,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -136,6 +136,9 @@
     <xf numFmtId="9" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1124,7 +1127,11 @@
         <f>IF(B5="","",RANK(B5,$B$5:$B$24,0)+COUNTIF($B$5:B5,B5)-1)</f>
         <v/>
       </c>
-      <c r="E5" s="9" t="n"/>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="G5" s="5" t="n">
         <v>1</v>
       </c>
@@ -1777,7 +1784,13 @@
         <v/>
       </c>
     </row>
-    <row r="25"/>
+    <row r="25" ht="90" customHeight="1">
+      <c r="A25" s="18" t="inlineStr">
+        <is>
+          <t>How to answer the last column, and why it is the one that matters. Open 50 tickets at random from your top category and read them. Count how many are genuinely that category rather than the code an agent picked under time pressure. Answer Yes only if 40 or more of the 50 hold up; below that your Pareto is ranking your data-entry habits and not your problems, and the business case built on it will not survive contact with the process. Row 5 is the worked example: 50 read, 41 held up, so Yes.</t>
+        </is>
+      </c>
+    </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
@@ -1790,7 +1803,7 @@
       <c r="E26" s="7" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="18" t="inlineStr">
+      <c r="A27" s="19" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
@@ -1801,7 +1814,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="18" t="inlineStr">
+      <c r="A28" s="19" t="inlineStr">
         <is>
           <t>Categories</t>
         </is>
@@ -1812,7 +1825,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="18" t="inlineStr">
+      <c r="A29" s="19" t="inlineStr">
         <is>
           <t>Share explained by the top three</t>
         </is>
@@ -1831,10 +1844,11 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
     <mergeCell ref="A26:E26"/>
     <mergeCell ref="A29:B29"/>
     <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A25:E25"/>
     <mergeCell ref="A28:B28"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A31:E31"/>
@@ -1913,112 +1927,112 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="inlineStr">
+      <c r="A6" s="19" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
-      <c r="B6" s="19">
+      <c r="B6" s="20">
         <f>COUNT($B$20:$B$1000)</f>
         <v/>
       </c>
-      <c r="D6" s="20" t="inlineStr">
+      <c r="D6" s="21" t="inlineStr">
         <is>
           <t>How many values you pasted.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="inlineStr">
+      <c r="A7" s="19" t="inlineStr">
         <is>
           <t>Mean</t>
         </is>
       </c>
-      <c r="B7" s="19">
+      <c r="B7" s="20">
         <f>IFERROR(AVERAGE($B$20:$B$1000),"")</f>
         <v/>
       </c>
-      <c r="D7" s="20" t="inlineStr">
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t>Dragged upward by the long tail. Rarely the number to quote.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="inlineStr">
+      <c r="A8" s="19" t="inlineStr">
         <is>
           <t>Median (p50)</t>
         </is>
       </c>
-      <c r="B8" s="19">
+      <c r="B8" s="20">
         <f>IFERROR(MEDIAN($B$20:$B$1000),"")</f>
         <v/>
       </c>
-      <c r="D8" s="20" t="inlineStr">
+      <c r="D8" s="21" t="inlineStr">
         <is>
           <t>The typical experience. Quote this.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="inlineStr">
+      <c r="A9" s="19" t="inlineStr">
         <is>
           <t>p90</t>
         </is>
       </c>
-      <c r="B9" s="19">
+      <c r="B9" s="20">
         <f>IFERROR(PERCENTILE($B$20:$B$1000,0.9),"")</f>
         <v/>
       </c>
-      <c r="D9" s="20" t="inlineStr">
+      <c r="D9" s="21" t="inlineStr">
         <is>
           <t>What your worst-served customers get. This is what generates complaints.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="inlineStr">
+      <c r="A10" s="19" t="inlineStr">
         <is>
           <t>Standard deviation</t>
         </is>
       </c>
-      <c r="B10" s="19">
+      <c r="B10" s="20">
         <f>IFERROR(STDEV($B$20:$B$1000),"")</f>
         <v/>
       </c>
-      <c r="D10" s="20" t="inlineStr">
+      <c r="D10" s="21" t="inlineStr">
         <is>
           <t>Assumes symmetry, so it describes skewed data poorly.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="inlineStr">
+      <c r="A11" s="19" t="inlineStr">
         <is>
           <t>Interquartile range</t>
         </is>
       </c>
-      <c r="B11" s="19">
+      <c r="B11" s="20">
         <f>IFERROR(QUARTILE($B$20:$B$1000,3)-QUARTILE($B$20:$B$1000,1),"")</f>
         <v/>
       </c>
-      <c r="D11" s="20" t="inlineStr">
+      <c r="D11" s="21" t="inlineStr">
         <is>
           <t>The middle half. A better spread measure for this data.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="inlineStr">
+      <c r="A12" s="19" t="inlineStr">
         <is>
           <t>Mean ÷ median</t>
         </is>
       </c>
-      <c r="B12" s="19">
+      <c r="B12" s="20">
         <f>IFERROR(AVERAGE($B$20:$B$1000)/MEDIAN($B$20:$B$1000),"")</f>
         <v/>
       </c>
-      <c r="D12" s="20" t="inlineStr">
+      <c r="D12" s="21" t="inlineStr">
         <is>
           <t>Above about 1.2 means meaningful right skew — use non-parametric tests and quote percentiles.</t>
         </is>
@@ -2036,7 +2050,7 @@
       <c r="D14" s="7" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="21">
+      <c r="A15" s="22">
         <f>IF(COUNT($B$20:$B$1000)=0,"Paste your data into column B below.",IF(AVERAGE($B$20:$B$1000)/MEDIAN($B$20:$B$1000)&gt;1.2,"RIGHT-SKEWED — quote the median and p90, and prefer non-parametric tests.","ROUGHLY SYMMETRIC — the mean and a parametric test are defensible."))</f>
         <v/>
       </c>
@@ -2044,12 +2058,12 @@
     <row r="16"/>
     <row r="17"/>
     <row r="18">
-      <c r="A18" s="18" t="inlineStr">
+      <c r="A18" s="19" t="inlineStr">
         <is>
           <t>Your data</t>
         </is>
       </c>
-      <c r="F18" s="18" t="inlineStr">
+      <c r="F18" s="19" t="inlineStr">
         <is>
           <t>What you would quote</t>
         </is>
@@ -2072,7 +2086,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="22" t="n">
+      <c r="B20" s="23" t="n">
         <v>182</v>
       </c>
       <c r="F20" s="5" t="inlineStr">
@@ -2086,7 +2100,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="22" t="n">
+      <c r="B21" s="23" t="n">
         <v>201</v>
       </c>
       <c r="F21" s="5" t="inlineStr">
@@ -2100,192 +2114,192 @@
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="22" t="n">
+      <c r="B22" s="23" t="n">
         <v>214</v>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="22" t="n">
+      <c r="B23" s="23" t="n">
         <v>227</v>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="22" t="n">
+      <c r="B24" s="23" t="n">
         <v>236</v>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="22" t="n">
+      <c r="B25" s="23" t="n">
         <v>241</v>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="22" t="n">
+      <c r="B26" s="23" t="n">
         <v>248</v>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="22" t="n">
+      <c r="B27" s="23" t="n">
         <v>255</v>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="22" t="n">
+      <c r="B28" s="23" t="n">
         <v>259</v>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="22" t="n">
+      <c r="B29" s="23" t="n">
         <v>263</v>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="22" t="n">
+      <c r="B30" s="23" t="n">
         <v>268</v>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="22" t="n">
+      <c r="B31" s="23" t="n">
         <v>272</v>
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="22" t="n">
+      <c r="B32" s="23" t="n">
         <v>277</v>
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="22" t="n">
+      <c r="B33" s="23" t="n">
         <v>281</v>
       </c>
     </row>
     <row r="34">
-      <c r="B34" s="22" t="n">
+      <c r="B34" s="23" t="n">
         <v>286</v>
       </c>
     </row>
     <row r="35">
-      <c r="B35" s="22" t="n">
+      <c r="B35" s="23" t="n">
         <v>292</v>
       </c>
     </row>
     <row r="36">
-      <c r="B36" s="22" t="n">
+      <c r="B36" s="23" t="n">
         <v>298</v>
       </c>
     </row>
     <row r="37">
-      <c r="B37" s="22" t="n">
+      <c r="B37" s="23" t="n">
         <v>305</v>
       </c>
     </row>
     <row r="38">
-      <c r="B38" s="22" t="n">
+      <c r="B38" s="23" t="n">
         <v>311</v>
       </c>
     </row>
     <row r="39">
-      <c r="B39" s="22" t="n">
+      <c r="B39" s="23" t="n">
         <v>318</v>
       </c>
     </row>
     <row r="40">
-      <c r="B40" s="22" t="n">
+      <c r="B40" s="23" t="n">
         <v>326</v>
       </c>
     </row>
     <row r="41">
-      <c r="B41" s="22" t="n">
+      <c r="B41" s="23" t="n">
         <v>335</v>
       </c>
     </row>
     <row r="42">
-      <c r="B42" s="22" t="n">
+      <c r="B42" s="23" t="n">
         <v>346</v>
       </c>
     </row>
     <row r="43">
-      <c r="B43" s="22" t="n">
+      <c r="B43" s="23" t="n">
         <v>358</v>
       </c>
     </row>
     <row r="44">
-      <c r="B44" s="22" t="n">
+      <c r="B44" s="23" t="n">
         <v>372</v>
       </c>
     </row>
     <row r="45">
-      <c r="B45" s="22" t="n">
+      <c r="B45" s="23" t="n">
         <v>389</v>
       </c>
     </row>
     <row r="46">
-      <c r="B46" s="22" t="n">
+      <c r="B46" s="23" t="n">
         <v>408</v>
       </c>
     </row>
     <row r="47">
-      <c r="B47" s="22" t="n">
+      <c r="B47" s="23" t="n">
         <v>431</v>
       </c>
     </row>
     <row r="48">
-      <c r="B48" s="22" t="n">
+      <c r="B48" s="23" t="n">
         <v>459</v>
       </c>
     </row>
     <row r="49">
-      <c r="B49" s="22" t="n">
+      <c r="B49" s="23" t="n">
         <v>494</v>
       </c>
     </row>
     <row r="50">
-      <c r="B50" s="22" t="n">
+      <c r="B50" s="23" t="n">
         <v>538</v>
       </c>
     </row>
     <row r="51">
-      <c r="B51" s="22" t="n">
+      <c r="B51" s="23" t="n">
         <v>594</v>
       </c>
     </row>
     <row r="52">
-      <c r="B52" s="22" t="n">
+      <c r="B52" s="23" t="n">
         <v>668</v>
       </c>
     </row>
     <row r="53">
-      <c r="B53" s="22" t="n">
+      <c r="B53" s="23" t="n">
         <v>771</v>
       </c>
     </row>
     <row r="54">
-      <c r="B54" s="22" t="n">
+      <c r="B54" s="23" t="n">
         <v>918</v>
       </c>
     </row>
     <row r="55">
-      <c r="B55" s="22" t="n">
+      <c r="B55" s="23" t="n">
         <v>1140</v>
       </c>
     </row>
     <row r="56">
-      <c r="B56" s="22" t="n">
+      <c r="B56" s="23" t="n">
         <v>1502</v>
       </c>
     </row>
     <row r="57">
-      <c r="B57" s="22" t="n">
+      <c r="B57" s="23" t="n">
         <v>2160</v>
       </c>
     </row>
     <row r="58">
-      <c r="B58" s="22" t="n">
+      <c r="B58" s="23" t="n">
         <v>3480</v>
       </c>
     </row>
     <row r="59">
-      <c r="B59" s="22" t="n">
+      <c r="B59" s="23" t="n">
         <v>5220</v>
       </c>
     </row>

--- a/templates/25-pareto-and-distribution.xlsx
+++ b/templates/25-pareto-and-distribution.xlsx
@@ -134,8 +134,8 @@
     <xf numFmtId="3" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1153,23 +1153,23 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="16" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>Wrong plan applied</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n">
+      <c r="B6" s="9" t="n">
         <v>233</v>
       </c>
       <c r="C6" s="14">
         <f>IF(OR(B6="",SUM($B$5:$B$24)=0),"",B6/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D6" s="17">
+      <c r="D6" s="16">
         <f>IF(B6="","",RANK(B6,$B$5:$B$24,0)+COUNTIF($B$5:B6,B6)-1)</f>
         <v/>
       </c>
-      <c r="E6" s="16" t="n"/>
+      <c r="E6" s="17" t="n"/>
       <c r="G6" s="5" t="n">
         <v>2</v>
       </c>
@@ -1191,23 +1191,23 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="16" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>Duplicate charge</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n">
+      <c r="B7" s="9" t="n">
         <v>151</v>
       </c>
       <c r="C7" s="14">
         <f>IF(OR(B7="",SUM($B$5:$B$24)=0),"",B7/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D7" s="17">
+      <c r="D7" s="16">
         <f>IF(B7="","",RANK(B7,$B$5:$B$24,0)+COUNTIF($B$5:B7,B7)-1)</f>
         <v/>
       </c>
-      <c r="E7" s="16" t="n"/>
+      <c r="E7" s="17" t="n"/>
       <c r="G7" s="5" t="n">
         <v>3</v>
       </c>
@@ -1229,23 +1229,23 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="16" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>Proration misunderstood</t>
         </is>
       </c>
-      <c r="B8" s="16" t="n">
+      <c r="B8" s="9" t="n">
         <v>96</v>
       </c>
       <c r="C8" s="14">
         <f>IF(OR(B8="",SUM($B$5:$B$24)=0),"",B8/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D8" s="17">
+      <c r="D8" s="16">
         <f>IF(B8="","",RANK(B8,$B$5:$B$24,0)+COUNTIF($B$5:B8,B8)-1)</f>
         <v/>
       </c>
-      <c r="E8" s="16" t="n"/>
+      <c r="E8" s="17" t="n"/>
       <c r="G8" s="5" t="n">
         <v>4</v>
       </c>
@@ -1267,23 +1267,23 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="16" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>Refund timing</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n">
+      <c r="B9" s="9" t="n">
         <v>74</v>
       </c>
       <c r="C9" s="14">
         <f>IF(OR(B9="",SUM($B$5:$B$24)=0),"",B9/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D9" s="17">
+      <c r="D9" s="16">
         <f>IF(B9="","",RANK(B9,$B$5:$B$24,0)+COUNTIF($B$5:B9,B9)-1)</f>
         <v/>
       </c>
-      <c r="E9" s="16" t="n"/>
+      <c r="E9" s="17" t="n"/>
       <c r="G9" s="5" t="n">
         <v>5</v>
       </c>
@@ -1305,17 +1305,17 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="16" t="n"/>
-      <c r="B10" s="16" t="n"/>
+      <c r="A10" s="17" t="n"/>
+      <c r="B10" s="17" t="n"/>
       <c r="C10" s="14">
         <f>IF(OR(B10="",SUM($B$5:$B$24)=0),"",B10/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D10" s="17">
+      <c r="D10" s="16">
         <f>IF(B10="","",RANK(B10,$B$5:$B$24,0)+COUNTIF($B$5:B10,B10)-1)</f>
         <v/>
       </c>
-      <c r="E10" s="16" t="n"/>
+      <c r="E10" s="17" t="n"/>
       <c r="G10" s="5" t="n">
         <v>6</v>
       </c>
@@ -1337,17 +1337,17 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="16" t="n"/>
-      <c r="B11" s="16" t="n"/>
+      <c r="A11" s="17" t="n"/>
+      <c r="B11" s="17" t="n"/>
       <c r="C11" s="14">
         <f>IF(OR(B11="",SUM($B$5:$B$24)=0),"",B11/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D11" s="17">
+      <c r="D11" s="16">
         <f>IF(B11="","",RANK(B11,$B$5:$B$24,0)+COUNTIF($B$5:B11,B11)-1)</f>
         <v/>
       </c>
-      <c r="E11" s="16" t="n"/>
+      <c r="E11" s="17" t="n"/>
       <c r="G11" s="5" t="n">
         <v>7</v>
       </c>
@@ -1369,17 +1369,17 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="16" t="n"/>
-      <c r="B12" s="16" t="n"/>
+      <c r="A12" s="17" t="n"/>
+      <c r="B12" s="17" t="n"/>
       <c r="C12" s="14">
         <f>IF(OR(B12="",SUM($B$5:$B$24)=0),"",B12/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D12" s="17">
+      <c r="D12" s="16">
         <f>IF(B12="","",RANK(B12,$B$5:$B$24,0)+COUNTIF($B$5:B12,B12)-1)</f>
         <v/>
       </c>
-      <c r="E12" s="16" t="n"/>
+      <c r="E12" s="17" t="n"/>
       <c r="G12" s="5" t="n">
         <v>8</v>
       </c>
@@ -1401,17 +1401,17 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="16" t="n"/>
-      <c r="B13" s="16" t="n"/>
+      <c r="A13" s="17" t="n"/>
+      <c r="B13" s="17" t="n"/>
       <c r="C13" s="14">
         <f>IF(OR(B13="",SUM($B$5:$B$24)=0),"",B13/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D13" s="17">
+      <c r="D13" s="16">
         <f>IF(B13="","",RANK(B13,$B$5:$B$24,0)+COUNTIF($B$5:B13,B13)-1)</f>
         <v/>
       </c>
-      <c r="E13" s="16" t="n"/>
+      <c r="E13" s="17" t="n"/>
       <c r="G13" s="5" t="n">
         <v>9</v>
       </c>
@@ -1433,17 +1433,17 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="16" t="n"/>
-      <c r="B14" s="16" t="n"/>
+      <c r="A14" s="17" t="n"/>
+      <c r="B14" s="17" t="n"/>
       <c r="C14" s="14">
         <f>IF(OR(B14="",SUM($B$5:$B$24)=0),"",B14/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D14" s="17">
+      <c r="D14" s="16">
         <f>IF(B14="","",RANK(B14,$B$5:$B$24,0)+COUNTIF($B$5:B14,B14)-1)</f>
         <v/>
       </c>
-      <c r="E14" s="16" t="n"/>
+      <c r="E14" s="17" t="n"/>
       <c r="G14" s="5" t="n">
         <v>10</v>
       </c>
@@ -1465,17 +1465,17 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="16" t="n"/>
-      <c r="B15" s="16" t="n"/>
+      <c r="A15" s="17" t="n"/>
+      <c r="B15" s="17" t="n"/>
       <c r="C15" s="14">
         <f>IF(OR(B15="",SUM($B$5:$B$24)=0),"",B15/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D15" s="17">
+      <c r="D15" s="16">
         <f>IF(B15="","",RANK(B15,$B$5:$B$24,0)+COUNTIF($B$5:B15,B15)-1)</f>
         <v/>
       </c>
-      <c r="E15" s="16" t="n"/>
+      <c r="E15" s="17" t="n"/>
       <c r="G15" s="5" t="n">
         <v>11</v>
       </c>
@@ -1497,17 +1497,17 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="16" t="n"/>
-      <c r="B16" s="16" t="n"/>
+      <c r="A16" s="17" t="n"/>
+      <c r="B16" s="17" t="n"/>
       <c r="C16" s="14">
         <f>IF(OR(B16="",SUM($B$5:$B$24)=0),"",B16/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D16" s="17">
+      <c r="D16" s="16">
         <f>IF(B16="","",RANK(B16,$B$5:$B$24,0)+COUNTIF($B$5:B16,B16)-1)</f>
         <v/>
       </c>
-      <c r="E16" s="16" t="n"/>
+      <c r="E16" s="17" t="n"/>
       <c r="G16" s="5" t="n">
         <v>12</v>
       </c>
@@ -1529,17 +1529,17 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="16" t="n"/>
-      <c r="B17" s="16" t="n"/>
+      <c r="A17" s="17" t="n"/>
+      <c r="B17" s="17" t="n"/>
       <c r="C17" s="14">
         <f>IF(OR(B17="",SUM($B$5:$B$24)=0),"",B17/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D17" s="17">
+      <c r="D17" s="16">
         <f>IF(B17="","",RANK(B17,$B$5:$B$24,0)+COUNTIF($B$5:B17,B17)-1)</f>
         <v/>
       </c>
-      <c r="E17" s="16" t="n"/>
+      <c r="E17" s="17" t="n"/>
       <c r="G17" s="5" t="n">
         <v>13</v>
       </c>
@@ -1561,17 +1561,17 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="16" t="n"/>
-      <c r="B18" s="16" t="n"/>
+      <c r="A18" s="17" t="n"/>
+      <c r="B18" s="17" t="n"/>
       <c r="C18" s="14">
         <f>IF(OR(B18="",SUM($B$5:$B$24)=0),"",B18/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D18" s="17">
+      <c r="D18" s="16">
         <f>IF(B18="","",RANK(B18,$B$5:$B$24,0)+COUNTIF($B$5:B18,B18)-1)</f>
         <v/>
       </c>
-      <c r="E18" s="16" t="n"/>
+      <c r="E18" s="17" t="n"/>
       <c r="G18" s="5" t="n">
         <v>14</v>
       </c>
@@ -1593,17 +1593,17 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="16" t="n"/>
-      <c r="B19" s="16" t="n"/>
+      <c r="A19" s="17" t="n"/>
+      <c r="B19" s="17" t="n"/>
       <c r="C19" s="14">
         <f>IF(OR(B19="",SUM($B$5:$B$24)=0),"",B19/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D19" s="17">
+      <c r="D19" s="16">
         <f>IF(B19="","",RANK(B19,$B$5:$B$24,0)+COUNTIF($B$5:B19,B19)-1)</f>
         <v/>
       </c>
-      <c r="E19" s="16" t="n"/>
+      <c r="E19" s="17" t="n"/>
       <c r="G19" s="5" t="n">
         <v>15</v>
       </c>
@@ -1625,17 +1625,17 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="16" t="n"/>
-      <c r="B20" s="16" t="n"/>
+      <c r="A20" s="17" t="n"/>
+      <c r="B20" s="17" t="n"/>
       <c r="C20" s="14">
         <f>IF(OR(B20="",SUM($B$5:$B$24)=0),"",B20/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D20" s="17">
+      <c r="D20" s="16">
         <f>IF(B20="","",RANK(B20,$B$5:$B$24,0)+COUNTIF($B$5:B20,B20)-1)</f>
         <v/>
       </c>
-      <c r="E20" s="16" t="n"/>
+      <c r="E20" s="17" t="n"/>
       <c r="G20" s="5" t="n">
         <v>16</v>
       </c>
@@ -1657,17 +1657,17 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="16" t="n"/>
-      <c r="B21" s="16" t="n"/>
+      <c r="A21" s="17" t="n"/>
+      <c r="B21" s="17" t="n"/>
       <c r="C21" s="14">
         <f>IF(OR(B21="",SUM($B$5:$B$24)=0),"",B21/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D21" s="17">
+      <c r="D21" s="16">
         <f>IF(B21="","",RANK(B21,$B$5:$B$24,0)+COUNTIF($B$5:B21,B21)-1)</f>
         <v/>
       </c>
-      <c r="E21" s="16" t="n"/>
+      <c r="E21" s="17" t="n"/>
       <c r="G21" s="5" t="n">
         <v>17</v>
       </c>
@@ -1689,17 +1689,17 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="16" t="n"/>
-      <c r="B22" s="16" t="n"/>
+      <c r="A22" s="17" t="n"/>
+      <c r="B22" s="17" t="n"/>
       <c r="C22" s="14">
         <f>IF(OR(B22="",SUM($B$5:$B$24)=0),"",B22/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D22" s="17">
+      <c r="D22" s="16">
         <f>IF(B22="","",RANK(B22,$B$5:$B$24,0)+COUNTIF($B$5:B22,B22)-1)</f>
         <v/>
       </c>
-      <c r="E22" s="16" t="n"/>
+      <c r="E22" s="17" t="n"/>
       <c r="G22" s="5" t="n">
         <v>18</v>
       </c>
@@ -1721,17 +1721,17 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="16" t="n"/>
-      <c r="B23" s="16" t="n"/>
+      <c r="A23" s="17" t="n"/>
+      <c r="B23" s="17" t="n"/>
       <c r="C23" s="14">
         <f>IF(OR(B23="",SUM($B$5:$B$24)=0),"",B23/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D23" s="17">
+      <c r="D23" s="16">
         <f>IF(B23="","",RANK(B23,$B$5:$B$24,0)+COUNTIF($B$5:B23,B23)-1)</f>
         <v/>
       </c>
-      <c r="E23" s="16" t="n"/>
+      <c r="E23" s="17" t="n"/>
       <c r="G23" s="5" t="n">
         <v>19</v>
       </c>
@@ -1753,17 +1753,17 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="16" t="n"/>
-      <c r="B24" s="16" t="n"/>
+      <c r="A24" s="17" t="n"/>
+      <c r="B24" s="17" t="n"/>
       <c r="C24" s="14">
         <f>IF(OR(B24="",SUM($B$5:$B$24)=0),"",B24/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D24" s="17">
+      <c r="D24" s="16">
         <f>IF(B24="","",RANK(B24,$B$5:$B$24,0)+COUNTIF($B$5:B24,B24)-1)</f>
         <v/>
       </c>
-      <c r="E24" s="16" t="n"/>
+      <c r="E24" s="17" t="n"/>
       <c r="G24" s="5" t="n">
         <v>20</v>
       </c>

--- a/templates/25-pareto-and-distribution.xlsx
+++ b/templates/25-pareto-and-distribution.xlsx
@@ -1896,7 +1896,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Support durations are right-skewed. The mean flatters you; the median and p90 do not.</t>
+          <t>Normality assessment for support data. Support durations are right-skewed: the mean flatters you, the median and p90 do not. Read the skew before you pick a test — a two-sample t-test on data this shaped will mislead you, and the non-parametric equivalent will not.</t>
         </is>
       </c>
     </row>

--- a/templates/25-pareto-and-distribution.xlsx
+++ b/templates/25-pareto-and-distribution.xlsx
@@ -111,7 +111,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -134,8 +134,8 @@
     <xf numFmtId="3" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -146,6 +146,7 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1153,23 +1154,23 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>Wrong plan applied</t>
         </is>
       </c>
-      <c r="B6" s="9" t="n">
+      <c r="B6" s="16" t="n">
         <v>233</v>
       </c>
       <c r="C6" s="14">
         <f>IF(OR(B6="",SUM($B$5:$B$24)=0),"",B6/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D6" s="16">
+      <c r="D6" s="17">
         <f>IF(B6="","",RANK(B6,$B$5:$B$24,0)+COUNTIF($B$5:B6,B6)-1)</f>
         <v/>
       </c>
-      <c r="E6" s="17" t="n"/>
+      <c r="E6" s="16" t="n"/>
       <c r="G6" s="5" t="n">
         <v>2</v>
       </c>
@@ -1191,23 +1192,23 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>Duplicate charge</t>
         </is>
       </c>
-      <c r="B7" s="9" t="n">
+      <c r="B7" s="16" t="n">
         <v>151</v>
       </c>
       <c r="C7" s="14">
         <f>IF(OR(B7="",SUM($B$5:$B$24)=0),"",B7/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D7" s="16">
+      <c r="D7" s="17">
         <f>IF(B7="","",RANK(B7,$B$5:$B$24,0)+COUNTIF($B$5:B7,B7)-1)</f>
         <v/>
       </c>
-      <c r="E7" s="17" t="n"/>
+      <c r="E7" s="16" t="n"/>
       <c r="G7" s="5" t="n">
         <v>3</v>
       </c>
@@ -1229,23 +1230,23 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>Proration misunderstood</t>
         </is>
       </c>
-      <c r="B8" s="9" t="n">
+      <c r="B8" s="16" t="n">
         <v>96</v>
       </c>
       <c r="C8" s="14">
         <f>IF(OR(B8="",SUM($B$5:$B$24)=0),"",B8/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D8" s="16">
+      <c r="D8" s="17">
         <f>IF(B8="","",RANK(B8,$B$5:$B$24,0)+COUNTIF($B$5:B8,B8)-1)</f>
         <v/>
       </c>
-      <c r="E8" s="17" t="n"/>
+      <c r="E8" s="16" t="n"/>
       <c r="G8" s="5" t="n">
         <v>4</v>
       </c>
@@ -1267,23 +1268,23 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>Refund timing</t>
         </is>
       </c>
-      <c r="B9" s="9" t="n">
+      <c r="B9" s="16" t="n">
         <v>74</v>
       </c>
       <c r="C9" s="14">
         <f>IF(OR(B9="",SUM($B$5:$B$24)=0),"",B9/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D9" s="16">
+      <c r="D9" s="17">
         <f>IF(B9="","",RANK(B9,$B$5:$B$24,0)+COUNTIF($B$5:B9,B9)-1)</f>
         <v/>
       </c>
-      <c r="E9" s="17" t="n"/>
+      <c r="E9" s="16" t="n"/>
       <c r="G9" s="5" t="n">
         <v>5</v>
       </c>
@@ -1305,17 +1306,17 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="17" t="n"/>
-      <c r="B10" s="17" t="n"/>
+      <c r="A10" s="16" t="n"/>
+      <c r="B10" s="16" t="n"/>
       <c r="C10" s="14">
         <f>IF(OR(B10="",SUM($B$5:$B$24)=0),"",B10/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D10" s="16">
+      <c r="D10" s="17">
         <f>IF(B10="","",RANK(B10,$B$5:$B$24,0)+COUNTIF($B$5:B10,B10)-1)</f>
         <v/>
       </c>
-      <c r="E10" s="17" t="n"/>
+      <c r="E10" s="16" t="n"/>
       <c r="G10" s="5" t="n">
         <v>6</v>
       </c>
@@ -1337,17 +1338,17 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="n"/>
-      <c r="B11" s="17" t="n"/>
+      <c r="A11" s="16" t="n"/>
+      <c r="B11" s="16" t="n"/>
       <c r="C11" s="14">
         <f>IF(OR(B11="",SUM($B$5:$B$24)=0),"",B11/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D11" s="16">
+      <c r="D11" s="17">
         <f>IF(B11="","",RANK(B11,$B$5:$B$24,0)+COUNTIF($B$5:B11,B11)-1)</f>
         <v/>
       </c>
-      <c r="E11" s="17" t="n"/>
+      <c r="E11" s="16" t="n"/>
       <c r="G11" s="5" t="n">
         <v>7</v>
       </c>
@@ -1369,17 +1370,17 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="17" t="n"/>
-      <c r="B12" s="17" t="n"/>
+      <c r="A12" s="16" t="n"/>
+      <c r="B12" s="16" t="n"/>
       <c r="C12" s="14">
         <f>IF(OR(B12="",SUM($B$5:$B$24)=0),"",B12/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D12" s="16">
+      <c r="D12" s="17">
         <f>IF(B12="","",RANK(B12,$B$5:$B$24,0)+COUNTIF($B$5:B12,B12)-1)</f>
         <v/>
       </c>
-      <c r="E12" s="17" t="n"/>
+      <c r="E12" s="16" t="n"/>
       <c r="G12" s="5" t="n">
         <v>8</v>
       </c>
@@ -1401,17 +1402,17 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="17" t="n"/>
-      <c r="B13" s="17" t="n"/>
+      <c r="A13" s="16" t="n"/>
+      <c r="B13" s="16" t="n"/>
       <c r="C13" s="14">
         <f>IF(OR(B13="",SUM($B$5:$B$24)=0),"",B13/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D13" s="16">
+      <c r="D13" s="17">
         <f>IF(B13="","",RANK(B13,$B$5:$B$24,0)+COUNTIF($B$5:B13,B13)-1)</f>
         <v/>
       </c>
-      <c r="E13" s="17" t="n"/>
+      <c r="E13" s="16" t="n"/>
       <c r="G13" s="5" t="n">
         <v>9</v>
       </c>
@@ -1433,17 +1434,17 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="17" t="n"/>
-      <c r="B14" s="17" t="n"/>
+      <c r="A14" s="16" t="n"/>
+      <c r="B14" s="16" t="n"/>
       <c r="C14" s="14">
         <f>IF(OR(B14="",SUM($B$5:$B$24)=0),"",B14/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D14" s="16">
+      <c r="D14" s="17">
         <f>IF(B14="","",RANK(B14,$B$5:$B$24,0)+COUNTIF($B$5:B14,B14)-1)</f>
         <v/>
       </c>
-      <c r="E14" s="17" t="n"/>
+      <c r="E14" s="16" t="n"/>
       <c r="G14" s="5" t="n">
         <v>10</v>
       </c>
@@ -1465,17 +1466,17 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="17" t="n"/>
-      <c r="B15" s="17" t="n"/>
+      <c r="A15" s="16" t="n"/>
+      <c r="B15" s="16" t="n"/>
       <c r="C15" s="14">
         <f>IF(OR(B15="",SUM($B$5:$B$24)=0),"",B15/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D15" s="16">
+      <c r="D15" s="17">
         <f>IF(B15="","",RANK(B15,$B$5:$B$24,0)+COUNTIF($B$5:B15,B15)-1)</f>
         <v/>
       </c>
-      <c r="E15" s="17" t="n"/>
+      <c r="E15" s="16" t="n"/>
       <c r="G15" s="5" t="n">
         <v>11</v>
       </c>
@@ -1497,17 +1498,17 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="17" t="n"/>
-      <c r="B16" s="17" t="n"/>
+      <c r="A16" s="16" t="n"/>
+      <c r="B16" s="16" t="n"/>
       <c r="C16" s="14">
         <f>IF(OR(B16="",SUM($B$5:$B$24)=0),"",B16/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D16" s="16">
+      <c r="D16" s="17">
         <f>IF(B16="","",RANK(B16,$B$5:$B$24,0)+COUNTIF($B$5:B16,B16)-1)</f>
         <v/>
       </c>
-      <c r="E16" s="17" t="n"/>
+      <c r="E16" s="16" t="n"/>
       <c r="G16" s="5" t="n">
         <v>12</v>
       </c>
@@ -1529,17 +1530,17 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="17" t="n"/>
-      <c r="B17" s="17" t="n"/>
+      <c r="A17" s="16" t="n"/>
+      <c r="B17" s="16" t="n"/>
       <c r="C17" s="14">
         <f>IF(OR(B17="",SUM($B$5:$B$24)=0),"",B17/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D17" s="16">
+      <c r="D17" s="17">
         <f>IF(B17="","",RANK(B17,$B$5:$B$24,0)+COUNTIF($B$5:B17,B17)-1)</f>
         <v/>
       </c>
-      <c r="E17" s="17" t="n"/>
+      <c r="E17" s="16" t="n"/>
       <c r="G17" s="5" t="n">
         <v>13</v>
       </c>
@@ -1561,17 +1562,17 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="17" t="n"/>
-      <c r="B18" s="17" t="n"/>
+      <c r="A18" s="16" t="n"/>
+      <c r="B18" s="16" t="n"/>
       <c r="C18" s="14">
         <f>IF(OR(B18="",SUM($B$5:$B$24)=0),"",B18/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D18" s="16">
+      <c r="D18" s="17">
         <f>IF(B18="","",RANK(B18,$B$5:$B$24,0)+COUNTIF($B$5:B18,B18)-1)</f>
         <v/>
       </c>
-      <c r="E18" s="17" t="n"/>
+      <c r="E18" s="16" t="n"/>
       <c r="G18" s="5" t="n">
         <v>14</v>
       </c>
@@ -1593,17 +1594,17 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="17" t="n"/>
-      <c r="B19" s="17" t="n"/>
+      <c r="A19" s="16" t="n"/>
+      <c r="B19" s="16" t="n"/>
       <c r="C19" s="14">
         <f>IF(OR(B19="",SUM($B$5:$B$24)=0),"",B19/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D19" s="16">
+      <c r="D19" s="17">
         <f>IF(B19="","",RANK(B19,$B$5:$B$24,0)+COUNTIF($B$5:B19,B19)-1)</f>
         <v/>
       </c>
-      <c r="E19" s="17" t="n"/>
+      <c r="E19" s="16" t="n"/>
       <c r="G19" s="5" t="n">
         <v>15</v>
       </c>
@@ -1625,17 +1626,17 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="17" t="n"/>
-      <c r="B20" s="17" t="n"/>
+      <c r="A20" s="16" t="n"/>
+      <c r="B20" s="16" t="n"/>
       <c r="C20" s="14">
         <f>IF(OR(B20="",SUM($B$5:$B$24)=0),"",B20/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D20" s="16">
+      <c r="D20" s="17">
         <f>IF(B20="","",RANK(B20,$B$5:$B$24,0)+COUNTIF($B$5:B20,B20)-1)</f>
         <v/>
       </c>
-      <c r="E20" s="17" t="n"/>
+      <c r="E20" s="16" t="n"/>
       <c r="G20" s="5" t="n">
         <v>16</v>
       </c>
@@ -1657,17 +1658,17 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="17" t="n"/>
-      <c r="B21" s="17" t="n"/>
+      <c r="A21" s="16" t="n"/>
+      <c r="B21" s="16" t="n"/>
       <c r="C21" s="14">
         <f>IF(OR(B21="",SUM($B$5:$B$24)=0),"",B21/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D21" s="16">
+      <c r="D21" s="17">
         <f>IF(B21="","",RANK(B21,$B$5:$B$24,0)+COUNTIF($B$5:B21,B21)-1)</f>
         <v/>
       </c>
-      <c r="E21" s="17" t="n"/>
+      <c r="E21" s="16" t="n"/>
       <c r="G21" s="5" t="n">
         <v>17</v>
       </c>
@@ -1689,17 +1690,17 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="17" t="n"/>
-      <c r="B22" s="17" t="n"/>
+      <c r="A22" s="16" t="n"/>
+      <c r="B22" s="16" t="n"/>
       <c r="C22" s="14">
         <f>IF(OR(B22="",SUM($B$5:$B$24)=0),"",B22/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D22" s="16">
+      <c r="D22" s="17">
         <f>IF(B22="","",RANK(B22,$B$5:$B$24,0)+COUNTIF($B$5:B22,B22)-1)</f>
         <v/>
       </c>
-      <c r="E22" s="17" t="n"/>
+      <c r="E22" s="16" t="n"/>
       <c r="G22" s="5" t="n">
         <v>18</v>
       </c>
@@ -1721,17 +1722,17 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="17" t="n"/>
-      <c r="B23" s="17" t="n"/>
+      <c r="A23" s="16" t="n"/>
+      <c r="B23" s="16" t="n"/>
       <c r="C23" s="14">
         <f>IF(OR(B23="",SUM($B$5:$B$24)=0),"",B23/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D23" s="16">
+      <c r="D23" s="17">
         <f>IF(B23="","",RANK(B23,$B$5:$B$24,0)+COUNTIF($B$5:B23,B23)-1)</f>
         <v/>
       </c>
-      <c r="E23" s="17" t="n"/>
+      <c r="E23" s="16" t="n"/>
       <c r="G23" s="5" t="n">
         <v>19</v>
       </c>
@@ -1753,17 +1754,17 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="17" t="n"/>
-      <c r="B24" s="17" t="n"/>
+      <c r="A24" s="16" t="n"/>
+      <c r="B24" s="16" t="n"/>
       <c r="C24" s="14">
         <f>IF(OR(B24="",SUM($B$5:$B$24)=0),"",B24/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D24" s="16">
+      <c r="D24" s="17">
         <f>IF(B24="","",RANK(B24,$B$5:$B$24,0)+COUNTIF($B$5:B24,B24)-1)</f>
         <v/>
       </c>
-      <c r="E24" s="17" t="n"/>
+      <c r="E24" s="16" t="n"/>
       <c r="G24" s="5" t="n">
         <v>20</v>
       </c>
@@ -2100,7 +2101,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="23" t="n">
+      <c r="B21" s="24" t="n">
         <v>201</v>
       </c>
       <c r="F21" s="5" t="inlineStr">
@@ -2114,192 +2115,192 @@
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="23" t="n">
+      <c r="B22" s="24" t="n">
         <v>214</v>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="23" t="n">
+      <c r="B23" s="24" t="n">
         <v>227</v>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="23" t="n">
+      <c r="B24" s="24" t="n">
         <v>236</v>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="23" t="n">
+      <c r="B25" s="24" t="n">
         <v>241</v>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="23" t="n">
+      <c r="B26" s="24" t="n">
         <v>248</v>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="23" t="n">
+      <c r="B27" s="24" t="n">
         <v>255</v>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="23" t="n">
+      <c r="B28" s="24" t="n">
         <v>259</v>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="23" t="n">
+      <c r="B29" s="24" t="n">
         <v>263</v>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="23" t="n">
+      <c r="B30" s="24" t="n">
         <v>268</v>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="23" t="n">
+      <c r="B31" s="24" t="n">
         <v>272</v>
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="23" t="n">
+      <c r="B32" s="24" t="n">
         <v>277</v>
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="23" t="n">
+      <c r="B33" s="24" t="n">
         <v>281</v>
       </c>
     </row>
     <row r="34">
-      <c r="B34" s="23" t="n">
+      <c r="B34" s="24" t="n">
         <v>286</v>
       </c>
     </row>
     <row r="35">
-      <c r="B35" s="23" t="n">
+      <c r="B35" s="24" t="n">
         <v>292</v>
       </c>
     </row>
     <row r="36">
-      <c r="B36" s="23" t="n">
+      <c r="B36" s="24" t="n">
         <v>298</v>
       </c>
     </row>
     <row r="37">
-      <c r="B37" s="23" t="n">
+      <c r="B37" s="24" t="n">
         <v>305</v>
       </c>
     </row>
     <row r="38">
-      <c r="B38" s="23" t="n">
+      <c r="B38" s="24" t="n">
         <v>311</v>
       </c>
     </row>
     <row r="39">
-      <c r="B39" s="23" t="n">
+      <c r="B39" s="24" t="n">
         <v>318</v>
       </c>
     </row>
     <row r="40">
-      <c r="B40" s="23" t="n">
+      <c r="B40" s="24" t="n">
         <v>326</v>
       </c>
     </row>
     <row r="41">
-      <c r="B41" s="23" t="n">
+      <c r="B41" s="24" t="n">
         <v>335</v>
       </c>
     </row>
     <row r="42">
-      <c r="B42" s="23" t="n">
+      <c r="B42" s="24" t="n">
         <v>346</v>
       </c>
     </row>
     <row r="43">
-      <c r="B43" s="23" t="n">
+      <c r="B43" s="24" t="n">
         <v>358</v>
       </c>
     </row>
     <row r="44">
-      <c r="B44" s="23" t="n">
+      <c r="B44" s="24" t="n">
         <v>372</v>
       </c>
     </row>
     <row r="45">
-      <c r="B45" s="23" t="n">
+      <c r="B45" s="24" t="n">
         <v>389</v>
       </c>
     </row>
     <row r="46">
-      <c r="B46" s="23" t="n">
+      <c r="B46" s="24" t="n">
         <v>408</v>
       </c>
     </row>
     <row r="47">
-      <c r="B47" s="23" t="n">
+      <c r="B47" s="24" t="n">
         <v>431</v>
       </c>
     </row>
     <row r="48">
-      <c r="B48" s="23" t="n">
+      <c r="B48" s="24" t="n">
         <v>459</v>
       </c>
     </row>
     <row r="49">
-      <c r="B49" s="23" t="n">
+      <c r="B49" s="24" t="n">
         <v>494</v>
       </c>
     </row>
     <row r="50">
-      <c r="B50" s="23" t="n">
+      <c r="B50" s="24" t="n">
         <v>538</v>
       </c>
     </row>
     <row r="51">
-      <c r="B51" s="23" t="n">
+      <c r="B51" s="24" t="n">
         <v>594</v>
       </c>
     </row>
     <row r="52">
-      <c r="B52" s="23" t="n">
+      <c r="B52" s="24" t="n">
         <v>668</v>
       </c>
     </row>
     <row r="53">
-      <c r="B53" s="23" t="n">
+      <c r="B53" s="24" t="n">
         <v>771</v>
       </c>
     </row>
     <row r="54">
-      <c r="B54" s="23" t="n">
+      <c r="B54" s="24" t="n">
         <v>918</v>
       </c>
     </row>
     <row r="55">
-      <c r="B55" s="23" t="n">
+      <c r="B55" s="24" t="n">
         <v>1140</v>
       </c>
     </row>
     <row r="56">
-      <c r="B56" s="23" t="n">
+      <c r="B56" s="24" t="n">
         <v>1502</v>
       </c>
     </row>
     <row r="57">
-      <c r="B57" s="23" t="n">
+      <c r="B57" s="24" t="n">
         <v>2160</v>
       </c>
     </row>
     <row r="58">
-      <c r="B58" s="23" t="n">
+      <c r="B58" s="24" t="n">
         <v>3480</v>
       </c>
     </row>
     <row r="59">
-      <c r="B59" s="23" t="n">
+      <c r="B59" s="24" t="n">
         <v>5220</v>
       </c>
     </row>

--- a/templates/25-pareto-and-distribution.xlsx
+++ b/templates/25-pareto-and-distribution.xlsx
@@ -111,7 +111,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -134,8 +134,8 @@
     <xf numFmtId="3" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -146,7 +146,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -921,14 +920,14 @@
     <row r="6">
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>Green row</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
+          <t>Green cells</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>A worked example so you can see the expected format. Delete it when you start.</t>
+          <t>A worked example, so you can see the expected format and the charts say something the moment you open the file. Replace it with your own data when you start.</t>
         </is>
       </c>
     </row>
@@ -1154,23 +1153,23 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="16" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>Wrong plan applied</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n">
+      <c r="B6" s="9" t="n">
         <v>233</v>
       </c>
       <c r="C6" s="14">
         <f>IF(OR(B6="",SUM($B$5:$B$24)=0),"",B6/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D6" s="17">
+      <c r="D6" s="16">
         <f>IF(B6="","",RANK(B6,$B$5:$B$24,0)+COUNTIF($B$5:B6,B6)-1)</f>
         <v/>
       </c>
-      <c r="E6" s="16" t="n"/>
+      <c r="E6" s="17" t="n"/>
       <c r="G6" s="5" t="n">
         <v>2</v>
       </c>
@@ -1192,23 +1191,23 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="16" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>Duplicate charge</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n">
+      <c r="B7" s="9" t="n">
         <v>151</v>
       </c>
       <c r="C7" s="14">
         <f>IF(OR(B7="",SUM($B$5:$B$24)=0),"",B7/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D7" s="17">
+      <c r="D7" s="16">
         <f>IF(B7="","",RANK(B7,$B$5:$B$24,0)+COUNTIF($B$5:B7,B7)-1)</f>
         <v/>
       </c>
-      <c r="E7" s="16" t="n"/>
+      <c r="E7" s="17" t="n"/>
       <c r="G7" s="5" t="n">
         <v>3</v>
       </c>
@@ -1230,23 +1229,23 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="16" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>Proration misunderstood</t>
         </is>
       </c>
-      <c r="B8" s="16" t="n">
+      <c r="B8" s="9" t="n">
         <v>96</v>
       </c>
       <c r="C8" s="14">
         <f>IF(OR(B8="",SUM($B$5:$B$24)=0),"",B8/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D8" s="17">
+      <c r="D8" s="16">
         <f>IF(B8="","",RANK(B8,$B$5:$B$24,0)+COUNTIF($B$5:B8,B8)-1)</f>
         <v/>
       </c>
-      <c r="E8" s="16" t="n"/>
+      <c r="E8" s="17" t="n"/>
       <c r="G8" s="5" t="n">
         <v>4</v>
       </c>
@@ -1268,23 +1267,23 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="16" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>Refund timing</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n">
+      <c r="B9" s="9" t="n">
         <v>74</v>
       </c>
       <c r="C9" s="14">
         <f>IF(OR(B9="",SUM($B$5:$B$24)=0),"",B9/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D9" s="17">
+      <c r="D9" s="16">
         <f>IF(B9="","",RANK(B9,$B$5:$B$24,0)+COUNTIF($B$5:B9,B9)-1)</f>
         <v/>
       </c>
-      <c r="E9" s="16" t="n"/>
+      <c r="E9" s="17" t="n"/>
       <c r="G9" s="5" t="n">
         <v>5</v>
       </c>
@@ -1306,17 +1305,17 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="16" t="n"/>
-      <c r="B10" s="16" t="n"/>
+      <c r="A10" s="17" t="n"/>
+      <c r="B10" s="17" t="n"/>
       <c r="C10" s="14">
         <f>IF(OR(B10="",SUM($B$5:$B$24)=0),"",B10/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D10" s="17">
+      <c r="D10" s="16">
         <f>IF(B10="","",RANK(B10,$B$5:$B$24,0)+COUNTIF($B$5:B10,B10)-1)</f>
         <v/>
       </c>
-      <c r="E10" s="16" t="n"/>
+      <c r="E10" s="17" t="n"/>
       <c r="G10" s="5" t="n">
         <v>6</v>
       </c>
@@ -1338,17 +1337,17 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="16" t="n"/>
-      <c r="B11" s="16" t="n"/>
+      <c r="A11" s="17" t="n"/>
+      <c r="B11" s="17" t="n"/>
       <c r="C11" s="14">
         <f>IF(OR(B11="",SUM($B$5:$B$24)=0),"",B11/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D11" s="17">
+      <c r="D11" s="16">
         <f>IF(B11="","",RANK(B11,$B$5:$B$24,0)+COUNTIF($B$5:B11,B11)-1)</f>
         <v/>
       </c>
-      <c r="E11" s="16" t="n"/>
+      <c r="E11" s="17" t="n"/>
       <c r="G11" s="5" t="n">
         <v>7</v>
       </c>
@@ -1370,17 +1369,17 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="16" t="n"/>
-      <c r="B12" s="16" t="n"/>
+      <c r="A12" s="17" t="n"/>
+      <c r="B12" s="17" t="n"/>
       <c r="C12" s="14">
         <f>IF(OR(B12="",SUM($B$5:$B$24)=0),"",B12/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D12" s="17">
+      <c r="D12" s="16">
         <f>IF(B12="","",RANK(B12,$B$5:$B$24,0)+COUNTIF($B$5:B12,B12)-1)</f>
         <v/>
       </c>
-      <c r="E12" s="16" t="n"/>
+      <c r="E12" s="17" t="n"/>
       <c r="G12" s="5" t="n">
         <v>8</v>
       </c>
@@ -1402,17 +1401,17 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="16" t="n"/>
-      <c r="B13" s="16" t="n"/>
+      <c r="A13" s="17" t="n"/>
+      <c r="B13" s="17" t="n"/>
       <c r="C13" s="14">
         <f>IF(OR(B13="",SUM($B$5:$B$24)=0),"",B13/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D13" s="17">
+      <c r="D13" s="16">
         <f>IF(B13="","",RANK(B13,$B$5:$B$24,0)+COUNTIF($B$5:B13,B13)-1)</f>
         <v/>
       </c>
-      <c r="E13" s="16" t="n"/>
+      <c r="E13" s="17" t="n"/>
       <c r="G13" s="5" t="n">
         <v>9</v>
       </c>
@@ -1434,17 +1433,17 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="16" t="n"/>
-      <c r="B14" s="16" t="n"/>
+      <c r="A14" s="17" t="n"/>
+      <c r="B14" s="17" t="n"/>
       <c r="C14" s="14">
         <f>IF(OR(B14="",SUM($B$5:$B$24)=0),"",B14/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D14" s="17">
+      <c r="D14" s="16">
         <f>IF(B14="","",RANK(B14,$B$5:$B$24,0)+COUNTIF($B$5:B14,B14)-1)</f>
         <v/>
       </c>
-      <c r="E14" s="16" t="n"/>
+      <c r="E14" s="17" t="n"/>
       <c r="G14" s="5" t="n">
         <v>10</v>
       </c>
@@ -1466,17 +1465,17 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="16" t="n"/>
-      <c r="B15" s="16" t="n"/>
+      <c r="A15" s="17" t="n"/>
+      <c r="B15" s="17" t="n"/>
       <c r="C15" s="14">
         <f>IF(OR(B15="",SUM($B$5:$B$24)=0),"",B15/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D15" s="17">
+      <c r="D15" s="16">
         <f>IF(B15="","",RANK(B15,$B$5:$B$24,0)+COUNTIF($B$5:B15,B15)-1)</f>
         <v/>
       </c>
-      <c r="E15" s="16" t="n"/>
+      <c r="E15" s="17" t="n"/>
       <c r="G15" s="5" t="n">
         <v>11</v>
       </c>
@@ -1498,17 +1497,17 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="16" t="n"/>
-      <c r="B16" s="16" t="n"/>
+      <c r="A16" s="17" t="n"/>
+      <c r="B16" s="17" t="n"/>
       <c r="C16" s="14">
         <f>IF(OR(B16="",SUM($B$5:$B$24)=0),"",B16/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D16" s="17">
+      <c r="D16" s="16">
         <f>IF(B16="","",RANK(B16,$B$5:$B$24,0)+COUNTIF($B$5:B16,B16)-1)</f>
         <v/>
       </c>
-      <c r="E16" s="16" t="n"/>
+      <c r="E16" s="17" t="n"/>
       <c r="G16" s="5" t="n">
         <v>12</v>
       </c>
@@ -1530,17 +1529,17 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="16" t="n"/>
-      <c r="B17" s="16" t="n"/>
+      <c r="A17" s="17" t="n"/>
+      <c r="B17" s="17" t="n"/>
       <c r="C17" s="14">
         <f>IF(OR(B17="",SUM($B$5:$B$24)=0),"",B17/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D17" s="17">
+      <c r="D17" s="16">
         <f>IF(B17="","",RANK(B17,$B$5:$B$24,0)+COUNTIF($B$5:B17,B17)-1)</f>
         <v/>
       </c>
-      <c r="E17" s="16" t="n"/>
+      <c r="E17" s="17" t="n"/>
       <c r="G17" s="5" t="n">
         <v>13</v>
       </c>
@@ -1562,17 +1561,17 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="16" t="n"/>
-      <c r="B18" s="16" t="n"/>
+      <c r="A18" s="17" t="n"/>
+      <c r="B18" s="17" t="n"/>
       <c r="C18" s="14">
         <f>IF(OR(B18="",SUM($B$5:$B$24)=0),"",B18/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D18" s="17">
+      <c r="D18" s="16">
         <f>IF(B18="","",RANK(B18,$B$5:$B$24,0)+COUNTIF($B$5:B18,B18)-1)</f>
         <v/>
       </c>
-      <c r="E18" s="16" t="n"/>
+      <c r="E18" s="17" t="n"/>
       <c r="G18" s="5" t="n">
         <v>14</v>
       </c>
@@ -1594,17 +1593,17 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="16" t="n"/>
-      <c r="B19" s="16" t="n"/>
+      <c r="A19" s="17" t="n"/>
+      <c r="B19" s="17" t="n"/>
       <c r="C19" s="14">
         <f>IF(OR(B19="",SUM($B$5:$B$24)=0),"",B19/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D19" s="17">
+      <c r="D19" s="16">
         <f>IF(B19="","",RANK(B19,$B$5:$B$24,0)+COUNTIF($B$5:B19,B19)-1)</f>
         <v/>
       </c>
-      <c r="E19" s="16" t="n"/>
+      <c r="E19" s="17" t="n"/>
       <c r="G19" s="5" t="n">
         <v>15</v>
       </c>
@@ -1626,17 +1625,17 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="16" t="n"/>
-      <c r="B20" s="16" t="n"/>
+      <c r="A20" s="17" t="n"/>
+      <c r="B20" s="17" t="n"/>
       <c r="C20" s="14">
         <f>IF(OR(B20="",SUM($B$5:$B$24)=0),"",B20/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D20" s="17">
+      <c r="D20" s="16">
         <f>IF(B20="","",RANK(B20,$B$5:$B$24,0)+COUNTIF($B$5:B20,B20)-1)</f>
         <v/>
       </c>
-      <c r="E20" s="16" t="n"/>
+      <c r="E20" s="17" t="n"/>
       <c r="G20" s="5" t="n">
         <v>16</v>
       </c>
@@ -1658,17 +1657,17 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="16" t="n"/>
-      <c r="B21" s="16" t="n"/>
+      <c r="A21" s="17" t="n"/>
+      <c r="B21" s="17" t="n"/>
       <c r="C21" s="14">
         <f>IF(OR(B21="",SUM($B$5:$B$24)=0),"",B21/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D21" s="17">
+      <c r="D21" s="16">
         <f>IF(B21="","",RANK(B21,$B$5:$B$24,0)+COUNTIF($B$5:B21,B21)-1)</f>
         <v/>
       </c>
-      <c r="E21" s="16" t="n"/>
+      <c r="E21" s="17" t="n"/>
       <c r="G21" s="5" t="n">
         <v>17</v>
       </c>
@@ -1690,17 +1689,17 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="16" t="n"/>
-      <c r="B22" s="16" t="n"/>
+      <c r="A22" s="17" t="n"/>
+      <c r="B22" s="17" t="n"/>
       <c r="C22" s="14">
         <f>IF(OR(B22="",SUM($B$5:$B$24)=0),"",B22/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D22" s="17">
+      <c r="D22" s="16">
         <f>IF(B22="","",RANK(B22,$B$5:$B$24,0)+COUNTIF($B$5:B22,B22)-1)</f>
         <v/>
       </c>
-      <c r="E22" s="16" t="n"/>
+      <c r="E22" s="17" t="n"/>
       <c r="G22" s="5" t="n">
         <v>18</v>
       </c>
@@ -1722,17 +1721,17 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="16" t="n"/>
-      <c r="B23" s="16" t="n"/>
+      <c r="A23" s="17" t="n"/>
+      <c r="B23" s="17" t="n"/>
       <c r="C23" s="14">
         <f>IF(OR(B23="",SUM($B$5:$B$24)=0),"",B23/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D23" s="17">
+      <c r="D23" s="16">
         <f>IF(B23="","",RANK(B23,$B$5:$B$24,0)+COUNTIF($B$5:B23,B23)-1)</f>
         <v/>
       </c>
-      <c r="E23" s="16" t="n"/>
+      <c r="E23" s="17" t="n"/>
       <c r="G23" s="5" t="n">
         <v>19</v>
       </c>
@@ -1754,17 +1753,17 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="16" t="n"/>
-      <c r="B24" s="16" t="n"/>
+      <c r="A24" s="17" t="n"/>
+      <c r="B24" s="17" t="n"/>
       <c r="C24" s="14">
         <f>IF(OR(B24="",SUM($B$5:$B$24)=0),"",B24/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D24" s="17">
+      <c r="D24" s="16">
         <f>IF(B24="","",RANK(B24,$B$5:$B$24,0)+COUNTIF($B$5:B24,B24)-1)</f>
         <v/>
       </c>
-      <c r="E24" s="16" t="n"/>
+      <c r="E24" s="17" t="n"/>
       <c r="G24" s="5" t="n">
         <v>20</v>
       </c>
@@ -2101,7 +2100,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="24" t="n">
+      <c r="B21" s="23" t="n">
         <v>201</v>
       </c>
       <c r="F21" s="5" t="inlineStr">
@@ -2115,192 +2114,192 @@
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="24" t="n">
+      <c r="B22" s="23" t="n">
         <v>214</v>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="24" t="n">
+      <c r="B23" s="23" t="n">
         <v>227</v>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="24" t="n">
+      <c r="B24" s="23" t="n">
         <v>236</v>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="24" t="n">
+      <c r="B25" s="23" t="n">
         <v>241</v>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="24" t="n">
+      <c r="B26" s="23" t="n">
         <v>248</v>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="24" t="n">
+      <c r="B27" s="23" t="n">
         <v>255</v>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="24" t="n">
+      <c r="B28" s="23" t="n">
         <v>259</v>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="24" t="n">
+      <c r="B29" s="23" t="n">
         <v>263</v>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="24" t="n">
+      <c r="B30" s="23" t="n">
         <v>268</v>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="24" t="n">
+      <c r="B31" s="23" t="n">
         <v>272</v>
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="24" t="n">
+      <c r="B32" s="23" t="n">
         <v>277</v>
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="24" t="n">
+      <c r="B33" s="23" t="n">
         <v>281</v>
       </c>
     </row>
     <row r="34">
-      <c r="B34" s="24" t="n">
+      <c r="B34" s="23" t="n">
         <v>286</v>
       </c>
     </row>
     <row r="35">
-      <c r="B35" s="24" t="n">
+      <c r="B35" s="23" t="n">
         <v>292</v>
       </c>
     </row>
     <row r="36">
-      <c r="B36" s="24" t="n">
+      <c r="B36" s="23" t="n">
         <v>298</v>
       </c>
     </row>
     <row r="37">
-      <c r="B37" s="24" t="n">
+      <c r="B37" s="23" t="n">
         <v>305</v>
       </c>
     </row>
     <row r="38">
-      <c r="B38" s="24" t="n">
+      <c r="B38" s="23" t="n">
         <v>311</v>
       </c>
     </row>
     <row r="39">
-      <c r="B39" s="24" t="n">
+      <c r="B39" s="23" t="n">
         <v>318</v>
       </c>
     </row>
     <row r="40">
-      <c r="B40" s="24" t="n">
+      <c r="B40" s="23" t="n">
         <v>326</v>
       </c>
     </row>
     <row r="41">
-      <c r="B41" s="24" t="n">
+      <c r="B41" s="23" t="n">
         <v>335</v>
       </c>
     </row>
     <row r="42">
-      <c r="B42" s="24" t="n">
+      <c r="B42" s="23" t="n">
         <v>346</v>
       </c>
     </row>
     <row r="43">
-      <c r="B43" s="24" t="n">
+      <c r="B43" s="23" t="n">
         <v>358</v>
       </c>
     </row>
     <row r="44">
-      <c r="B44" s="24" t="n">
+      <c r="B44" s="23" t="n">
         <v>372</v>
       </c>
     </row>
     <row r="45">
-      <c r="B45" s="24" t="n">
+      <c r="B45" s="23" t="n">
         <v>389</v>
       </c>
     </row>
     <row r="46">
-      <c r="B46" s="24" t="n">
+      <c r="B46" s="23" t="n">
         <v>408</v>
       </c>
     </row>
     <row r="47">
-      <c r="B47" s="24" t="n">
+      <c r="B47" s="23" t="n">
         <v>431</v>
       </c>
     </row>
     <row r="48">
-      <c r="B48" s="24" t="n">
+      <c r="B48" s="23" t="n">
         <v>459</v>
       </c>
     </row>
     <row r="49">
-      <c r="B49" s="24" t="n">
+      <c r="B49" s="23" t="n">
         <v>494</v>
       </c>
     </row>
     <row r="50">
-      <c r="B50" s="24" t="n">
+      <c r="B50" s="23" t="n">
         <v>538</v>
       </c>
     </row>
     <row r="51">
-      <c r="B51" s="24" t="n">
+      <c r="B51" s="23" t="n">
         <v>594</v>
       </c>
     </row>
     <row r="52">
-      <c r="B52" s="24" t="n">
+      <c r="B52" s="23" t="n">
         <v>668</v>
       </c>
     </row>
     <row r="53">
-      <c r="B53" s="24" t="n">
+      <c r="B53" s="23" t="n">
         <v>771</v>
       </c>
     </row>
     <row r="54">
-      <c r="B54" s="24" t="n">
+      <c r="B54" s="23" t="n">
         <v>918</v>
       </c>
     </row>
     <row r="55">
-      <c r="B55" s="24" t="n">
+      <c r="B55" s="23" t="n">
         <v>1140</v>
       </c>
     </row>
     <row r="56">
-      <c r="B56" s="24" t="n">
+      <c r="B56" s="23" t="n">
         <v>1502</v>
       </c>
     </row>
     <row r="57">
-      <c r="B57" s="24" t="n">
+      <c r="B57" s="23" t="n">
         <v>2160</v>
       </c>
     </row>
     <row r="58">
-      <c r="B58" s="24" t="n">
+      <c r="B58" s="23" t="n">
         <v>3480</v>
       </c>
     </row>
     <row r="59">
-      <c r="B59" s="24" t="n">
+      <c r="B59" s="23" t="n">
         <v>5220</v>
       </c>
     </row>

--- a/templates/25-pareto-and-distribution.xlsx
+++ b/templates/25-pareto-and-distribution.xlsx
@@ -111,7 +111,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -128,13 +128,11 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -1143,11 +1141,11 @@
         <f>IFERROR(INDEX($B$5:$B$24,MATCH(G5,$D$5:$D$24,0)),"")</f>
         <v/>
       </c>
-      <c r="J5" s="14">
+      <c r="J5" s="10">
         <f>IF(I5="",NA(),SUM($I$5:I5)/SUM($I$5:$I$24))</f>
         <v/>
       </c>
-      <c r="K5" s="15">
+      <c r="K5" s="14">
         <f>IF(I5="",NA(),0.8)</f>
         <v/>
       </c>
@@ -1161,15 +1159,15 @@
       <c r="B6" s="9" t="n">
         <v>233</v>
       </c>
-      <c r="C6" s="14">
+      <c r="C6" s="10">
         <f>IF(OR(B6="",SUM($B$5:$B$24)=0),"",B6/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D6" s="16">
+      <c r="D6" s="11">
         <f>IF(B6="","",RANK(B6,$B$5:$B$24,0)+COUNTIF($B$5:B6,B6)-1)</f>
         <v/>
       </c>
-      <c r="E6" s="17" t="n"/>
+      <c r="E6" s="15" t="n"/>
       <c r="G6" s="5" t="n">
         <v>2</v>
       </c>
@@ -1181,11 +1179,11 @@
         <f>IFERROR(INDEX($B$5:$B$24,MATCH(G6,$D$5:$D$24,0)),"")</f>
         <v/>
       </c>
-      <c r="J6" s="14">
+      <c r="J6" s="10">
         <f>IF(I6="",NA(),SUM($I$5:I6)/SUM($I$5:$I$24))</f>
         <v/>
       </c>
-      <c r="K6" s="15">
+      <c r="K6" s="14">
         <f>IF(I6="",NA(),0.8)</f>
         <v/>
       </c>
@@ -1199,15 +1197,15 @@
       <c r="B7" s="9" t="n">
         <v>151</v>
       </c>
-      <c r="C7" s="14">
+      <c r="C7" s="10">
         <f>IF(OR(B7="",SUM($B$5:$B$24)=0),"",B7/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D7" s="16">
+      <c r="D7" s="11">
         <f>IF(B7="","",RANK(B7,$B$5:$B$24,0)+COUNTIF($B$5:B7,B7)-1)</f>
         <v/>
       </c>
-      <c r="E7" s="17" t="n"/>
+      <c r="E7" s="15" t="n"/>
       <c r="G7" s="5" t="n">
         <v>3</v>
       </c>
@@ -1219,11 +1217,11 @@
         <f>IFERROR(INDEX($B$5:$B$24,MATCH(G7,$D$5:$D$24,0)),"")</f>
         <v/>
       </c>
-      <c r="J7" s="14">
+      <c r="J7" s="10">
         <f>IF(I7="",NA(),SUM($I$5:I7)/SUM($I$5:$I$24))</f>
         <v/>
       </c>
-      <c r="K7" s="15">
+      <c r="K7" s="14">
         <f>IF(I7="",NA(),0.8)</f>
         <v/>
       </c>
@@ -1237,15 +1235,15 @@
       <c r="B8" s="9" t="n">
         <v>96</v>
       </c>
-      <c r="C8" s="14">
+      <c r="C8" s="10">
         <f>IF(OR(B8="",SUM($B$5:$B$24)=0),"",B8/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D8" s="16">
+      <c r="D8" s="11">
         <f>IF(B8="","",RANK(B8,$B$5:$B$24,0)+COUNTIF($B$5:B8,B8)-1)</f>
         <v/>
       </c>
-      <c r="E8" s="17" t="n"/>
+      <c r="E8" s="15" t="n"/>
       <c r="G8" s="5" t="n">
         <v>4</v>
       </c>
@@ -1257,11 +1255,11 @@
         <f>IFERROR(INDEX($B$5:$B$24,MATCH(G8,$D$5:$D$24,0)),"")</f>
         <v/>
       </c>
-      <c r="J8" s="14">
+      <c r="J8" s="10">
         <f>IF(I8="",NA(),SUM($I$5:I8)/SUM($I$5:$I$24))</f>
         <v/>
       </c>
-      <c r="K8" s="15">
+      <c r="K8" s="14">
         <f>IF(I8="",NA(),0.8)</f>
         <v/>
       </c>
@@ -1275,15 +1273,15 @@
       <c r="B9" s="9" t="n">
         <v>74</v>
       </c>
-      <c r="C9" s="14">
+      <c r="C9" s="10">
         <f>IF(OR(B9="",SUM($B$5:$B$24)=0),"",B9/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D9" s="16">
+      <c r="D9" s="11">
         <f>IF(B9="","",RANK(B9,$B$5:$B$24,0)+COUNTIF($B$5:B9,B9)-1)</f>
         <v/>
       </c>
-      <c r="E9" s="17" t="n"/>
+      <c r="E9" s="15" t="n"/>
       <c r="G9" s="5" t="n">
         <v>5</v>
       </c>
@@ -1295,27 +1293,27 @@
         <f>IFERROR(INDEX($B$5:$B$24,MATCH(G9,$D$5:$D$24,0)),"")</f>
         <v/>
       </c>
-      <c r="J9" s="14">
+      <c r="J9" s="10">
         <f>IF(I9="",NA(),SUM($I$5:I9)/SUM($I$5:$I$24))</f>
         <v/>
       </c>
-      <c r="K9" s="15">
+      <c r="K9" s="14">
         <f>IF(I9="",NA(),0.8)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="17" t="n"/>
-      <c r="B10" s="17" t="n"/>
-      <c r="C10" s="14">
+      <c r="A10" s="15" t="n"/>
+      <c r="B10" s="15" t="n"/>
+      <c r="C10" s="10">
         <f>IF(OR(B10="",SUM($B$5:$B$24)=0),"",B10/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D10" s="16">
+      <c r="D10" s="11">
         <f>IF(B10="","",RANK(B10,$B$5:$B$24,0)+COUNTIF($B$5:B10,B10)-1)</f>
         <v/>
       </c>
-      <c r="E10" s="17" t="n"/>
+      <c r="E10" s="15" t="n"/>
       <c r="G10" s="5" t="n">
         <v>6</v>
       </c>
@@ -1327,27 +1325,27 @@
         <f>IFERROR(INDEX($B$5:$B$24,MATCH(G10,$D$5:$D$24,0)),"")</f>
         <v/>
       </c>
-      <c r="J10" s="14">
+      <c r="J10" s="10">
         <f>IF(I10="",NA(),SUM($I$5:I10)/SUM($I$5:$I$24))</f>
         <v/>
       </c>
-      <c r="K10" s="15">
+      <c r="K10" s="14">
         <f>IF(I10="",NA(),0.8)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="n"/>
-      <c r="B11" s="17" t="n"/>
-      <c r="C11" s="14">
+      <c r="A11" s="15" t="n"/>
+      <c r="B11" s="15" t="n"/>
+      <c r="C11" s="10">
         <f>IF(OR(B11="",SUM($B$5:$B$24)=0),"",B11/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D11" s="16">
+      <c r="D11" s="11">
         <f>IF(B11="","",RANK(B11,$B$5:$B$24,0)+COUNTIF($B$5:B11,B11)-1)</f>
         <v/>
       </c>
-      <c r="E11" s="17" t="n"/>
+      <c r="E11" s="15" t="n"/>
       <c r="G11" s="5" t="n">
         <v>7</v>
       </c>
@@ -1359,27 +1357,27 @@
         <f>IFERROR(INDEX($B$5:$B$24,MATCH(G11,$D$5:$D$24,0)),"")</f>
         <v/>
       </c>
-      <c r="J11" s="14">
+      <c r="J11" s="10">
         <f>IF(I11="",NA(),SUM($I$5:I11)/SUM($I$5:$I$24))</f>
         <v/>
       </c>
-      <c r="K11" s="15">
+      <c r="K11" s="14">
         <f>IF(I11="",NA(),0.8)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="17" t="n"/>
-      <c r="B12" s="17" t="n"/>
-      <c r="C12" s="14">
+      <c r="A12" s="15" t="n"/>
+      <c r="B12" s="15" t="n"/>
+      <c r="C12" s="10">
         <f>IF(OR(B12="",SUM($B$5:$B$24)=0),"",B12/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D12" s="16">
+      <c r="D12" s="11">
         <f>IF(B12="","",RANK(B12,$B$5:$B$24,0)+COUNTIF($B$5:B12,B12)-1)</f>
         <v/>
       </c>
-      <c r="E12" s="17" t="n"/>
+      <c r="E12" s="15" t="n"/>
       <c r="G12" s="5" t="n">
         <v>8</v>
       </c>
@@ -1391,27 +1389,27 @@
         <f>IFERROR(INDEX($B$5:$B$24,MATCH(G12,$D$5:$D$24,0)),"")</f>
         <v/>
       </c>
-      <c r="J12" s="14">
+      <c r="J12" s="10">
         <f>IF(I12="",NA(),SUM($I$5:I12)/SUM($I$5:$I$24))</f>
         <v/>
       </c>
-      <c r="K12" s="15">
+      <c r="K12" s="14">
         <f>IF(I12="",NA(),0.8)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="17" t="n"/>
-      <c r="B13" s="17" t="n"/>
-      <c r="C13" s="14">
+      <c r="A13" s="15" t="n"/>
+      <c r="B13" s="15" t="n"/>
+      <c r="C13" s="10">
         <f>IF(OR(B13="",SUM($B$5:$B$24)=0),"",B13/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D13" s="16">
+      <c r="D13" s="11">
         <f>IF(B13="","",RANK(B13,$B$5:$B$24,0)+COUNTIF($B$5:B13,B13)-1)</f>
         <v/>
       </c>
-      <c r="E13" s="17" t="n"/>
+      <c r="E13" s="15" t="n"/>
       <c r="G13" s="5" t="n">
         <v>9</v>
       </c>
@@ -1423,27 +1421,27 @@
         <f>IFERROR(INDEX($B$5:$B$24,MATCH(G13,$D$5:$D$24,0)),"")</f>
         <v/>
       </c>
-      <c r="J13" s="14">
+      <c r="J13" s="10">
         <f>IF(I13="",NA(),SUM($I$5:I13)/SUM($I$5:$I$24))</f>
         <v/>
       </c>
-      <c r="K13" s="15">
+      <c r="K13" s="14">
         <f>IF(I13="",NA(),0.8)</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="17" t="n"/>
-      <c r="B14" s="17" t="n"/>
-      <c r="C14" s="14">
+      <c r="A14" s="15" t="n"/>
+      <c r="B14" s="15" t="n"/>
+      <c r="C14" s="10">
         <f>IF(OR(B14="",SUM($B$5:$B$24)=0),"",B14/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D14" s="16">
+      <c r="D14" s="11">
         <f>IF(B14="","",RANK(B14,$B$5:$B$24,0)+COUNTIF($B$5:B14,B14)-1)</f>
         <v/>
       </c>
-      <c r="E14" s="17" t="n"/>
+      <c r="E14" s="15" t="n"/>
       <c r="G14" s="5" t="n">
         <v>10</v>
       </c>
@@ -1455,27 +1453,27 @@
         <f>IFERROR(INDEX($B$5:$B$24,MATCH(G14,$D$5:$D$24,0)),"")</f>
         <v/>
       </c>
-      <c r="J14" s="14">
+      <c r="J14" s="10">
         <f>IF(I14="",NA(),SUM($I$5:I14)/SUM($I$5:$I$24))</f>
         <v/>
       </c>
-      <c r="K14" s="15">
+      <c r="K14" s="14">
         <f>IF(I14="",NA(),0.8)</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="17" t="n"/>
-      <c r="B15" s="17" t="n"/>
-      <c r="C15" s="14">
+      <c r="A15" s="15" t="n"/>
+      <c r="B15" s="15" t="n"/>
+      <c r="C15" s="10">
         <f>IF(OR(B15="",SUM($B$5:$B$24)=0),"",B15/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D15" s="16">
+      <c r="D15" s="11">
         <f>IF(B15="","",RANK(B15,$B$5:$B$24,0)+COUNTIF($B$5:B15,B15)-1)</f>
         <v/>
       </c>
-      <c r="E15" s="17" t="n"/>
+      <c r="E15" s="15" t="n"/>
       <c r="G15" s="5" t="n">
         <v>11</v>
       </c>
@@ -1487,27 +1485,27 @@
         <f>IFERROR(INDEX($B$5:$B$24,MATCH(G15,$D$5:$D$24,0)),"")</f>
         <v/>
       </c>
-      <c r="J15" s="14">
+      <c r="J15" s="10">
         <f>IF(I15="",NA(),SUM($I$5:I15)/SUM($I$5:$I$24))</f>
         <v/>
       </c>
-      <c r="K15" s="15">
+      <c r="K15" s="14">
         <f>IF(I15="",NA(),0.8)</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="17" t="n"/>
-      <c r="B16" s="17" t="n"/>
-      <c r="C16" s="14">
+      <c r="A16" s="15" t="n"/>
+      <c r="B16" s="15" t="n"/>
+      <c r="C16" s="10">
         <f>IF(OR(B16="",SUM($B$5:$B$24)=0),"",B16/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D16" s="16">
+      <c r="D16" s="11">
         <f>IF(B16="","",RANK(B16,$B$5:$B$24,0)+COUNTIF($B$5:B16,B16)-1)</f>
         <v/>
       </c>
-      <c r="E16" s="17" t="n"/>
+      <c r="E16" s="15" t="n"/>
       <c r="G16" s="5" t="n">
         <v>12</v>
       </c>
@@ -1519,27 +1517,27 @@
         <f>IFERROR(INDEX($B$5:$B$24,MATCH(G16,$D$5:$D$24,0)),"")</f>
         <v/>
       </c>
-      <c r="J16" s="14">
+      <c r="J16" s="10">
         <f>IF(I16="",NA(),SUM($I$5:I16)/SUM($I$5:$I$24))</f>
         <v/>
       </c>
-      <c r="K16" s="15">
+      <c r="K16" s="14">
         <f>IF(I16="",NA(),0.8)</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="17" t="n"/>
-      <c r="B17" s="17" t="n"/>
-      <c r="C17" s="14">
+      <c r="A17" s="15" t="n"/>
+      <c r="B17" s="15" t="n"/>
+      <c r="C17" s="10">
         <f>IF(OR(B17="",SUM($B$5:$B$24)=0),"",B17/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D17" s="16">
+      <c r="D17" s="11">
         <f>IF(B17="","",RANK(B17,$B$5:$B$24,0)+COUNTIF($B$5:B17,B17)-1)</f>
         <v/>
       </c>
-      <c r="E17" s="17" t="n"/>
+      <c r="E17" s="15" t="n"/>
       <c r="G17" s="5" t="n">
         <v>13</v>
       </c>
@@ -1551,27 +1549,27 @@
         <f>IFERROR(INDEX($B$5:$B$24,MATCH(G17,$D$5:$D$24,0)),"")</f>
         <v/>
       </c>
-      <c r="J17" s="14">
+      <c r="J17" s="10">
         <f>IF(I17="",NA(),SUM($I$5:I17)/SUM($I$5:$I$24))</f>
         <v/>
       </c>
-      <c r="K17" s="15">
+      <c r="K17" s="14">
         <f>IF(I17="",NA(),0.8)</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="17" t="n"/>
-      <c r="B18" s="17" t="n"/>
-      <c r="C18" s="14">
+      <c r="A18" s="15" t="n"/>
+      <c r="B18" s="15" t="n"/>
+      <c r="C18" s="10">
         <f>IF(OR(B18="",SUM($B$5:$B$24)=0),"",B18/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D18" s="16">
+      <c r="D18" s="11">
         <f>IF(B18="","",RANK(B18,$B$5:$B$24,0)+COUNTIF($B$5:B18,B18)-1)</f>
         <v/>
       </c>
-      <c r="E18" s="17" t="n"/>
+      <c r="E18" s="15" t="n"/>
       <c r="G18" s="5" t="n">
         <v>14</v>
       </c>
@@ -1583,27 +1581,27 @@
         <f>IFERROR(INDEX($B$5:$B$24,MATCH(G18,$D$5:$D$24,0)),"")</f>
         <v/>
       </c>
-      <c r="J18" s="14">
+      <c r="J18" s="10">
         <f>IF(I18="",NA(),SUM($I$5:I18)/SUM($I$5:$I$24))</f>
         <v/>
       </c>
-      <c r="K18" s="15">
+      <c r="K18" s="14">
         <f>IF(I18="",NA(),0.8)</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="17" t="n"/>
-      <c r="B19" s="17" t="n"/>
-      <c r="C19" s="14">
+      <c r="A19" s="15" t="n"/>
+      <c r="B19" s="15" t="n"/>
+      <c r="C19" s="10">
         <f>IF(OR(B19="",SUM($B$5:$B$24)=0),"",B19/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D19" s="16">
+      <c r="D19" s="11">
         <f>IF(B19="","",RANK(B19,$B$5:$B$24,0)+COUNTIF($B$5:B19,B19)-1)</f>
         <v/>
       </c>
-      <c r="E19" s="17" t="n"/>
+      <c r="E19" s="15" t="n"/>
       <c r="G19" s="5" t="n">
         <v>15</v>
       </c>
@@ -1615,27 +1613,27 @@
         <f>IFERROR(INDEX($B$5:$B$24,MATCH(G19,$D$5:$D$24,0)),"")</f>
         <v/>
       </c>
-      <c r="J19" s="14">
+      <c r="J19" s="10">
         <f>IF(I19="",NA(),SUM($I$5:I19)/SUM($I$5:$I$24))</f>
         <v/>
       </c>
-      <c r="K19" s="15">
+      <c r="K19" s="14">
         <f>IF(I19="",NA(),0.8)</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="17" t="n"/>
-      <c r="B20" s="17" t="n"/>
-      <c r="C20" s="14">
+      <c r="A20" s="15" t="n"/>
+      <c r="B20" s="15" t="n"/>
+      <c r="C20" s="10">
         <f>IF(OR(B20="",SUM($B$5:$B$24)=0),"",B20/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D20" s="16">
+      <c r="D20" s="11">
         <f>IF(B20="","",RANK(B20,$B$5:$B$24,0)+COUNTIF($B$5:B20,B20)-1)</f>
         <v/>
       </c>
-      <c r="E20" s="17" t="n"/>
+      <c r="E20" s="15" t="n"/>
       <c r="G20" s="5" t="n">
         <v>16</v>
       </c>
@@ -1647,27 +1645,27 @@
         <f>IFERROR(INDEX($B$5:$B$24,MATCH(G20,$D$5:$D$24,0)),"")</f>
         <v/>
       </c>
-      <c r="J20" s="14">
+      <c r="J20" s="10">
         <f>IF(I20="",NA(),SUM($I$5:I20)/SUM($I$5:$I$24))</f>
         <v/>
       </c>
-      <c r="K20" s="15">
+      <c r="K20" s="14">
         <f>IF(I20="",NA(),0.8)</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="17" t="n"/>
-      <c r="B21" s="17" t="n"/>
-      <c r="C21" s="14">
+      <c r="A21" s="15" t="n"/>
+      <c r="B21" s="15" t="n"/>
+      <c r="C21" s="10">
         <f>IF(OR(B21="",SUM($B$5:$B$24)=0),"",B21/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D21" s="16">
+      <c r="D21" s="11">
         <f>IF(B21="","",RANK(B21,$B$5:$B$24,0)+COUNTIF($B$5:B21,B21)-1)</f>
         <v/>
       </c>
-      <c r="E21" s="17" t="n"/>
+      <c r="E21" s="15" t="n"/>
       <c r="G21" s="5" t="n">
         <v>17</v>
       </c>
@@ -1679,27 +1677,27 @@
         <f>IFERROR(INDEX($B$5:$B$24,MATCH(G21,$D$5:$D$24,0)),"")</f>
         <v/>
       </c>
-      <c r="J21" s="14">
+      <c r="J21" s="10">
         <f>IF(I21="",NA(),SUM($I$5:I21)/SUM($I$5:$I$24))</f>
         <v/>
       </c>
-      <c r="K21" s="15">
+      <c r="K21" s="14">
         <f>IF(I21="",NA(),0.8)</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="17" t="n"/>
-      <c r="B22" s="17" t="n"/>
-      <c r="C22" s="14">
+      <c r="A22" s="15" t="n"/>
+      <c r="B22" s="15" t="n"/>
+      <c r="C22" s="10">
         <f>IF(OR(B22="",SUM($B$5:$B$24)=0),"",B22/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D22" s="16">
+      <c r="D22" s="11">
         <f>IF(B22="","",RANK(B22,$B$5:$B$24,0)+COUNTIF($B$5:B22,B22)-1)</f>
         <v/>
       </c>
-      <c r="E22" s="17" t="n"/>
+      <c r="E22" s="15" t="n"/>
       <c r="G22" s="5" t="n">
         <v>18</v>
       </c>
@@ -1711,27 +1709,27 @@
         <f>IFERROR(INDEX($B$5:$B$24,MATCH(G22,$D$5:$D$24,0)),"")</f>
         <v/>
       </c>
-      <c r="J22" s="14">
+      <c r="J22" s="10">
         <f>IF(I22="",NA(),SUM($I$5:I22)/SUM($I$5:$I$24))</f>
         <v/>
       </c>
-      <c r="K22" s="15">
+      <c r="K22" s="14">
         <f>IF(I22="",NA(),0.8)</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="17" t="n"/>
-      <c r="B23" s="17" t="n"/>
-      <c r="C23" s="14">
+      <c r="A23" s="15" t="n"/>
+      <c r="B23" s="15" t="n"/>
+      <c r="C23" s="10">
         <f>IF(OR(B23="",SUM($B$5:$B$24)=0),"",B23/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D23" s="16">
+      <c r="D23" s="11">
         <f>IF(B23="","",RANK(B23,$B$5:$B$24,0)+COUNTIF($B$5:B23,B23)-1)</f>
         <v/>
       </c>
-      <c r="E23" s="17" t="n"/>
+      <c r="E23" s="15" t="n"/>
       <c r="G23" s="5" t="n">
         <v>19</v>
       </c>
@@ -1743,27 +1741,27 @@
         <f>IFERROR(INDEX($B$5:$B$24,MATCH(G23,$D$5:$D$24,0)),"")</f>
         <v/>
       </c>
-      <c r="J23" s="14">
+      <c r="J23" s="10">
         <f>IF(I23="",NA(),SUM($I$5:I23)/SUM($I$5:$I$24))</f>
         <v/>
       </c>
-      <c r="K23" s="15">
+      <c r="K23" s="14">
         <f>IF(I23="",NA(),0.8)</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="17" t="n"/>
-      <c r="B24" s="17" t="n"/>
-      <c r="C24" s="14">
+      <c r="A24" s="15" t="n"/>
+      <c r="B24" s="15" t="n"/>
+      <c r="C24" s="10">
         <f>IF(OR(B24="",SUM($B$5:$B$24)=0),"",B24/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D24" s="16">
+      <c r="D24" s="11">
         <f>IF(B24="","",RANK(B24,$B$5:$B$24,0)+COUNTIF($B$5:B24,B24)-1)</f>
         <v/>
       </c>
-      <c r="E24" s="17" t="n"/>
+      <c r="E24" s="15" t="n"/>
       <c r="G24" s="5" t="n">
         <v>20</v>
       </c>
@@ -1775,17 +1773,17 @@
         <f>IFERROR(INDEX($B$5:$B$24,MATCH(G24,$D$5:$D$24,0)),"")</f>
         <v/>
       </c>
-      <c r="J24" s="14">
+      <c r="J24" s="10">
         <f>IF(I24="",NA(),SUM($I$5:I24)/SUM($I$5:$I$24))</f>
         <v/>
       </c>
-      <c r="K24" s="15">
+      <c r="K24" s="14">
         <f>IF(I24="",NA(),0.8)</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="90" customHeight="1">
-      <c r="A25" s="18" t="inlineStr">
+      <c r="A25" s="16" t="inlineStr">
         <is>
           <t>How to answer the last column, and why it is the one that matters. Open 50 tickets at random from your top category and read them. Count how many are genuinely that category rather than the code an agent picked under time pressure. Answer Yes only if 40 or more of the 50 hold up; below that your Pareto is ranking your data-entry habits and not your problems, and the business case built on it will not survive contact with the process. Row 5 is the worked example: 50 read, 41 held up, so Yes.</t>
         </is>
@@ -1803,7 +1801,7 @@
       <c r="E26" s="7" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="19" t="inlineStr">
+      <c r="A27" s="17" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
@@ -1814,7 +1812,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="19" t="inlineStr">
+      <c r="A28" s="17" t="inlineStr">
         <is>
           <t>Categories</t>
         </is>
@@ -1825,12 +1823,12 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="19" t="inlineStr">
+      <c r="A29" s="17" t="inlineStr">
         <is>
           <t>Share explained by the top three</t>
         </is>
       </c>
-      <c r="C29" s="14">
+      <c r="C29" s="10">
         <f>IFERROR(SUM(I5:I7)/SUM(I5:I24),"")</f>
         <v/>
       </c>
@@ -1927,112 +1925,112 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="19" t="inlineStr">
+      <c r="A6" s="17" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
-      <c r="B6" s="20">
+      <c r="B6" s="18">
         <f>COUNT($B$20:$B$1000)</f>
         <v/>
       </c>
-      <c r="D6" s="21" t="inlineStr">
+      <c r="D6" s="19" t="inlineStr">
         <is>
           <t>How many values you pasted.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="19" t="inlineStr">
+      <c r="A7" s="17" t="inlineStr">
         <is>
           <t>Mean</t>
         </is>
       </c>
-      <c r="B7" s="20">
+      <c r="B7" s="18">
         <f>IFERROR(AVERAGE($B$20:$B$1000),"")</f>
         <v/>
       </c>
-      <c r="D7" s="21" t="inlineStr">
+      <c r="D7" s="19" t="inlineStr">
         <is>
           <t>Dragged upward by the long tail. Rarely the number to quote.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="19" t="inlineStr">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t>Median (p50)</t>
         </is>
       </c>
-      <c r="B8" s="20">
+      <c r="B8" s="18">
         <f>IFERROR(MEDIAN($B$20:$B$1000),"")</f>
         <v/>
       </c>
-      <c r="D8" s="21" t="inlineStr">
+      <c r="D8" s="19" t="inlineStr">
         <is>
           <t>The typical experience. Quote this.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="19" t="inlineStr">
+      <c r="A9" s="17" t="inlineStr">
         <is>
           <t>p90</t>
         </is>
       </c>
-      <c r="B9" s="20">
+      <c r="B9" s="18">
         <f>IFERROR(PERCENTILE($B$20:$B$1000,0.9),"")</f>
         <v/>
       </c>
-      <c r="D9" s="21" t="inlineStr">
+      <c r="D9" s="19" t="inlineStr">
         <is>
           <t>What your worst-served customers get. This is what generates complaints.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="19" t="inlineStr">
+      <c r="A10" s="17" t="inlineStr">
         <is>
           <t>Standard deviation</t>
         </is>
       </c>
-      <c r="B10" s="20">
+      <c r="B10" s="18">
         <f>IFERROR(STDEV($B$20:$B$1000),"")</f>
         <v/>
       </c>
-      <c r="D10" s="21" t="inlineStr">
+      <c r="D10" s="19" t="inlineStr">
         <is>
           <t>Assumes symmetry, so it describes skewed data poorly.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="19" t="inlineStr">
+      <c r="A11" s="17" t="inlineStr">
         <is>
           <t>Interquartile range</t>
         </is>
       </c>
-      <c r="B11" s="20">
+      <c r="B11" s="18">
         <f>IFERROR(QUARTILE($B$20:$B$1000,3)-QUARTILE($B$20:$B$1000,1),"")</f>
         <v/>
       </c>
-      <c r="D11" s="21" t="inlineStr">
+      <c r="D11" s="19" t="inlineStr">
         <is>
           <t>The middle half. A better spread measure for this data.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="19" t="inlineStr">
+      <c r="A12" s="17" t="inlineStr">
         <is>
           <t>Mean ÷ median</t>
         </is>
       </c>
-      <c r="B12" s="20">
+      <c r="B12" s="18">
         <f>IFERROR(AVERAGE($B$20:$B$1000)/MEDIAN($B$20:$B$1000),"")</f>
         <v/>
       </c>
-      <c r="D12" s="21" t="inlineStr">
+      <c r="D12" s="19" t="inlineStr">
         <is>
           <t>Above about 1.2 means meaningful right skew — use non-parametric tests and quote percentiles.</t>
         </is>
@@ -2050,7 +2048,7 @@
       <c r="D14" s="7" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="22">
+      <c r="A15" s="20">
         <f>IF(COUNT($B$20:$B$1000)=0,"Paste your data into column B below.",IF(AVERAGE($B$20:$B$1000)/MEDIAN($B$20:$B$1000)&gt;1.2,"RIGHT-SKEWED — quote the median and p90, and prefer non-parametric tests.","ROUGHLY SYMMETRIC — the mean and a parametric test are defensible."))</f>
         <v/>
       </c>
@@ -2058,12 +2056,12 @@
     <row r="16"/>
     <row r="17"/>
     <row r="18">
-      <c r="A18" s="19" t="inlineStr">
+      <c r="A18" s="17" t="inlineStr">
         <is>
           <t>Your data</t>
         </is>
       </c>
-      <c r="F18" s="19" t="inlineStr">
+      <c r="F18" s="17" t="inlineStr">
         <is>
           <t>What you would quote</t>
         </is>
@@ -2086,7 +2084,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="23" t="n">
+      <c r="B20" s="21" t="n">
         <v>182</v>
       </c>
       <c r="F20" s="5" t="inlineStr">
@@ -2100,7 +2098,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="23" t="n">
+      <c r="B21" s="21" t="n">
         <v>201</v>
       </c>
       <c r="F21" s="5" t="inlineStr">
@@ -2114,192 +2112,192 @@
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="23" t="n">
+      <c r="B22" s="21" t="n">
         <v>214</v>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="23" t="n">
+      <c r="B23" s="21" t="n">
         <v>227</v>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="23" t="n">
+      <c r="B24" s="21" t="n">
         <v>236</v>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="23" t="n">
+      <c r="B25" s="21" t="n">
         <v>241</v>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="23" t="n">
+      <c r="B26" s="21" t="n">
         <v>248</v>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="23" t="n">
+      <c r="B27" s="21" t="n">
         <v>255</v>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="23" t="n">
+      <c r="B28" s="21" t="n">
         <v>259</v>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="23" t="n">
+      <c r="B29" s="21" t="n">
         <v>263</v>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="23" t="n">
+      <c r="B30" s="21" t="n">
         <v>268</v>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="23" t="n">
+      <c r="B31" s="21" t="n">
         <v>272</v>
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="23" t="n">
+      <c r="B32" s="21" t="n">
         <v>277</v>
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="23" t="n">
+      <c r="B33" s="21" t="n">
         <v>281</v>
       </c>
     </row>
     <row r="34">
-      <c r="B34" s="23" t="n">
+      <c r="B34" s="21" t="n">
         <v>286</v>
       </c>
     </row>
     <row r="35">
-      <c r="B35" s="23" t="n">
+      <c r="B35" s="21" t="n">
         <v>292</v>
       </c>
     </row>
     <row r="36">
-      <c r="B36" s="23" t="n">
+      <c r="B36" s="21" t="n">
         <v>298</v>
       </c>
     </row>
     <row r="37">
-      <c r="B37" s="23" t="n">
+      <c r="B37" s="21" t="n">
         <v>305</v>
       </c>
     </row>
     <row r="38">
-      <c r="B38" s="23" t="n">
+      <c r="B38" s="21" t="n">
         <v>311</v>
       </c>
     </row>
     <row r="39">
-      <c r="B39" s="23" t="n">
+      <c r="B39" s="21" t="n">
         <v>318</v>
       </c>
     </row>
     <row r="40">
-      <c r="B40" s="23" t="n">
+      <c r="B40" s="21" t="n">
         <v>326</v>
       </c>
     </row>
     <row r="41">
-      <c r="B41" s="23" t="n">
+      <c r="B41" s="21" t="n">
         <v>335</v>
       </c>
     </row>
     <row r="42">
-      <c r="B42" s="23" t="n">
+      <c r="B42" s="21" t="n">
         <v>346</v>
       </c>
     </row>
     <row r="43">
-      <c r="B43" s="23" t="n">
+      <c r="B43" s="21" t="n">
         <v>358</v>
       </c>
     </row>
     <row r="44">
-      <c r="B44" s="23" t="n">
+      <c r="B44" s="21" t="n">
         <v>372</v>
       </c>
     </row>
     <row r="45">
-      <c r="B45" s="23" t="n">
+      <c r="B45" s="21" t="n">
         <v>389</v>
       </c>
     </row>
     <row r="46">
-      <c r="B46" s="23" t="n">
+      <c r="B46" s="21" t="n">
         <v>408</v>
       </c>
     </row>
     <row r="47">
-      <c r="B47" s="23" t="n">
+      <c r="B47" s="21" t="n">
         <v>431</v>
       </c>
     </row>
     <row r="48">
-      <c r="B48" s="23" t="n">
+      <c r="B48" s="21" t="n">
         <v>459</v>
       </c>
     </row>
     <row r="49">
-      <c r="B49" s="23" t="n">
+      <c r="B49" s="21" t="n">
         <v>494</v>
       </c>
     </row>
     <row r="50">
-      <c r="B50" s="23" t="n">
+      <c r="B50" s="21" t="n">
         <v>538</v>
       </c>
     </row>
     <row r="51">
-      <c r="B51" s="23" t="n">
+      <c r="B51" s="21" t="n">
         <v>594</v>
       </c>
     </row>
     <row r="52">
-      <c r="B52" s="23" t="n">
+      <c r="B52" s="21" t="n">
         <v>668</v>
       </c>
     </row>
     <row r="53">
-      <c r="B53" s="23" t="n">
+      <c r="B53" s="21" t="n">
         <v>771</v>
       </c>
     </row>
     <row r="54">
-      <c r="B54" s="23" t="n">
+      <c r="B54" s="21" t="n">
         <v>918</v>
       </c>
     </row>
     <row r="55">
-      <c r="B55" s="23" t="n">
+      <c r="B55" s="21" t="n">
         <v>1140</v>
       </c>
     </row>
     <row r="56">
-      <c r="B56" s="23" t="n">
+      <c r="B56" s="21" t="n">
         <v>1502</v>
       </c>
     </row>
     <row r="57">
-      <c r="B57" s="23" t="n">
+      <c r="B57" s="21" t="n">
         <v>2160</v>
       </c>
     </row>
     <row r="58">
-      <c r="B58" s="23" t="n">
+      <c r="B58" s="21" t="n">
         <v>3480</v>
       </c>
     </row>
     <row r="59">
-      <c r="B59" s="23" t="n">
+      <c r="B59" s="21" t="n">
         <v>5220</v>
       </c>
     </row>

--- a/templates/25-pareto-and-distribution.xlsx
+++ b/templates/25-pareto-and-distribution.xlsx
@@ -111,7 +111,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -122,8 +122,9 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -137,6 +138,8 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1045,87 +1048,83 @@
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="26" customHeight="1">
       <c r="G3" s="6" t="inlineStr">
         <is>
           <t>RANKED — this is what the chart plots. Type above in any order; this sorts itself.</t>
         </is>
       </c>
-      <c r="H3" s="7" t="n"/>
-      <c r="I3" s="7" t="n"/>
-      <c r="J3" s="7" t="n"/>
-      <c r="K3" s="7" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>Share</t>
         </is>
       </c>
-      <c r="D4" s="8" t="inlineStr">
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>Rank</t>
         </is>
       </c>
-      <c r="E4" s="8" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>Validated by reading tickets?</t>
         </is>
       </c>
-      <c r="G4" s="8" t="inlineStr">
+      <c r="G4" s="7" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="H4" s="8" t="inlineStr">
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="I4" s="8" t="inlineStr">
+      <c r="I4" s="7" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
-      <c r="J4" s="8" t="inlineStr">
+      <c r="J4" s="7" t="inlineStr">
         <is>
           <t>Cumulative</t>
         </is>
       </c>
-      <c r="K4" s="8" t="inlineStr">
+      <c r="K4" s="7" t="inlineStr">
         <is>
           <t>80% line</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>Adjustment not posted at closure</t>
         </is>
       </c>
-      <c r="B5" s="9" t="n">
+      <c r="B5" s="8" t="n">
         <v>412</v>
       </c>
-      <c r="C5" s="10">
+      <c r="C5" s="9">
         <f>IF(OR(B5="",SUM($B$5:$B$24)=0),"",B5/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D5" s="11">
+      <c r="D5" s="10">
         <f>IF(B5="","",RANK(B5,$B$5:$B$24,0)+COUNTIF($B$5:B5,B5)-1)</f>
         <v/>
       </c>
-      <c r="E5" s="9" t="inlineStr">
+      <c r="E5" s="8" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -1133,702 +1132,702 @@
       <c r="G5" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="H5" s="12">
+      <c r="H5" s="11">
         <f>IFERROR(INDEX($A$5:$A$24,MATCH(G5,$D$5:$D$24,0)),"")</f>
         <v/>
       </c>
-      <c r="I5" s="13">
+      <c r="I5" s="12">
         <f>IFERROR(INDEX($B$5:$B$24,MATCH(G5,$D$5:$D$24,0)),"")</f>
         <v/>
       </c>
-      <c r="J5" s="10">
+      <c r="J5" s="9">
         <f>IF(I5="",NA(),SUM($I$5:I5)/SUM($I$5:$I$24))</f>
         <v/>
       </c>
-      <c r="K5" s="14">
+      <c r="K5" s="13">
         <f>IF(I5="",NA(),0.8)</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Wrong plan applied</t>
         </is>
       </c>
-      <c r="B6" s="9" t="n">
+      <c r="B6" s="8" t="n">
         <v>233</v>
       </c>
-      <c r="C6" s="10">
+      <c r="C6" s="9">
         <f>IF(OR(B6="",SUM($B$5:$B$24)=0),"",B6/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D6" s="11">
+      <c r="D6" s="10">
         <f>IF(B6="","",RANK(B6,$B$5:$B$24,0)+COUNTIF($B$5:B6,B6)-1)</f>
         <v/>
       </c>
-      <c r="E6" s="15" t="n"/>
+      <c r="E6" s="14" t="n"/>
       <c r="G6" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="H6" s="12">
+      <c r="H6" s="11">
         <f>IFERROR(INDEX($A$5:$A$24,MATCH(G6,$D$5:$D$24,0)),"")</f>
         <v/>
       </c>
-      <c r="I6" s="13">
+      <c r="I6" s="12">
         <f>IFERROR(INDEX($B$5:$B$24,MATCH(G6,$D$5:$D$24,0)),"")</f>
         <v/>
       </c>
-      <c r="J6" s="10">
+      <c r="J6" s="9">
         <f>IF(I6="",NA(),SUM($I$5:I6)/SUM($I$5:$I$24))</f>
         <v/>
       </c>
-      <c r="K6" s="14">
+      <c r="K6" s="13">
         <f>IF(I6="",NA(),0.8)</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Duplicate charge</t>
         </is>
       </c>
-      <c r="B7" s="9" t="n">
+      <c r="B7" s="8" t="n">
         <v>151</v>
       </c>
-      <c r="C7" s="10">
+      <c r="C7" s="9">
         <f>IF(OR(B7="",SUM($B$5:$B$24)=0),"",B7/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D7" s="11">
+      <c r="D7" s="10">
         <f>IF(B7="","",RANK(B7,$B$5:$B$24,0)+COUNTIF($B$5:B7,B7)-1)</f>
         <v/>
       </c>
-      <c r="E7" s="15" t="n"/>
+      <c r="E7" s="14" t="n"/>
       <c r="G7" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="H7" s="12">
+      <c r="H7" s="11">
         <f>IFERROR(INDEX($A$5:$A$24,MATCH(G7,$D$5:$D$24,0)),"")</f>
         <v/>
       </c>
-      <c r="I7" s="13">
+      <c r="I7" s="12">
         <f>IFERROR(INDEX($B$5:$B$24,MATCH(G7,$D$5:$D$24,0)),"")</f>
         <v/>
       </c>
-      <c r="J7" s="10">
+      <c r="J7" s="9">
         <f>IF(I7="",NA(),SUM($I$5:I7)/SUM($I$5:$I$24))</f>
         <v/>
       </c>
-      <c r="K7" s="14">
+      <c r="K7" s="13">
         <f>IF(I7="",NA(),0.8)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>Proration misunderstood</t>
         </is>
       </c>
-      <c r="B8" s="9" t="n">
+      <c r="B8" s="8" t="n">
         <v>96</v>
       </c>
-      <c r="C8" s="10">
+      <c r="C8" s="9">
         <f>IF(OR(B8="",SUM($B$5:$B$24)=0),"",B8/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D8" s="11">
+      <c r="D8" s="10">
         <f>IF(B8="","",RANK(B8,$B$5:$B$24,0)+COUNTIF($B$5:B8,B8)-1)</f>
         <v/>
       </c>
-      <c r="E8" s="15" t="n"/>
+      <c r="E8" s="14" t="n"/>
       <c r="G8" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="H8" s="12">
+      <c r="H8" s="11">
         <f>IFERROR(INDEX($A$5:$A$24,MATCH(G8,$D$5:$D$24,0)),"")</f>
         <v/>
       </c>
-      <c r="I8" s="13">
+      <c r="I8" s="12">
         <f>IFERROR(INDEX($B$5:$B$24,MATCH(G8,$D$5:$D$24,0)),"")</f>
         <v/>
       </c>
-      <c r="J8" s="10">
+      <c r="J8" s="9">
         <f>IF(I8="",NA(),SUM($I$5:I8)/SUM($I$5:$I$24))</f>
         <v/>
       </c>
-      <c r="K8" s="14">
+      <c r="K8" s="13">
         <f>IF(I8="",NA(),0.8)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>Refund timing</t>
         </is>
       </c>
-      <c r="B9" s="9" t="n">
+      <c r="B9" s="8" t="n">
         <v>74</v>
       </c>
-      <c r="C9" s="10">
+      <c r="C9" s="9">
         <f>IF(OR(B9="",SUM($B$5:$B$24)=0),"",B9/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D9" s="11">
+      <c r="D9" s="10">
         <f>IF(B9="","",RANK(B9,$B$5:$B$24,0)+COUNTIF($B$5:B9,B9)-1)</f>
         <v/>
       </c>
-      <c r="E9" s="15" t="n"/>
+      <c r="E9" s="14" t="n"/>
       <c r="G9" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="H9" s="12">
+      <c r="H9" s="11">
         <f>IFERROR(INDEX($A$5:$A$24,MATCH(G9,$D$5:$D$24,0)),"")</f>
         <v/>
       </c>
-      <c r="I9" s="13">
+      <c r="I9" s="12">
         <f>IFERROR(INDEX($B$5:$B$24,MATCH(G9,$D$5:$D$24,0)),"")</f>
         <v/>
       </c>
-      <c r="J9" s="10">
+      <c r="J9" s="9">
         <f>IF(I9="",NA(),SUM($I$5:I9)/SUM($I$5:$I$24))</f>
         <v/>
       </c>
-      <c r="K9" s="14">
+      <c r="K9" s="13">
         <f>IF(I9="",NA(),0.8)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="n"/>
-      <c r="B10" s="15" t="n"/>
-      <c r="C10" s="10">
+      <c r="A10" s="14" t="n"/>
+      <c r="B10" s="14" t="n"/>
+      <c r="C10" s="9">
         <f>IF(OR(B10="",SUM($B$5:$B$24)=0),"",B10/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D10" s="11">
+      <c r="D10" s="10">
         <f>IF(B10="","",RANK(B10,$B$5:$B$24,0)+COUNTIF($B$5:B10,B10)-1)</f>
         <v/>
       </c>
-      <c r="E10" s="15" t="n"/>
+      <c r="E10" s="14" t="n"/>
       <c r="G10" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="H10" s="12">
+      <c r="H10" s="11">
         <f>IFERROR(INDEX($A$5:$A$24,MATCH(G10,$D$5:$D$24,0)),"")</f>
         <v/>
       </c>
-      <c r="I10" s="13">
+      <c r="I10" s="12">
         <f>IFERROR(INDEX($B$5:$B$24,MATCH(G10,$D$5:$D$24,0)),"")</f>
         <v/>
       </c>
-      <c r="J10" s="10">
+      <c r="J10" s="9">
         <f>IF(I10="",NA(),SUM($I$5:I10)/SUM($I$5:$I$24))</f>
         <v/>
       </c>
-      <c r="K10" s="14">
+      <c r="K10" s="13">
         <f>IF(I10="",NA(),0.8)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="n"/>
-      <c r="B11" s="15" t="n"/>
-      <c r="C11" s="10">
+      <c r="A11" s="14" t="n"/>
+      <c r="B11" s="14" t="n"/>
+      <c r="C11" s="9">
         <f>IF(OR(B11="",SUM($B$5:$B$24)=0),"",B11/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D11" s="11">
+      <c r="D11" s="10">
         <f>IF(B11="","",RANK(B11,$B$5:$B$24,0)+COUNTIF($B$5:B11,B11)-1)</f>
         <v/>
       </c>
-      <c r="E11" s="15" t="n"/>
+      <c r="E11" s="14" t="n"/>
       <c r="G11" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="H11" s="12">
+      <c r="H11" s="11">
         <f>IFERROR(INDEX($A$5:$A$24,MATCH(G11,$D$5:$D$24,0)),"")</f>
         <v/>
       </c>
-      <c r="I11" s="13">
+      <c r="I11" s="12">
         <f>IFERROR(INDEX($B$5:$B$24,MATCH(G11,$D$5:$D$24,0)),"")</f>
         <v/>
       </c>
-      <c r="J11" s="10">
+      <c r="J11" s="9">
         <f>IF(I11="",NA(),SUM($I$5:I11)/SUM($I$5:$I$24))</f>
         <v/>
       </c>
-      <c r="K11" s="14">
+      <c r="K11" s="13">
         <f>IF(I11="",NA(),0.8)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="n"/>
-      <c r="B12" s="15" t="n"/>
-      <c r="C12" s="10">
+      <c r="A12" s="14" t="n"/>
+      <c r="B12" s="14" t="n"/>
+      <c r="C12" s="9">
         <f>IF(OR(B12="",SUM($B$5:$B$24)=0),"",B12/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D12" s="11">
+      <c r="D12" s="10">
         <f>IF(B12="","",RANK(B12,$B$5:$B$24,0)+COUNTIF($B$5:B12,B12)-1)</f>
         <v/>
       </c>
-      <c r="E12" s="15" t="n"/>
+      <c r="E12" s="14" t="n"/>
       <c r="G12" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="H12" s="12">
+      <c r="H12" s="11">
         <f>IFERROR(INDEX($A$5:$A$24,MATCH(G12,$D$5:$D$24,0)),"")</f>
         <v/>
       </c>
-      <c r="I12" s="13">
+      <c r="I12" s="12">
         <f>IFERROR(INDEX($B$5:$B$24,MATCH(G12,$D$5:$D$24,0)),"")</f>
         <v/>
       </c>
-      <c r="J12" s="10">
+      <c r="J12" s="9">
         <f>IF(I12="",NA(),SUM($I$5:I12)/SUM($I$5:$I$24))</f>
         <v/>
       </c>
-      <c r="K12" s="14">
+      <c r="K12" s="13">
         <f>IF(I12="",NA(),0.8)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="n"/>
-      <c r="B13" s="15" t="n"/>
-      <c r="C13" s="10">
+      <c r="A13" s="14" t="n"/>
+      <c r="B13" s="14" t="n"/>
+      <c r="C13" s="9">
         <f>IF(OR(B13="",SUM($B$5:$B$24)=0),"",B13/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D13" s="11">
+      <c r="D13" s="10">
         <f>IF(B13="","",RANK(B13,$B$5:$B$24,0)+COUNTIF($B$5:B13,B13)-1)</f>
         <v/>
       </c>
-      <c r="E13" s="15" t="n"/>
+      <c r="E13" s="14" t="n"/>
       <c r="G13" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="H13" s="12">
+      <c r="H13" s="11">
         <f>IFERROR(INDEX($A$5:$A$24,MATCH(G13,$D$5:$D$24,0)),"")</f>
         <v/>
       </c>
-      <c r="I13" s="13">
+      <c r="I13" s="12">
         <f>IFERROR(INDEX($B$5:$B$24,MATCH(G13,$D$5:$D$24,0)),"")</f>
         <v/>
       </c>
-      <c r="J13" s="10">
+      <c r="J13" s="9">
         <f>IF(I13="",NA(),SUM($I$5:I13)/SUM($I$5:$I$24))</f>
         <v/>
       </c>
-      <c r="K13" s="14">
+      <c r="K13" s="13">
         <f>IF(I13="",NA(),0.8)</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="n"/>
-      <c r="B14" s="15" t="n"/>
-      <c r="C14" s="10">
+      <c r="A14" s="14" t="n"/>
+      <c r="B14" s="14" t="n"/>
+      <c r="C14" s="9">
         <f>IF(OR(B14="",SUM($B$5:$B$24)=0),"",B14/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D14" s="11">
+      <c r="D14" s="10">
         <f>IF(B14="","",RANK(B14,$B$5:$B$24,0)+COUNTIF($B$5:B14,B14)-1)</f>
         <v/>
       </c>
-      <c r="E14" s="15" t="n"/>
+      <c r="E14" s="14" t="n"/>
       <c r="G14" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="H14" s="12">
+      <c r="H14" s="11">
         <f>IFERROR(INDEX($A$5:$A$24,MATCH(G14,$D$5:$D$24,0)),"")</f>
         <v/>
       </c>
-      <c r="I14" s="13">
+      <c r="I14" s="12">
         <f>IFERROR(INDEX($B$5:$B$24,MATCH(G14,$D$5:$D$24,0)),"")</f>
         <v/>
       </c>
-      <c r="J14" s="10">
+      <c r="J14" s="9">
         <f>IF(I14="",NA(),SUM($I$5:I14)/SUM($I$5:$I$24))</f>
         <v/>
       </c>
-      <c r="K14" s="14">
+      <c r="K14" s="13">
         <f>IF(I14="",NA(),0.8)</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="15" t="n"/>
-      <c r="B15" s="15" t="n"/>
-      <c r="C15" s="10">
+      <c r="A15" s="14" t="n"/>
+      <c r="B15" s="14" t="n"/>
+      <c r="C15" s="9">
         <f>IF(OR(B15="",SUM($B$5:$B$24)=0),"",B15/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D15" s="11">
+      <c r="D15" s="10">
         <f>IF(B15="","",RANK(B15,$B$5:$B$24,0)+COUNTIF($B$5:B15,B15)-1)</f>
         <v/>
       </c>
-      <c r="E15" s="15" t="n"/>
+      <c r="E15" s="14" t="n"/>
       <c r="G15" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="H15" s="12">
+      <c r="H15" s="11">
         <f>IFERROR(INDEX($A$5:$A$24,MATCH(G15,$D$5:$D$24,0)),"")</f>
         <v/>
       </c>
-      <c r="I15" s="13">
+      <c r="I15" s="12">
         <f>IFERROR(INDEX($B$5:$B$24,MATCH(G15,$D$5:$D$24,0)),"")</f>
         <v/>
       </c>
-      <c r="J15" s="10">
+      <c r="J15" s="9">
         <f>IF(I15="",NA(),SUM($I$5:I15)/SUM($I$5:$I$24))</f>
         <v/>
       </c>
-      <c r="K15" s="14">
+      <c r="K15" s="13">
         <f>IF(I15="",NA(),0.8)</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="15" t="n"/>
-      <c r="B16" s="15" t="n"/>
-      <c r="C16" s="10">
+      <c r="A16" s="14" t="n"/>
+      <c r="B16" s="14" t="n"/>
+      <c r="C16" s="9">
         <f>IF(OR(B16="",SUM($B$5:$B$24)=0),"",B16/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D16" s="11">
+      <c r="D16" s="10">
         <f>IF(B16="","",RANK(B16,$B$5:$B$24,0)+COUNTIF($B$5:B16,B16)-1)</f>
         <v/>
       </c>
-      <c r="E16" s="15" t="n"/>
+      <c r="E16" s="14" t="n"/>
       <c r="G16" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="H16" s="12">
+      <c r="H16" s="11">
         <f>IFERROR(INDEX($A$5:$A$24,MATCH(G16,$D$5:$D$24,0)),"")</f>
         <v/>
       </c>
-      <c r="I16" s="13">
+      <c r="I16" s="12">
         <f>IFERROR(INDEX($B$5:$B$24,MATCH(G16,$D$5:$D$24,0)),"")</f>
         <v/>
       </c>
-      <c r="J16" s="10">
+      <c r="J16" s="9">
         <f>IF(I16="",NA(),SUM($I$5:I16)/SUM($I$5:$I$24))</f>
         <v/>
       </c>
-      <c r="K16" s="14">
+      <c r="K16" s="13">
         <f>IF(I16="",NA(),0.8)</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="n"/>
-      <c r="B17" s="15" t="n"/>
-      <c r="C17" s="10">
+      <c r="A17" s="14" t="n"/>
+      <c r="B17" s="14" t="n"/>
+      <c r="C17" s="9">
         <f>IF(OR(B17="",SUM($B$5:$B$24)=0),"",B17/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D17" s="11">
+      <c r="D17" s="10">
         <f>IF(B17="","",RANK(B17,$B$5:$B$24,0)+COUNTIF($B$5:B17,B17)-1)</f>
         <v/>
       </c>
-      <c r="E17" s="15" t="n"/>
+      <c r="E17" s="14" t="n"/>
       <c r="G17" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="H17" s="12">
+      <c r="H17" s="11">
         <f>IFERROR(INDEX($A$5:$A$24,MATCH(G17,$D$5:$D$24,0)),"")</f>
         <v/>
       </c>
-      <c r="I17" s="13">
+      <c r="I17" s="12">
         <f>IFERROR(INDEX($B$5:$B$24,MATCH(G17,$D$5:$D$24,0)),"")</f>
         <v/>
       </c>
-      <c r="J17" s="10">
+      <c r="J17" s="9">
         <f>IF(I17="",NA(),SUM($I$5:I17)/SUM($I$5:$I$24))</f>
         <v/>
       </c>
-      <c r="K17" s="14">
+      <c r="K17" s="13">
         <f>IF(I17="",NA(),0.8)</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="n"/>
-      <c r="B18" s="15" t="n"/>
-      <c r="C18" s="10">
+      <c r="A18" s="14" t="n"/>
+      <c r="B18" s="14" t="n"/>
+      <c r="C18" s="9">
         <f>IF(OR(B18="",SUM($B$5:$B$24)=0),"",B18/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D18" s="11">
+      <c r="D18" s="10">
         <f>IF(B18="","",RANK(B18,$B$5:$B$24,0)+COUNTIF($B$5:B18,B18)-1)</f>
         <v/>
       </c>
-      <c r="E18" s="15" t="n"/>
+      <c r="E18" s="14" t="n"/>
       <c r="G18" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="H18" s="12">
+      <c r="H18" s="11">
         <f>IFERROR(INDEX($A$5:$A$24,MATCH(G18,$D$5:$D$24,0)),"")</f>
         <v/>
       </c>
-      <c r="I18" s="13">
+      <c r="I18" s="12">
         <f>IFERROR(INDEX($B$5:$B$24,MATCH(G18,$D$5:$D$24,0)),"")</f>
         <v/>
       </c>
-      <c r="J18" s="10">
+      <c r="J18" s="9">
         <f>IF(I18="",NA(),SUM($I$5:I18)/SUM($I$5:$I$24))</f>
         <v/>
       </c>
-      <c r="K18" s="14">
+      <c r="K18" s="13">
         <f>IF(I18="",NA(),0.8)</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="n"/>
-      <c r="B19" s="15" t="n"/>
-      <c r="C19" s="10">
+      <c r="A19" s="14" t="n"/>
+      <c r="B19" s="14" t="n"/>
+      <c r="C19" s="9">
         <f>IF(OR(B19="",SUM($B$5:$B$24)=0),"",B19/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D19" s="11">
+      <c r="D19" s="10">
         <f>IF(B19="","",RANK(B19,$B$5:$B$24,0)+COUNTIF($B$5:B19,B19)-1)</f>
         <v/>
       </c>
-      <c r="E19" s="15" t="n"/>
+      <c r="E19" s="14" t="n"/>
       <c r="G19" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="H19" s="12">
+      <c r="H19" s="11">
         <f>IFERROR(INDEX($A$5:$A$24,MATCH(G19,$D$5:$D$24,0)),"")</f>
         <v/>
       </c>
-      <c r="I19" s="13">
+      <c r="I19" s="12">
         <f>IFERROR(INDEX($B$5:$B$24,MATCH(G19,$D$5:$D$24,0)),"")</f>
         <v/>
       </c>
-      <c r="J19" s="10">
+      <c r="J19" s="9">
         <f>IF(I19="",NA(),SUM($I$5:I19)/SUM($I$5:$I$24))</f>
         <v/>
       </c>
-      <c r="K19" s="14">
+      <c r="K19" s="13">
         <f>IF(I19="",NA(),0.8)</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="15" t="n"/>
-      <c r="B20" s="15" t="n"/>
-      <c r="C20" s="10">
+      <c r="A20" s="14" t="n"/>
+      <c r="B20" s="14" t="n"/>
+      <c r="C20" s="9">
         <f>IF(OR(B20="",SUM($B$5:$B$24)=0),"",B20/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D20" s="11">
+      <c r="D20" s="10">
         <f>IF(B20="","",RANK(B20,$B$5:$B$24,0)+COUNTIF($B$5:B20,B20)-1)</f>
         <v/>
       </c>
-      <c r="E20" s="15" t="n"/>
+      <c r="E20" s="14" t="n"/>
       <c r="G20" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="H20" s="12">
+      <c r="H20" s="11">
         <f>IFERROR(INDEX($A$5:$A$24,MATCH(G20,$D$5:$D$24,0)),"")</f>
         <v/>
       </c>
-      <c r="I20" s="13">
+      <c r="I20" s="12">
         <f>IFERROR(INDEX($B$5:$B$24,MATCH(G20,$D$5:$D$24,0)),"")</f>
         <v/>
       </c>
-      <c r="J20" s="10">
+      <c r="J20" s="9">
         <f>IF(I20="",NA(),SUM($I$5:I20)/SUM($I$5:$I$24))</f>
         <v/>
       </c>
-      <c r="K20" s="14">
+      <c r="K20" s="13">
         <f>IF(I20="",NA(),0.8)</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="15" t="n"/>
-      <c r="B21" s="15" t="n"/>
-      <c r="C21" s="10">
+      <c r="A21" s="14" t="n"/>
+      <c r="B21" s="14" t="n"/>
+      <c r="C21" s="9">
         <f>IF(OR(B21="",SUM($B$5:$B$24)=0),"",B21/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D21" s="11">
+      <c r="D21" s="10">
         <f>IF(B21="","",RANK(B21,$B$5:$B$24,0)+COUNTIF($B$5:B21,B21)-1)</f>
         <v/>
       </c>
-      <c r="E21" s="15" t="n"/>
+      <c r="E21" s="14" t="n"/>
       <c r="G21" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="H21" s="12">
+      <c r="H21" s="11">
         <f>IFERROR(INDEX($A$5:$A$24,MATCH(G21,$D$5:$D$24,0)),"")</f>
         <v/>
       </c>
-      <c r="I21" s="13">
+      <c r="I21" s="12">
         <f>IFERROR(INDEX($B$5:$B$24,MATCH(G21,$D$5:$D$24,0)),"")</f>
         <v/>
       </c>
-      <c r="J21" s="10">
+      <c r="J21" s="9">
         <f>IF(I21="",NA(),SUM($I$5:I21)/SUM($I$5:$I$24))</f>
         <v/>
       </c>
-      <c r="K21" s="14">
+      <c r="K21" s="13">
         <f>IF(I21="",NA(),0.8)</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="15" t="n"/>
-      <c r="B22" s="15" t="n"/>
-      <c r="C22" s="10">
+      <c r="A22" s="14" t="n"/>
+      <c r="B22" s="14" t="n"/>
+      <c r="C22" s="9">
         <f>IF(OR(B22="",SUM($B$5:$B$24)=0),"",B22/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D22" s="11">
+      <c r="D22" s="10">
         <f>IF(B22="","",RANK(B22,$B$5:$B$24,0)+COUNTIF($B$5:B22,B22)-1)</f>
         <v/>
       </c>
-      <c r="E22" s="15" t="n"/>
+      <c r="E22" s="14" t="n"/>
       <c r="G22" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="H22" s="12">
+      <c r="H22" s="11">
         <f>IFERROR(INDEX($A$5:$A$24,MATCH(G22,$D$5:$D$24,0)),"")</f>
         <v/>
       </c>
-      <c r="I22" s="13">
+      <c r="I22" s="12">
         <f>IFERROR(INDEX($B$5:$B$24,MATCH(G22,$D$5:$D$24,0)),"")</f>
         <v/>
       </c>
-      <c r="J22" s="10">
+      <c r="J22" s="9">
         <f>IF(I22="",NA(),SUM($I$5:I22)/SUM($I$5:$I$24))</f>
         <v/>
       </c>
-      <c r="K22" s="14">
+      <c r="K22" s="13">
         <f>IF(I22="",NA(),0.8)</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="15" t="n"/>
-      <c r="B23" s="15" t="n"/>
-      <c r="C23" s="10">
+      <c r="A23" s="14" t="n"/>
+      <c r="B23" s="14" t="n"/>
+      <c r="C23" s="9">
         <f>IF(OR(B23="",SUM($B$5:$B$24)=0),"",B23/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D23" s="11">
+      <c r="D23" s="10">
         <f>IF(B23="","",RANK(B23,$B$5:$B$24,0)+COUNTIF($B$5:B23,B23)-1)</f>
         <v/>
       </c>
-      <c r="E23" s="15" t="n"/>
+      <c r="E23" s="14" t="n"/>
       <c r="G23" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="H23" s="12">
+      <c r="H23" s="11">
         <f>IFERROR(INDEX($A$5:$A$24,MATCH(G23,$D$5:$D$24,0)),"")</f>
         <v/>
       </c>
-      <c r="I23" s="13">
+      <c r="I23" s="12">
         <f>IFERROR(INDEX($B$5:$B$24,MATCH(G23,$D$5:$D$24,0)),"")</f>
         <v/>
       </c>
-      <c r="J23" s="10">
+      <c r="J23" s="9">
         <f>IF(I23="",NA(),SUM($I$5:I23)/SUM($I$5:$I$24))</f>
         <v/>
       </c>
-      <c r="K23" s="14">
+      <c r="K23" s="13">
         <f>IF(I23="",NA(),0.8)</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="15" t="n"/>
-      <c r="B24" s="15" t="n"/>
-      <c r="C24" s="10">
+      <c r="A24" s="14" t="n"/>
+      <c r="B24" s="14" t="n"/>
+      <c r="C24" s="9">
         <f>IF(OR(B24="",SUM($B$5:$B$24)=0),"",B24/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D24" s="11">
+      <c r="D24" s="10">
         <f>IF(B24="","",RANK(B24,$B$5:$B$24,0)+COUNTIF($B$5:B24,B24)-1)</f>
         <v/>
       </c>
-      <c r="E24" s="15" t="n"/>
+      <c r="E24" s="14" t="n"/>
       <c r="G24" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="H24" s="12">
+      <c r="H24" s="11">
         <f>IFERROR(INDEX($A$5:$A$24,MATCH(G24,$D$5:$D$24,0)),"")</f>
         <v/>
       </c>
-      <c r="I24" s="13">
+      <c r="I24" s="12">
         <f>IFERROR(INDEX($B$5:$B$24,MATCH(G24,$D$5:$D$24,0)),"")</f>
         <v/>
       </c>
-      <c r="J24" s="10">
+      <c r="J24" s="9">
         <f>IF(I24="",NA(),SUM($I$5:I24)/SUM($I$5:$I$24))</f>
         <v/>
       </c>
-      <c r="K24" s="14">
+      <c r="K24" s="13">
         <f>IF(I24="",NA(),0.8)</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="90" customHeight="1">
-      <c r="A25" s="16" t="inlineStr">
+      <c r="A25" s="15" t="inlineStr">
         <is>
           <t>How to answer the last column, and why it is the one that matters. Open 50 tickets at random from your top category and read them. Count how many are genuinely that category rather than the code an agent picked under time pressure. Answer Yes only if 40 or more of the 50 hold up; below that your Pareto is ranking your data-entry habits and not your problems, and the business case built on it will not survive contact with the process. Row 5 is the worked example: 50 read, 41 held up, so Yes.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="6" t="inlineStr">
+      <c r="A26" s="16" t="inlineStr">
         <is>
           <t>SUMMARY</t>
         </is>
       </c>
-      <c r="B26" s="7" t="n"/>
-      <c r="C26" s="7" t="n"/>
-      <c r="D26" s="7" t="n"/>
-      <c r="E26" s="7" t="n"/>
+      <c r="B26" s="17" t="n"/>
+      <c r="C26" s="17" t="n"/>
+      <c r="D26" s="17" t="n"/>
+      <c r="E26" s="17" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="17" t="inlineStr">
+      <c r="A27" s="18" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C27" s="12">
+      <c r="C27" s="11">
         <f>SUM(B5:B24)</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="17" t="inlineStr">
+      <c r="A28" s="18" t="inlineStr">
         <is>
           <t>Categories</t>
         </is>
       </c>
-      <c r="C28" s="12">
+      <c r="C28" s="11">
         <f>COUNTA(A5:A24)</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="17" t="inlineStr">
+      <c r="A29" s="18" t="inlineStr">
         <is>
           <t>Share explained by the top three</t>
         </is>
       </c>
-      <c r="C29" s="10">
+      <c r="C29" s="9">
         <f>IFERROR(SUM(I5:I7)/SUM(I5:I24),"")</f>
         <v/>
       </c>
@@ -1842,7 +1841,8 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
+    <mergeCell ref="G3:K3"/>
     <mergeCell ref="A26:E26"/>
     <mergeCell ref="A29:B29"/>
     <mergeCell ref="A2:E2"/>
@@ -1907,130 +1907,130 @@
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Statistic</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr"/>
-      <c r="D5" s="8" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr"/>
+      <c r="D5" s="7" t="inlineStr">
         <is>
           <t>What it tells you</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="17" t="inlineStr">
+      <c r="A6" s="18" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
-      <c r="B6" s="18">
+      <c r="B6" s="19">
         <f>COUNT($B$20:$B$1000)</f>
         <v/>
       </c>
-      <c r="D6" s="19" t="inlineStr">
+      <c r="D6" s="20" t="inlineStr">
         <is>
           <t>How many values you pasted.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="inlineStr">
+      <c r="A7" s="18" t="inlineStr">
         <is>
           <t>Mean</t>
         </is>
       </c>
-      <c r="B7" s="18">
+      <c r="B7" s="19">
         <f>IFERROR(AVERAGE($B$20:$B$1000),"")</f>
         <v/>
       </c>
-      <c r="D7" s="19" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>Dragged upward by the long tail. Rarely the number to quote.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="A8" s="18" t="inlineStr">
         <is>
           <t>Median (p50)</t>
         </is>
       </c>
-      <c r="B8" s="18">
+      <c r="B8" s="19">
         <f>IFERROR(MEDIAN($B$20:$B$1000),"")</f>
         <v/>
       </c>
-      <c r="D8" s="19" t="inlineStr">
+      <c r="D8" s="20" t="inlineStr">
         <is>
           <t>The typical experience. Quote this.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="inlineStr">
+      <c r="A9" s="18" t="inlineStr">
         <is>
           <t>p90</t>
         </is>
       </c>
-      <c r="B9" s="18">
+      <c r="B9" s="19">
         <f>IFERROR(PERCENTILE($B$20:$B$1000,0.9),"")</f>
         <v/>
       </c>
-      <c r="D9" s="19" t="inlineStr">
+      <c r="D9" s="20" t="inlineStr">
         <is>
           <t>What your worst-served customers get. This is what generates complaints.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="17" t="inlineStr">
+      <c r="A10" s="18" t="inlineStr">
         <is>
           <t>Standard deviation</t>
         </is>
       </c>
-      <c r="B10" s="18">
+      <c r="B10" s="19">
         <f>IFERROR(STDEV($B$20:$B$1000),"")</f>
         <v/>
       </c>
-      <c r="D10" s="19" t="inlineStr">
+      <c r="D10" s="20" t="inlineStr">
         <is>
           <t>Assumes symmetry, so it describes skewed data poorly.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="inlineStr">
+      <c r="A11" s="18" t="inlineStr">
         <is>
           <t>Interquartile range</t>
         </is>
       </c>
-      <c r="B11" s="18">
+      <c r="B11" s="19">
         <f>IFERROR(QUARTILE($B$20:$B$1000,3)-QUARTILE($B$20:$B$1000,1),"")</f>
         <v/>
       </c>
-      <c r="D11" s="19" t="inlineStr">
+      <c r="D11" s="20" t="inlineStr">
         <is>
           <t>The middle half. A better spread measure for this data.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="17" t="inlineStr">
+      <c r="A12" s="18" t="inlineStr">
         <is>
           <t>Mean ÷ median</t>
         </is>
       </c>
-      <c r="B12" s="18">
+      <c r="B12" s="19">
         <f>IFERROR(AVERAGE($B$20:$B$1000)/MEDIAN($B$20:$B$1000),"")</f>
         <v/>
       </c>
-      <c r="D12" s="19" t="inlineStr">
+      <c r="D12" s="20" t="inlineStr">
         <is>
           <t>Above about 1.2 means meaningful right skew — use non-parametric tests and quote percentiles.</t>
         </is>
@@ -2038,17 +2038,17 @@
     </row>
     <row r="13"/>
     <row r="14">
-      <c r="A14" s="12" t="inlineStr">
+      <c r="A14" s="11" t="inlineStr">
         <is>
           <t>VERDICT</t>
         </is>
       </c>
-      <c r="B14" s="7" t="n"/>
-      <c r="C14" s="7" t="n"/>
-      <c r="D14" s="7" t="n"/>
+      <c r="B14" s="17" t="n"/>
+      <c r="C14" s="17" t="n"/>
+      <c r="D14" s="17" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="20">
+      <c r="A15" s="21">
         <f>IF(COUNT($B$20:$B$1000)=0,"Paste your data into column B below.",IF(AVERAGE($B$20:$B$1000)/MEDIAN($B$20:$B$1000)&gt;1.2,"RIGHT-SKEWED — quote the median and p90, and prefer non-parametric tests.","ROUGHLY SYMMETRIC — the mean and a parametric test are defensible."))</f>
         <v/>
       </c>
@@ -2056,12 +2056,12 @@
     <row r="16"/>
     <row r="17"/>
     <row r="18">
-      <c r="A18" s="17" t="inlineStr">
+      <c r="A18" s="18" t="inlineStr">
         <is>
           <t>Your data</t>
         </is>
       </c>
-      <c r="F18" s="17" t="inlineStr">
+      <c r="F18" s="18" t="inlineStr">
         <is>
           <t>What you would quote</t>
         </is>
@@ -2078,13 +2078,13 @@
           <t>Mean</t>
         </is>
       </c>
-      <c r="G19" s="13">
+      <c r="G19" s="12">
         <f>IFERROR(AVERAGE($B$20:$B$1000),"")</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="21" t="n">
+      <c r="B20" s="22" t="n">
         <v>182</v>
       </c>
       <c r="F20" s="5" t="inlineStr">
@@ -2092,13 +2092,13 @@
           <t>Median (p50)</t>
         </is>
       </c>
-      <c r="G20" s="13">
+      <c r="G20" s="12">
         <f>IFERROR(MEDIAN($B$20:$B$1000),"")</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="21" t="n">
+      <c r="B21" s="22" t="n">
         <v>201</v>
       </c>
       <c r="F21" s="5" t="inlineStr">
@@ -2106,198 +2106,198 @@
           <t>p90</t>
         </is>
       </c>
-      <c r="G21" s="13">
+      <c r="G21" s="12">
         <f>IFERROR(PERCENTILE($B$20:$B$1000,0.9),"")</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="21" t="n">
+      <c r="B22" s="22" t="n">
         <v>214</v>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="21" t="n">
+      <c r="B23" s="22" t="n">
         <v>227</v>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="21" t="n">
+      <c r="B24" s="22" t="n">
         <v>236</v>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="21" t="n">
+      <c r="B25" s="22" t="n">
         <v>241</v>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="21" t="n">
+      <c r="B26" s="22" t="n">
         <v>248</v>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="21" t="n">
+      <c r="B27" s="22" t="n">
         <v>255</v>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="21" t="n">
+      <c r="B28" s="22" t="n">
         <v>259</v>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="21" t="n">
+      <c r="B29" s="22" t="n">
         <v>263</v>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="21" t="n">
+      <c r="B30" s="22" t="n">
         <v>268</v>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="21" t="n">
+      <c r="B31" s="22" t="n">
         <v>272</v>
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="21" t="n">
+      <c r="B32" s="22" t="n">
         <v>277</v>
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="21" t="n">
+      <c r="B33" s="22" t="n">
         <v>281</v>
       </c>
     </row>
     <row r="34">
-      <c r="B34" s="21" t="n">
+      <c r="B34" s="22" t="n">
         <v>286</v>
       </c>
     </row>
     <row r="35">
-      <c r="B35" s="21" t="n">
+      <c r="B35" s="22" t="n">
         <v>292</v>
       </c>
     </row>
     <row r="36">
-      <c r="B36" s="21" t="n">
+      <c r="B36" s="22" t="n">
         <v>298</v>
       </c>
     </row>
     <row r="37">
-      <c r="B37" s="21" t="n">
+      <c r="B37" s="22" t="n">
         <v>305</v>
       </c>
     </row>
     <row r="38">
-      <c r="B38" s="21" t="n">
+      <c r="B38" s="22" t="n">
         <v>311</v>
       </c>
     </row>
     <row r="39">
-      <c r="B39" s="21" t="n">
+      <c r="B39" s="22" t="n">
         <v>318</v>
       </c>
     </row>
     <row r="40">
-      <c r="B40" s="21" t="n">
+      <c r="B40" s="22" t="n">
         <v>326</v>
       </c>
     </row>
     <row r="41">
-      <c r="B41" s="21" t="n">
+      <c r="B41" s="22" t="n">
         <v>335</v>
       </c>
     </row>
     <row r="42">
-      <c r="B42" s="21" t="n">
+      <c r="B42" s="22" t="n">
         <v>346</v>
       </c>
     </row>
     <row r="43">
-      <c r="B43" s="21" t="n">
+      <c r="B43" s="22" t="n">
         <v>358</v>
       </c>
     </row>
     <row r="44">
-      <c r="B44" s="21" t="n">
+      <c r="B44" s="22" t="n">
         <v>372</v>
       </c>
     </row>
     <row r="45">
-      <c r="B45" s="21" t="n">
+      <c r="B45" s="22" t="n">
         <v>389</v>
       </c>
     </row>
     <row r="46">
-      <c r="B46" s="21" t="n">
+      <c r="B46" s="22" t="n">
         <v>408</v>
       </c>
     </row>
     <row r="47">
-      <c r="B47" s="21" t="n">
+      <c r="B47" s="22" t="n">
         <v>431</v>
       </c>
     </row>
     <row r="48">
-      <c r="B48" s="21" t="n">
+      <c r="B48" s="22" t="n">
         <v>459</v>
       </c>
     </row>
     <row r="49">
-      <c r="B49" s="21" t="n">
+      <c r="B49" s="22" t="n">
         <v>494</v>
       </c>
     </row>
     <row r="50">
-      <c r="B50" s="21" t="n">
+      <c r="B50" s="22" t="n">
         <v>538</v>
       </c>
     </row>
     <row r="51">
-      <c r="B51" s="21" t="n">
+      <c r="B51" s="22" t="n">
         <v>594</v>
       </c>
     </row>
     <row r="52">
-      <c r="B52" s="21" t="n">
+      <c r="B52" s="22" t="n">
         <v>668</v>
       </c>
     </row>
     <row r="53">
-      <c r="B53" s="21" t="n">
+      <c r="B53" s="22" t="n">
         <v>771</v>
       </c>
     </row>
     <row r="54">
-      <c r="B54" s="21" t="n">
+      <c r="B54" s="22" t="n">
         <v>918</v>
       </c>
     </row>
     <row r="55">
-      <c r="B55" s="21" t="n">
+      <c r="B55" s="22" t="n">
         <v>1140</v>
       </c>
     </row>
     <row r="56">
-      <c r="B56" s="21" t="n">
+      <c r="B56" s="22" t="n">
         <v>1502</v>
       </c>
     </row>
     <row r="57">
-      <c r="B57" s="21" t="n">
+      <c r="B57" s="22" t="n">
         <v>2160</v>
       </c>
     </row>
     <row r="58">
-      <c r="B58" s="21" t="n">
+      <c r="B58" s="22" t="n">
         <v>3480</v>
       </c>
     </row>
     <row r="59">
-      <c r="B59" s="21" t="n">
+      <c r="B59" s="22" t="n">
         <v>5220</v>
       </c>
     </row>

--- a/templates/25-pareto-and-distribution.xlsx
+++ b/templates/25-pareto-and-distribution.xlsx
@@ -1048,10 +1048,10 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="26" customHeight="1">
+    <row r="3" ht="117" customHeight="1">
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>RANKED — this is what the chart plots. Type above in any order; this sorts itself.</t>
+          <t>RANKED — this is what the chart plots. Type above in any order; this sorts itself.  ·  Key: Share = that category's count as a percentage of the total, before any sorting. The largest billing category runs 412 of 966 contacts, 42.7% (B5, C5). Read it beside the cumulative column: share tells you how big one bar is, cumulative tells you how few bars you need · Cumulative = the running total of share down the SORTED list, which is the line a Pareto chart draws. The top category alone reaches 42.7% and the top two reach 66.8% (J5, J6), so two of the categories carry two-thirds of the volume. Where the line crosses 80% is the set worth working on</t>
         </is>
       </c>
     </row>

--- a/templates/25-pareto-and-distribution.xlsx
+++ b/templates/25-pareto-and-distribution.xlsx
@@ -1048,10 +1048,10 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="117" customHeight="1">
+    <row r="3" ht="156" customHeight="1">
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>RANKED — this is what the chart plots. Type above in any order; this sorts itself.  ·  Key: Share = that category's count as a percentage of the total, before any sorting. The largest billing category runs 412 of 966 contacts, 42.7% (B5, C5). Read it beside the cumulative column: share tells you how big one bar is, cumulative tells you how few bars you need · Cumulative = the running total of share down the SORTED list, which is the line a Pareto chart draws. The top category alone reaches 42.7% and the top two reach 66.8% (J5, J6), so two of the categories carry two-thirds of the volume. Where the line crosses 80% is the set worth working on</t>
+          <t>RANKED — this is what the chart plots. Type above in any order; this sorts itself.  ·  Key: Share = that category's count as a percentage of the total, before any sorting. The largest billing category runs 412 of 966 contacts, 42.7% (B5, C5). Read it beside the cumulative column: share tells you how big one bar is, cumulative tells you how few bars you need · Rank = position by weighted total, 1 being highest. Ties are not broken, so two rows can share a rank. Read it with the totals beside it: rank 1 at 270 and rank 2 at 261 (H15, H16) is a photo finish, and a rank alone hides that · Cumulative = the running total of share down the SORTED list, which is the line a Pareto chart draws. The top category alone reaches 42.7% and the top two reach 66.8% (J5, J6), so two of the categories carry two-thirds of the volume. Where the line crosses 80% is the set worth working on</t>
         </is>
       </c>
     </row>

--- a/templates/25-pareto-and-distribution.xlsx
+++ b/templates/25-pareto-and-distribution.xlsx
@@ -1051,7 +1051,10 @@
     <row r="3" ht="156" customHeight="1">
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>RANKED — this is what the chart plots. Type above in any order; this sorts itself.  ·  Key: Share = that category's count as a percentage of the total, before any sorting. The largest billing category runs 412 of 966 contacts, 42.7% (B5, C5). Read it beside the cumulative column: share tells you how big one bar is, cumulative tells you how few bars you need · Rank = position by weighted total, 1 being highest. Ties are not broken, so two rows can share a rank. Read it with the totals beside it: rank 1 at 270 and rank 2 at 261 (H15, H16) is a photo finish, and a rank alone hides that · Cumulative = the running total of share down the SORTED list, which is the line a Pareto chart draws. The top category alone reaches 42.7% and the top two reach 66.8% (J5, J6), so two of the categories carry two-thirds of the volume. Where the line crosses 80% is the set worth working on</t>
+          <t>RANKED — this is what the chart plots. Type above in any order; this sorts itself.  ·  Key:
+• Share = that category's count as a percentage of the total, before any sorting. The largest billing category runs 412 of 966 contacts, 42.7% (B5, C5). Read it beside the cumulative column: share tells you how big one bar is, cumulative tells you how few bars you need
+• Rank = position by weighted total, 1 being highest. Ties are not broken, so two rows can share a rank. Read it with the totals beside it: rank 1 at 270 and rank 2 at 261 (H15, H16) is a photo finish, and a rank alone hides that
+• Cumulative = the running total of share down the SORTED list, which is the line a Pareto chart draws. The top category alone reaches 42.7% and the top two reach 66.8% (J5, J6), so two of the categories carry two-thirds of the volume. Where the line crosses 80% is the set worth working on</t>
         </is>
       </c>
     </row>

--- a/templates/25-pareto-and-distribution.xlsx
+++ b/templates/25-pareto-and-distribution.xlsx
@@ -21,7 +21,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -54,6 +54,11 @@
     </font>
     <font>
       <sz val="11"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="FF4B5563"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="8">
@@ -111,7 +116,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -141,6 +146,9 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="4" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -543,7 +551,7 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>12</col>
+      <col>15</col>
       <colOff>0</colOff>
       <row>2</row>
       <rowOff>0</rowOff>
@@ -1014,7 +1022,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K31"/>
+  <dimension ref="A1:V31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1028,6 +1036,15 @@
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
     <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
+    <col width="13" customWidth="1" min="19" max="19"/>
+    <col width="13" customWidth="1" min="20" max="20"/>
+    <col width="13" customWidth="1" min="21" max="21"/>
+    <col width="13" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -1802,7 +1819,7 @@
       <c r="D26" s="17" t="n"/>
       <c r="E26" s="17" t="n"/>
     </row>
-    <row r="27">
+    <row r="27" ht="77" customHeight="1">
       <c r="A27" s="18" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1811,6 +1828,12 @@
       <c r="C27" s="11">
         <f>SUM(B5:B24)</f>
         <v/>
+      </c>
+      <c r="N27" s="19" t="inlineStr">
+        <is>
+          <t>HOW TO READ IT.  Bars ranked, line cumulative. The top category runs 42.7% and the top two reach 66.8%, so two of them carry two-thirds of the volume. Where the line crosses 80% is the set worth working on. A flat Pareto with no clear break means the categories are wrong, not that the problem is evenly spread.
+SO:  Scope the project to the categories left of the 80% crossing — two of them here — and leave the tail alone. If the bars are flat with no clear break, re-cut the categories before starting: a flat Pareto means the categories are wrong, not that the problem is evenly spread.</t>
+        </is>
       </c>
     </row>
     <row r="28">
@@ -1844,13 +1867,14 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="10">
     <mergeCell ref="G3:K3"/>
     <mergeCell ref="A26:E26"/>
     <mergeCell ref="A29:B29"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A25:E25"/>
     <mergeCell ref="A28:B28"/>
+    <mergeCell ref="N27:V27"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A31:E31"/>
     <mergeCell ref="A27:B27"/>
@@ -1873,7 +1897,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G59"/>
+  <dimension ref="A1:N59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1882,6 +1906,13 @@
     <col width="60" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -1933,11 +1964,11 @@
           <t>Count</t>
         </is>
       </c>
-      <c r="B6" s="19">
+      <c r="B6" s="20">
         <f>COUNT($B$20:$B$1000)</f>
         <v/>
       </c>
-      <c r="D6" s="20" t="inlineStr">
+      <c r="D6" s="21" t="inlineStr">
         <is>
           <t>How many values you pasted.</t>
         </is>
@@ -1949,11 +1980,11 @@
           <t>Mean</t>
         </is>
       </c>
-      <c r="B7" s="19">
+      <c r="B7" s="20">
         <f>IFERROR(AVERAGE($B$20:$B$1000),"")</f>
         <v/>
       </c>
-      <c r="D7" s="20" t="inlineStr">
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t>Dragged upward by the long tail. Rarely the number to quote.</t>
         </is>
@@ -1965,11 +1996,11 @@
           <t>Median (p50)</t>
         </is>
       </c>
-      <c r="B8" s="19">
+      <c r="B8" s="20">
         <f>IFERROR(MEDIAN($B$20:$B$1000),"")</f>
         <v/>
       </c>
-      <c r="D8" s="20" t="inlineStr">
+      <c r="D8" s="21" t="inlineStr">
         <is>
           <t>The typical experience. Quote this.</t>
         </is>
@@ -1981,11 +2012,11 @@
           <t>p90</t>
         </is>
       </c>
-      <c r="B9" s="19">
+      <c r="B9" s="20">
         <f>IFERROR(PERCENTILE($B$20:$B$1000,0.9),"")</f>
         <v/>
       </c>
-      <c r="D9" s="20" t="inlineStr">
+      <c r="D9" s="21" t="inlineStr">
         <is>
           <t>What your worst-served customers get. This is what generates complaints.</t>
         </is>
@@ -1997,11 +2028,11 @@
           <t>Standard deviation</t>
         </is>
       </c>
-      <c r="B10" s="19">
+      <c r="B10" s="20">
         <f>IFERROR(STDEV($B$20:$B$1000),"")</f>
         <v/>
       </c>
-      <c r="D10" s="20" t="inlineStr">
+      <c r="D10" s="21" t="inlineStr">
         <is>
           <t>Assumes symmetry, so it describes skewed data poorly.</t>
         </is>
@@ -2013,11 +2044,11 @@
           <t>Interquartile range</t>
         </is>
       </c>
-      <c r="B11" s="19">
+      <c r="B11" s="20">
         <f>IFERROR(QUARTILE($B$20:$B$1000,3)-QUARTILE($B$20:$B$1000,1),"")</f>
         <v/>
       </c>
-      <c r="D11" s="20" t="inlineStr">
+      <c r="D11" s="21" t="inlineStr">
         <is>
           <t>The middle half. A better spread measure for this data.</t>
         </is>
@@ -2029,11 +2060,11 @@
           <t>Mean ÷ median</t>
         </is>
       </c>
-      <c r="B12" s="19">
+      <c r="B12" s="20">
         <f>IFERROR(AVERAGE($B$20:$B$1000)/MEDIAN($B$20:$B$1000),"")</f>
         <v/>
       </c>
-      <c r="D12" s="20" t="inlineStr">
+      <c r="D12" s="21" t="inlineStr">
         <is>
           <t>Above about 1.2 means meaningful right skew — use non-parametric tests and quote percentiles.</t>
         </is>
@@ -2051,7 +2082,7 @@
       <c r="D14" s="17" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="21">
+      <c r="A15" s="22">
         <f>IF(COUNT($B$20:$B$1000)=0,"Paste your data into column B below.",IF(AVERAGE($B$20:$B$1000)/MEDIAN($B$20:$B$1000)&gt;1.2,"RIGHT-SKEWED — quote the median and p90, and prefer non-parametric tests.","ROUGHLY SYMMETRIC — the mean and a parametric test are defensible."))</f>
         <v/>
       </c>
@@ -2087,7 +2118,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="22" t="n">
+      <c r="B20" s="23" t="n">
         <v>182</v>
       </c>
       <c r="F20" s="5" t="inlineStr">
@@ -2101,7 +2132,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="22" t="n">
+      <c r="B21" s="23" t="n">
         <v>201</v>
       </c>
       <c r="F21" s="5" t="inlineStr">
@@ -2115,201 +2146,208 @@
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="22" t="n">
+      <c r="B22" s="23" t="n">
         <v>214</v>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="22" t="n">
+      <c r="B23" s="23" t="n">
         <v>227</v>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="22" t="n">
+      <c r="B24" s="23" t="n">
         <v>236</v>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="22" t="n">
+      <c r="B25" s="23" t="n">
         <v>241</v>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="22" t="n">
+      <c r="B26" s="23" t="n">
         <v>248</v>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="22" t="n">
+      <c r="B27" s="23" t="n">
         <v>255</v>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="22" t="n">
+      <c r="B28" s="23" t="n">
         <v>259</v>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="22" t="n">
+      <c r="B29" s="23" t="n">
         <v>263</v>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="22" t="n">
+      <c r="B30" s="23" t="n">
         <v>268</v>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="22" t="n">
+      <c r="B31" s="23" t="n">
         <v>272</v>
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="22" t="n">
+      <c r="B32" s="23" t="n">
         <v>277</v>
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="22" t="n">
+      <c r="B33" s="23" t="n">
         <v>281</v>
       </c>
     </row>
     <row r="34">
-      <c r="B34" s="22" t="n">
+      <c r="B34" s="23" t="n">
         <v>286</v>
       </c>
     </row>
     <row r="35">
-      <c r="B35" s="22" t="n">
+      <c r="B35" s="23" t="n">
         <v>292</v>
       </c>
     </row>
     <row r="36">
-      <c r="B36" s="22" t="n">
+      <c r="B36" s="23" t="n">
         <v>298</v>
       </c>
     </row>
     <row r="37">
-      <c r="B37" s="22" t="n">
+      <c r="B37" s="23" t="n">
         <v>305</v>
       </c>
     </row>
     <row r="38">
-      <c r="B38" s="22" t="n">
+      <c r="B38" s="23" t="n">
         <v>311</v>
       </c>
     </row>
     <row r="39">
-      <c r="B39" s="22" t="n">
+      <c r="B39" s="23" t="n">
         <v>318</v>
       </c>
     </row>
-    <row r="40">
-      <c r="B40" s="22" t="n">
+    <row r="40" ht="66" customHeight="1">
+      <c r="B40" s="23" t="n">
         <v>326</v>
       </c>
+      <c r="F40" s="19" t="inlineStr">
+        <is>
+          <t>HOW TO READ IT.  Three markers on one axis. The gap between mean and median is the skew, and the distance out to p90 is what your customers actually feel. If the mean sits well below the median you are quoting a number almost nobody experiences — report the median and the p90 together, or report neither.
+SO:  Quote the median and the p90 together in every report, and retire the mean. If a target is written against the mean, renegotiate it — the tail is what customers escalate about.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
-      <c r="B41" s="22" t="n">
+      <c r="B41" s="23" t="n">
         <v>335</v>
       </c>
     </row>
     <row r="42">
-      <c r="B42" s="22" t="n">
+      <c r="B42" s="23" t="n">
         <v>346</v>
       </c>
     </row>
     <row r="43">
-      <c r="B43" s="22" t="n">
+      <c r="B43" s="23" t="n">
         <v>358</v>
       </c>
     </row>
     <row r="44">
-      <c r="B44" s="22" t="n">
+      <c r="B44" s="23" t="n">
         <v>372</v>
       </c>
     </row>
     <row r="45">
-      <c r="B45" s="22" t="n">
+      <c r="B45" s="23" t="n">
         <v>389</v>
       </c>
     </row>
     <row r="46">
-      <c r="B46" s="22" t="n">
+      <c r="B46" s="23" t="n">
         <v>408</v>
       </c>
     </row>
     <row r="47">
-      <c r="B47" s="22" t="n">
+      <c r="B47" s="23" t="n">
         <v>431</v>
       </c>
     </row>
     <row r="48">
-      <c r="B48" s="22" t="n">
+      <c r="B48" s="23" t="n">
         <v>459</v>
       </c>
     </row>
     <row r="49">
-      <c r="B49" s="22" t="n">
+      <c r="B49" s="23" t="n">
         <v>494</v>
       </c>
     </row>
     <row r="50">
-      <c r="B50" s="22" t="n">
+      <c r="B50" s="23" t="n">
         <v>538</v>
       </c>
     </row>
     <row r="51">
-      <c r="B51" s="22" t="n">
+      <c r="B51" s="23" t="n">
         <v>594</v>
       </c>
     </row>
     <row r="52">
-      <c r="B52" s="22" t="n">
+      <c r="B52" s="23" t="n">
         <v>668</v>
       </c>
     </row>
     <row r="53">
-      <c r="B53" s="22" t="n">
+      <c r="B53" s="23" t="n">
         <v>771</v>
       </c>
     </row>
     <row r="54">
-      <c r="B54" s="22" t="n">
+      <c r="B54" s="23" t="n">
         <v>918</v>
       </c>
     </row>
     <row r="55">
-      <c r="B55" s="22" t="n">
+      <c r="B55" s="23" t="n">
         <v>1140</v>
       </c>
     </row>
     <row r="56">
-      <c r="B56" s="22" t="n">
+      <c r="B56" s="23" t="n">
         <v>1502</v>
       </c>
     </row>
     <row r="57">
-      <c r="B57" s="22" t="n">
+      <c r="B57" s="23" t="n">
         <v>2160</v>
       </c>
     </row>
     <row r="58">
-      <c r="B58" s="22" t="n">
+      <c r="B58" s="23" t="n">
         <v>3480</v>
       </c>
     </row>
     <row r="59">
-      <c r="B59" s="22" t="n">
+      <c r="B59" s="23" t="n">
         <v>5220</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="F40:N40"/>
+    <mergeCell ref="A2:D2"/>
     <mergeCell ref="A14:D14"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A15:D15"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>

--- a/templates/25-pareto-and-distribution.xlsx
+++ b/templates/25-pareto-and-distribution.xlsx
@@ -21,7 +21,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -59,6 +59,10 @@
       <i val="1"/>
       <color rgb="FF4B5563"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="8">
@@ -116,12 +120,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -146,9 +156,6 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="4" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -890,11 +897,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B40"/>
+  <dimension ref="A1:H40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
     <col width="108" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -984,10 +997,34 @@
     </row>
     <row r="14"/>
     <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
+    <row r="16" ht="14" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>WHAT THE COLUMNS MEAN — the short version sits above each table; this is the same thing with the worked example</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Share = that category's count as a percentage of the total, before any sorting. The largest billing category runs 412 of 966 contacts, 42.7% (B5, C5). Read it beside the cumulative column: share tells you how big one bar is, cumulative tells you how few bars you need</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Rank = position by weighted total, 1 being highest. Ties are not broken, so two rows can share a rank. Read it with the totals beside it: rank 1 at 270 and rank 2 at 261 (H15, H16) is a photo finish, and a rank alone hides that</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Cumulative = the running total of share down the SORTED list, which is the line a Pareto chart draws. The top category alone reaches 42.7% and the top two reach 66.8% (J5, J6), so two of the categories carry two-thirds of the volume. Where the line crosses 80% is the set worth working on</t>
+        </is>
+      </c>
+    </row>
     <row r="20"/>
     <row r="21"/>
     <row r="22"/>
@@ -1010,6 +1047,12 @@
     <row r="39"/>
     <row r="40"/>
   </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A18:H18"/>
+    <mergeCell ref="A19:H19"/>
+    <mergeCell ref="A16:H16"/>
+    <mergeCell ref="A17:H17"/>
+  </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -1048,788 +1091,788 @@
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Pareto — where the bulk of the problem actually sits</t>
         </is>
       </c>
-      <c r="B1" s="4" t="n"/>
-      <c r="C1" s="4" t="n"/>
-      <c r="D1" s="4" t="n"/>
-      <c r="E1" s="4" t="n"/>
+      <c r="B1" s="6" t="n"/>
+      <c r="C1" s="6" t="n"/>
+      <c r="D1" s="6" t="n"/>
+      <c r="E1" s="6" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>Ranked categories with a running cumulative share, so you can see how much of the problem the top few explain.</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="156" customHeight="1">
-      <c r="G3" s="6" t="inlineStr">
+    <row r="3" ht="65" customHeight="1">
+      <c r="G3" s="8" t="inlineStr">
         <is>
           <t>RANKED — this is what the chart plots. Type above in any order; this sorts itself.  ·  Key:
-• Share = that category's count as a percentage of the total, before any sorting. The largest billing category runs 412 of 966 contacts, 42.7% (B5, C5). Read it beside the cumulative column: share tells you how big one bar is, cumulative tells you how few bars you need
-• Rank = position by weighted total, 1 being highest. Ties are not broken, so two rows can share a rank. Read it with the totals beside it: rank 1 at 270 and rank 2 at 261 (H15, H16) is a photo finish, and a rank alone hides that
-• Cumulative = the running total of share down the SORTED list, which is the line a Pareto chart draws. The top category alone reaches 42.7% and the top two reach 66.8% (J5, J6), so two of the categories carry two-thirds of the volume. Where the line crosses 80% is the set worth working on</t>
+• Share = that category's count as a percentage of the total, before any sorting.
+• Rank = position by weighted total, 1 being highest.
+• Cumulative = the running total of share down the SORTED list, which is the line a Pareto chart draws.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="9" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="C4" s="9" t="inlineStr">
         <is>
           <t>Share</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="D4" s="9" t="inlineStr">
         <is>
           <t>Rank</t>
         </is>
       </c>
-      <c r="E4" s="7" t="inlineStr">
+      <c r="E4" s="9" t="inlineStr">
         <is>
           <t>Validated by reading tickets?</t>
         </is>
       </c>
-      <c r="G4" s="7" t="inlineStr">
+      <c r="G4" s="9" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="H4" s="7" t="inlineStr">
+      <c r="H4" s="9" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="I4" s="7" t="inlineStr">
+      <c r="I4" s="9" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
-      <c r="J4" s="7" t="inlineStr">
+      <c r="J4" s="9" t="inlineStr">
         <is>
           <t>Cumulative</t>
         </is>
       </c>
-      <c r="K4" s="7" t="inlineStr">
+      <c r="K4" s="9" t="inlineStr">
         <is>
           <t>80% line</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>Adjustment not posted at closure</t>
         </is>
       </c>
-      <c r="B5" s="8" t="n">
+      <c r="B5" s="10" t="n">
         <v>412</v>
       </c>
-      <c r="C5" s="9">
+      <c r="C5" s="11">
         <f>IF(OR(B5="",SUM($B$5:$B$24)=0),"",B5/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D5" s="10">
+      <c r="D5" s="12">
         <f>IF(B5="","",RANK(B5,$B$5:$B$24,0)+COUNTIF($B$5:B5,B5)-1)</f>
         <v/>
       </c>
-      <c r="E5" s="8" t="inlineStr">
+      <c r="E5" s="10" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G5" s="5" t="n">
+      <c r="G5" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="H5" s="11">
+      <c r="H5" s="13">
         <f>IFERROR(INDEX($A$5:$A$24,MATCH(G5,$D$5:$D$24,0)),"")</f>
         <v/>
       </c>
-      <c r="I5" s="12">
+      <c r="I5" s="14">
         <f>IFERROR(INDEX($B$5:$B$24,MATCH(G5,$D$5:$D$24,0)),"")</f>
         <v/>
       </c>
-      <c r="J5" s="9">
+      <c r="J5" s="11">
         <f>IF(I5="",NA(),SUM($I$5:I5)/SUM($I$5:$I$24))</f>
         <v/>
       </c>
-      <c r="K5" s="13">
+      <c r="K5" s="15">
         <f>IF(I5="",NA(),0.8)</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Wrong plan applied</t>
         </is>
       </c>
-      <c r="B6" s="8" t="n">
+      <c r="B6" s="10" t="n">
         <v>233</v>
       </c>
-      <c r="C6" s="9">
+      <c r="C6" s="11">
         <f>IF(OR(B6="",SUM($B$5:$B$24)=0),"",B6/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D6" s="10">
+      <c r="D6" s="12">
         <f>IF(B6="","",RANK(B6,$B$5:$B$24,0)+COUNTIF($B$5:B6,B6)-1)</f>
         <v/>
       </c>
-      <c r="E6" s="14" t="n"/>
-      <c r="G6" s="5" t="n">
+      <c r="E6" s="16" t="n"/>
+      <c r="G6" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="H6" s="11">
+      <c r="H6" s="13">
         <f>IFERROR(INDEX($A$5:$A$24,MATCH(G6,$D$5:$D$24,0)),"")</f>
         <v/>
       </c>
-      <c r="I6" s="12">
+      <c r="I6" s="14">
         <f>IFERROR(INDEX($B$5:$B$24,MATCH(G6,$D$5:$D$24,0)),"")</f>
         <v/>
       </c>
-      <c r="J6" s="9">
+      <c r="J6" s="11">
         <f>IF(I6="",NA(),SUM($I$5:I6)/SUM($I$5:$I$24))</f>
         <v/>
       </c>
-      <c r="K6" s="13">
+      <c r="K6" s="15">
         <f>IF(I6="",NA(),0.8)</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>Duplicate charge</t>
         </is>
       </c>
-      <c r="B7" s="8" t="n">
+      <c r="B7" s="10" t="n">
         <v>151</v>
       </c>
-      <c r="C7" s="9">
+      <c r="C7" s="11">
         <f>IF(OR(B7="",SUM($B$5:$B$24)=0),"",B7/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D7" s="10">
+      <c r="D7" s="12">
         <f>IF(B7="","",RANK(B7,$B$5:$B$24,0)+COUNTIF($B$5:B7,B7)-1)</f>
         <v/>
       </c>
-      <c r="E7" s="14" t="n"/>
-      <c r="G7" s="5" t="n">
+      <c r="E7" s="16" t="n"/>
+      <c r="G7" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="H7" s="11">
+      <c r="H7" s="13">
         <f>IFERROR(INDEX($A$5:$A$24,MATCH(G7,$D$5:$D$24,0)),"")</f>
         <v/>
       </c>
-      <c r="I7" s="12">
+      <c r="I7" s="14">
         <f>IFERROR(INDEX($B$5:$B$24,MATCH(G7,$D$5:$D$24,0)),"")</f>
         <v/>
       </c>
-      <c r="J7" s="9">
+      <c r="J7" s="11">
         <f>IF(I7="",NA(),SUM($I$5:I7)/SUM($I$5:$I$24))</f>
         <v/>
       </c>
-      <c r="K7" s="13">
+      <c r="K7" s="15">
         <f>IF(I7="",NA(),0.8)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>Proration misunderstood</t>
         </is>
       </c>
-      <c r="B8" s="8" t="n">
+      <c r="B8" s="10" t="n">
         <v>96</v>
       </c>
-      <c r="C8" s="9">
+      <c r="C8" s="11">
         <f>IF(OR(B8="",SUM($B$5:$B$24)=0),"",B8/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D8" s="10">
+      <c r="D8" s="12">
         <f>IF(B8="","",RANK(B8,$B$5:$B$24,0)+COUNTIF($B$5:B8,B8)-1)</f>
         <v/>
       </c>
-      <c r="E8" s="14" t="n"/>
-      <c r="G8" s="5" t="n">
+      <c r="E8" s="16" t="n"/>
+      <c r="G8" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="H8" s="11">
+      <c r="H8" s="13">
         <f>IFERROR(INDEX($A$5:$A$24,MATCH(G8,$D$5:$D$24,0)),"")</f>
         <v/>
       </c>
-      <c r="I8" s="12">
+      <c r="I8" s="14">
         <f>IFERROR(INDEX($B$5:$B$24,MATCH(G8,$D$5:$D$24,0)),"")</f>
         <v/>
       </c>
-      <c r="J8" s="9">
+      <c r="J8" s="11">
         <f>IF(I8="",NA(),SUM($I$5:I8)/SUM($I$5:$I$24))</f>
         <v/>
       </c>
-      <c r="K8" s="13">
+      <c r="K8" s="15">
         <f>IF(I8="",NA(),0.8)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>Refund timing</t>
         </is>
       </c>
-      <c r="B9" s="8" t="n">
+      <c r="B9" s="10" t="n">
         <v>74</v>
       </c>
-      <c r="C9" s="9">
+      <c r="C9" s="11">
         <f>IF(OR(B9="",SUM($B$5:$B$24)=0),"",B9/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D9" s="10">
+      <c r="D9" s="12">
         <f>IF(B9="","",RANK(B9,$B$5:$B$24,0)+COUNTIF($B$5:B9,B9)-1)</f>
         <v/>
       </c>
-      <c r="E9" s="14" t="n"/>
-      <c r="G9" s="5" t="n">
+      <c r="E9" s="16" t="n"/>
+      <c r="G9" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="H9" s="11">
+      <c r="H9" s="13">
         <f>IFERROR(INDEX($A$5:$A$24,MATCH(G9,$D$5:$D$24,0)),"")</f>
         <v/>
       </c>
-      <c r="I9" s="12">
+      <c r="I9" s="14">
         <f>IFERROR(INDEX($B$5:$B$24,MATCH(G9,$D$5:$D$24,0)),"")</f>
         <v/>
       </c>
-      <c r="J9" s="9">
+      <c r="J9" s="11">
         <f>IF(I9="",NA(),SUM($I$5:I9)/SUM($I$5:$I$24))</f>
         <v/>
       </c>
-      <c r="K9" s="13">
+      <c r="K9" s="15">
         <f>IF(I9="",NA(),0.8)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="14" t="n"/>
-      <c r="B10" s="14" t="n"/>
-      <c r="C10" s="9">
+      <c r="A10" s="16" t="n"/>
+      <c r="B10" s="16" t="n"/>
+      <c r="C10" s="11">
         <f>IF(OR(B10="",SUM($B$5:$B$24)=0),"",B10/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D10" s="10">
+      <c r="D10" s="12">
         <f>IF(B10="","",RANK(B10,$B$5:$B$24,0)+COUNTIF($B$5:B10,B10)-1)</f>
         <v/>
       </c>
-      <c r="E10" s="14" t="n"/>
-      <c r="G10" s="5" t="n">
+      <c r="E10" s="16" t="n"/>
+      <c r="G10" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="H10" s="11">
+      <c r="H10" s="13">
         <f>IFERROR(INDEX($A$5:$A$24,MATCH(G10,$D$5:$D$24,0)),"")</f>
         <v/>
       </c>
-      <c r="I10" s="12">
+      <c r="I10" s="14">
         <f>IFERROR(INDEX($B$5:$B$24,MATCH(G10,$D$5:$D$24,0)),"")</f>
         <v/>
       </c>
-      <c r="J10" s="9">
+      <c r="J10" s="11">
         <f>IF(I10="",NA(),SUM($I$5:I10)/SUM($I$5:$I$24))</f>
         <v/>
       </c>
-      <c r="K10" s="13">
+      <c r="K10" s="15">
         <f>IF(I10="",NA(),0.8)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="14" t="n"/>
-      <c r="B11" s="14" t="n"/>
-      <c r="C11" s="9">
+      <c r="A11" s="16" t="n"/>
+      <c r="B11" s="16" t="n"/>
+      <c r="C11" s="11">
         <f>IF(OR(B11="",SUM($B$5:$B$24)=0),"",B11/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D11" s="10">
+      <c r="D11" s="12">
         <f>IF(B11="","",RANK(B11,$B$5:$B$24,0)+COUNTIF($B$5:B11,B11)-1)</f>
         <v/>
       </c>
-      <c r="E11" s="14" t="n"/>
-      <c r="G11" s="5" t="n">
+      <c r="E11" s="16" t="n"/>
+      <c r="G11" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="H11" s="11">
+      <c r="H11" s="13">
         <f>IFERROR(INDEX($A$5:$A$24,MATCH(G11,$D$5:$D$24,0)),"")</f>
         <v/>
       </c>
-      <c r="I11" s="12">
+      <c r="I11" s="14">
         <f>IFERROR(INDEX($B$5:$B$24,MATCH(G11,$D$5:$D$24,0)),"")</f>
         <v/>
       </c>
-      <c r="J11" s="9">
+      <c r="J11" s="11">
         <f>IF(I11="",NA(),SUM($I$5:I11)/SUM($I$5:$I$24))</f>
         <v/>
       </c>
-      <c r="K11" s="13">
+      <c r="K11" s="15">
         <f>IF(I11="",NA(),0.8)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="14" t="n"/>
-      <c r="B12" s="14" t="n"/>
-      <c r="C12" s="9">
+      <c r="A12" s="16" t="n"/>
+      <c r="B12" s="16" t="n"/>
+      <c r="C12" s="11">
         <f>IF(OR(B12="",SUM($B$5:$B$24)=0),"",B12/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D12" s="10">
+      <c r="D12" s="12">
         <f>IF(B12="","",RANK(B12,$B$5:$B$24,0)+COUNTIF($B$5:B12,B12)-1)</f>
         <v/>
       </c>
-      <c r="E12" s="14" t="n"/>
-      <c r="G12" s="5" t="n">
+      <c r="E12" s="16" t="n"/>
+      <c r="G12" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="H12" s="11">
+      <c r="H12" s="13">
         <f>IFERROR(INDEX($A$5:$A$24,MATCH(G12,$D$5:$D$24,0)),"")</f>
         <v/>
       </c>
-      <c r="I12" s="12">
+      <c r="I12" s="14">
         <f>IFERROR(INDEX($B$5:$B$24,MATCH(G12,$D$5:$D$24,0)),"")</f>
         <v/>
       </c>
-      <c r="J12" s="9">
+      <c r="J12" s="11">
         <f>IF(I12="",NA(),SUM($I$5:I12)/SUM($I$5:$I$24))</f>
         <v/>
       </c>
-      <c r="K12" s="13">
+      <c r="K12" s="15">
         <f>IF(I12="",NA(),0.8)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="14" t="n"/>
-      <c r="B13" s="14" t="n"/>
-      <c r="C13" s="9">
+      <c r="A13" s="16" t="n"/>
+      <c r="B13" s="16" t="n"/>
+      <c r="C13" s="11">
         <f>IF(OR(B13="",SUM($B$5:$B$24)=0),"",B13/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D13" s="10">
+      <c r="D13" s="12">
         <f>IF(B13="","",RANK(B13,$B$5:$B$24,0)+COUNTIF($B$5:B13,B13)-1)</f>
         <v/>
       </c>
-      <c r="E13" s="14" t="n"/>
-      <c r="G13" s="5" t="n">
+      <c r="E13" s="16" t="n"/>
+      <c r="G13" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="H13" s="11">
+      <c r="H13" s="13">
         <f>IFERROR(INDEX($A$5:$A$24,MATCH(G13,$D$5:$D$24,0)),"")</f>
         <v/>
       </c>
-      <c r="I13" s="12">
+      <c r="I13" s="14">
         <f>IFERROR(INDEX($B$5:$B$24,MATCH(G13,$D$5:$D$24,0)),"")</f>
         <v/>
       </c>
-      <c r="J13" s="9">
+      <c r="J13" s="11">
         <f>IF(I13="",NA(),SUM($I$5:I13)/SUM($I$5:$I$24))</f>
         <v/>
       </c>
-      <c r="K13" s="13">
+      <c r="K13" s="15">
         <f>IF(I13="",NA(),0.8)</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="14" t="n"/>
-      <c r="B14" s="14" t="n"/>
-      <c r="C14" s="9">
+      <c r="A14" s="16" t="n"/>
+      <c r="B14" s="16" t="n"/>
+      <c r="C14" s="11">
         <f>IF(OR(B14="",SUM($B$5:$B$24)=0),"",B14/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D14" s="10">
+      <c r="D14" s="12">
         <f>IF(B14="","",RANK(B14,$B$5:$B$24,0)+COUNTIF($B$5:B14,B14)-1)</f>
         <v/>
       </c>
-      <c r="E14" s="14" t="n"/>
-      <c r="G14" s="5" t="n">
+      <c r="E14" s="16" t="n"/>
+      <c r="G14" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="H14" s="11">
+      <c r="H14" s="13">
         <f>IFERROR(INDEX($A$5:$A$24,MATCH(G14,$D$5:$D$24,0)),"")</f>
         <v/>
       </c>
-      <c r="I14" s="12">
+      <c r="I14" s="14">
         <f>IFERROR(INDEX($B$5:$B$24,MATCH(G14,$D$5:$D$24,0)),"")</f>
         <v/>
       </c>
-      <c r="J14" s="9">
+      <c r="J14" s="11">
         <f>IF(I14="",NA(),SUM($I$5:I14)/SUM($I$5:$I$24))</f>
         <v/>
       </c>
-      <c r="K14" s="13">
+      <c r="K14" s="15">
         <f>IF(I14="",NA(),0.8)</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="14" t="n"/>
-      <c r="B15" s="14" t="n"/>
-      <c r="C15" s="9">
+      <c r="A15" s="16" t="n"/>
+      <c r="B15" s="16" t="n"/>
+      <c r="C15" s="11">
         <f>IF(OR(B15="",SUM($B$5:$B$24)=0),"",B15/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D15" s="10">
+      <c r="D15" s="12">
         <f>IF(B15="","",RANK(B15,$B$5:$B$24,0)+COUNTIF($B$5:B15,B15)-1)</f>
         <v/>
       </c>
-      <c r="E15" s="14" t="n"/>
-      <c r="G15" s="5" t="n">
+      <c r="E15" s="16" t="n"/>
+      <c r="G15" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="H15" s="11">
+      <c r="H15" s="13">
         <f>IFERROR(INDEX($A$5:$A$24,MATCH(G15,$D$5:$D$24,0)),"")</f>
         <v/>
       </c>
-      <c r="I15" s="12">
+      <c r="I15" s="14">
         <f>IFERROR(INDEX($B$5:$B$24,MATCH(G15,$D$5:$D$24,0)),"")</f>
         <v/>
       </c>
-      <c r="J15" s="9">
+      <c r="J15" s="11">
         <f>IF(I15="",NA(),SUM($I$5:I15)/SUM($I$5:$I$24))</f>
         <v/>
       </c>
-      <c r="K15" s="13">
+      <c r="K15" s="15">
         <f>IF(I15="",NA(),0.8)</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="14" t="n"/>
-      <c r="B16" s="14" t="n"/>
-      <c r="C16" s="9">
+      <c r="A16" s="16" t="n"/>
+      <c r="B16" s="16" t="n"/>
+      <c r="C16" s="11">
         <f>IF(OR(B16="",SUM($B$5:$B$24)=0),"",B16/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D16" s="10">
+      <c r="D16" s="12">
         <f>IF(B16="","",RANK(B16,$B$5:$B$24,0)+COUNTIF($B$5:B16,B16)-1)</f>
         <v/>
       </c>
-      <c r="E16" s="14" t="n"/>
-      <c r="G16" s="5" t="n">
+      <c r="E16" s="16" t="n"/>
+      <c r="G16" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="H16" s="11">
+      <c r="H16" s="13">
         <f>IFERROR(INDEX($A$5:$A$24,MATCH(G16,$D$5:$D$24,0)),"")</f>
         <v/>
       </c>
-      <c r="I16" s="12">
+      <c r="I16" s="14">
         <f>IFERROR(INDEX($B$5:$B$24,MATCH(G16,$D$5:$D$24,0)),"")</f>
         <v/>
       </c>
-      <c r="J16" s="9">
+      <c r="J16" s="11">
         <f>IF(I16="",NA(),SUM($I$5:I16)/SUM($I$5:$I$24))</f>
         <v/>
       </c>
-      <c r="K16" s="13">
+      <c r="K16" s="15">
         <f>IF(I16="",NA(),0.8)</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="14" t="n"/>
-      <c r="B17" s="14" t="n"/>
-      <c r="C17" s="9">
+      <c r="A17" s="16" t="n"/>
+      <c r="B17" s="16" t="n"/>
+      <c r="C17" s="11">
         <f>IF(OR(B17="",SUM($B$5:$B$24)=0),"",B17/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D17" s="10">
+      <c r="D17" s="12">
         <f>IF(B17="","",RANK(B17,$B$5:$B$24,0)+COUNTIF($B$5:B17,B17)-1)</f>
         <v/>
       </c>
-      <c r="E17" s="14" t="n"/>
-      <c r="G17" s="5" t="n">
+      <c r="E17" s="16" t="n"/>
+      <c r="G17" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="H17" s="11">
+      <c r="H17" s="13">
         <f>IFERROR(INDEX($A$5:$A$24,MATCH(G17,$D$5:$D$24,0)),"")</f>
         <v/>
       </c>
-      <c r="I17" s="12">
+      <c r="I17" s="14">
         <f>IFERROR(INDEX($B$5:$B$24,MATCH(G17,$D$5:$D$24,0)),"")</f>
         <v/>
       </c>
-      <c r="J17" s="9">
+      <c r="J17" s="11">
         <f>IF(I17="",NA(),SUM($I$5:I17)/SUM($I$5:$I$24))</f>
         <v/>
       </c>
-      <c r="K17" s="13">
+      <c r="K17" s="15">
         <f>IF(I17="",NA(),0.8)</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="14" t="n"/>
-      <c r="B18" s="14" t="n"/>
-      <c r="C18" s="9">
+      <c r="A18" s="16" t="n"/>
+      <c r="B18" s="16" t="n"/>
+      <c r="C18" s="11">
         <f>IF(OR(B18="",SUM($B$5:$B$24)=0),"",B18/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D18" s="10">
+      <c r="D18" s="12">
         <f>IF(B18="","",RANK(B18,$B$5:$B$24,0)+COUNTIF($B$5:B18,B18)-1)</f>
         <v/>
       </c>
-      <c r="E18" s="14" t="n"/>
-      <c r="G18" s="5" t="n">
+      <c r="E18" s="16" t="n"/>
+      <c r="G18" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="H18" s="11">
+      <c r="H18" s="13">
         <f>IFERROR(INDEX($A$5:$A$24,MATCH(G18,$D$5:$D$24,0)),"")</f>
         <v/>
       </c>
-      <c r="I18" s="12">
+      <c r="I18" s="14">
         <f>IFERROR(INDEX($B$5:$B$24,MATCH(G18,$D$5:$D$24,0)),"")</f>
         <v/>
       </c>
-      <c r="J18" s="9">
+      <c r="J18" s="11">
         <f>IF(I18="",NA(),SUM($I$5:I18)/SUM($I$5:$I$24))</f>
         <v/>
       </c>
-      <c r="K18" s="13">
+      <c r="K18" s="15">
         <f>IF(I18="",NA(),0.8)</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="14" t="n"/>
-      <c r="B19" s="14" t="n"/>
-      <c r="C19" s="9">
+      <c r="A19" s="16" t="n"/>
+      <c r="B19" s="16" t="n"/>
+      <c r="C19" s="11">
         <f>IF(OR(B19="",SUM($B$5:$B$24)=0),"",B19/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D19" s="10">
+      <c r="D19" s="12">
         <f>IF(B19="","",RANK(B19,$B$5:$B$24,0)+COUNTIF($B$5:B19,B19)-1)</f>
         <v/>
       </c>
-      <c r="E19" s="14" t="n"/>
-      <c r="G19" s="5" t="n">
+      <c r="E19" s="16" t="n"/>
+      <c r="G19" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="H19" s="11">
+      <c r="H19" s="13">
         <f>IFERROR(INDEX($A$5:$A$24,MATCH(G19,$D$5:$D$24,0)),"")</f>
         <v/>
       </c>
-      <c r="I19" s="12">
+      <c r="I19" s="14">
         <f>IFERROR(INDEX($B$5:$B$24,MATCH(G19,$D$5:$D$24,0)),"")</f>
         <v/>
       </c>
-      <c r="J19" s="9">
+      <c r="J19" s="11">
         <f>IF(I19="",NA(),SUM($I$5:I19)/SUM($I$5:$I$24))</f>
         <v/>
       </c>
-      <c r="K19" s="13">
+      <c r="K19" s="15">
         <f>IF(I19="",NA(),0.8)</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="14" t="n"/>
-      <c r="B20" s="14" t="n"/>
-      <c r="C20" s="9">
+      <c r="A20" s="16" t="n"/>
+      <c r="B20" s="16" t="n"/>
+      <c r="C20" s="11">
         <f>IF(OR(B20="",SUM($B$5:$B$24)=0),"",B20/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D20" s="10">
+      <c r="D20" s="12">
         <f>IF(B20="","",RANK(B20,$B$5:$B$24,0)+COUNTIF($B$5:B20,B20)-1)</f>
         <v/>
       </c>
-      <c r="E20" s="14" t="n"/>
-      <c r="G20" s="5" t="n">
+      <c r="E20" s="16" t="n"/>
+      <c r="G20" s="7" t="n">
         <v>16</v>
       </c>
-      <c r="H20" s="11">
+      <c r="H20" s="13">
         <f>IFERROR(INDEX($A$5:$A$24,MATCH(G20,$D$5:$D$24,0)),"")</f>
         <v/>
       </c>
-      <c r="I20" s="12">
+      <c r="I20" s="14">
         <f>IFERROR(INDEX($B$5:$B$24,MATCH(G20,$D$5:$D$24,0)),"")</f>
         <v/>
       </c>
-      <c r="J20" s="9">
+      <c r="J20" s="11">
         <f>IF(I20="",NA(),SUM($I$5:I20)/SUM($I$5:$I$24))</f>
         <v/>
       </c>
-      <c r="K20" s="13">
+      <c r="K20" s="15">
         <f>IF(I20="",NA(),0.8)</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="14" t="n"/>
-      <c r="B21" s="14" t="n"/>
-      <c r="C21" s="9">
+      <c r="A21" s="16" t="n"/>
+      <c r="B21" s="16" t="n"/>
+      <c r="C21" s="11">
         <f>IF(OR(B21="",SUM($B$5:$B$24)=0),"",B21/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D21" s="10">
+      <c r="D21" s="12">
         <f>IF(B21="","",RANK(B21,$B$5:$B$24,0)+COUNTIF($B$5:B21,B21)-1)</f>
         <v/>
       </c>
-      <c r="E21" s="14" t="n"/>
-      <c r="G21" s="5" t="n">
+      <c r="E21" s="16" t="n"/>
+      <c r="G21" s="7" t="n">
         <v>17</v>
       </c>
-      <c r="H21" s="11">
+      <c r="H21" s="13">
         <f>IFERROR(INDEX($A$5:$A$24,MATCH(G21,$D$5:$D$24,0)),"")</f>
         <v/>
       </c>
-      <c r="I21" s="12">
+      <c r="I21" s="14">
         <f>IFERROR(INDEX($B$5:$B$24,MATCH(G21,$D$5:$D$24,0)),"")</f>
         <v/>
       </c>
-      <c r="J21" s="9">
+      <c r="J21" s="11">
         <f>IF(I21="",NA(),SUM($I$5:I21)/SUM($I$5:$I$24))</f>
         <v/>
       </c>
-      <c r="K21" s="13">
+      <c r="K21" s="15">
         <f>IF(I21="",NA(),0.8)</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="14" t="n"/>
-      <c r="B22" s="14" t="n"/>
-      <c r="C22" s="9">
+      <c r="A22" s="16" t="n"/>
+      <c r="B22" s="16" t="n"/>
+      <c r="C22" s="11">
         <f>IF(OR(B22="",SUM($B$5:$B$24)=0),"",B22/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D22" s="10">
+      <c r="D22" s="12">
         <f>IF(B22="","",RANK(B22,$B$5:$B$24,0)+COUNTIF($B$5:B22,B22)-1)</f>
         <v/>
       </c>
-      <c r="E22" s="14" t="n"/>
-      <c r="G22" s="5" t="n">
+      <c r="E22" s="16" t="n"/>
+      <c r="G22" s="7" t="n">
         <v>18</v>
       </c>
-      <c r="H22" s="11">
+      <c r="H22" s="13">
         <f>IFERROR(INDEX($A$5:$A$24,MATCH(G22,$D$5:$D$24,0)),"")</f>
         <v/>
       </c>
-      <c r="I22" s="12">
+      <c r="I22" s="14">
         <f>IFERROR(INDEX($B$5:$B$24,MATCH(G22,$D$5:$D$24,0)),"")</f>
         <v/>
       </c>
-      <c r="J22" s="9">
+      <c r="J22" s="11">
         <f>IF(I22="",NA(),SUM($I$5:I22)/SUM($I$5:$I$24))</f>
         <v/>
       </c>
-      <c r="K22" s="13">
+      <c r="K22" s="15">
         <f>IF(I22="",NA(),0.8)</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="14" t="n"/>
-      <c r="B23" s="14" t="n"/>
-      <c r="C23" s="9">
+      <c r="A23" s="16" t="n"/>
+      <c r="B23" s="16" t="n"/>
+      <c r="C23" s="11">
         <f>IF(OR(B23="",SUM($B$5:$B$24)=0),"",B23/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D23" s="10">
+      <c r="D23" s="12">
         <f>IF(B23="","",RANK(B23,$B$5:$B$24,0)+COUNTIF($B$5:B23,B23)-1)</f>
         <v/>
       </c>
-      <c r="E23" s="14" t="n"/>
-      <c r="G23" s="5" t="n">
+      <c r="E23" s="16" t="n"/>
+      <c r="G23" s="7" t="n">
         <v>19</v>
       </c>
-      <c r="H23" s="11">
+      <c r="H23" s="13">
         <f>IFERROR(INDEX($A$5:$A$24,MATCH(G23,$D$5:$D$24,0)),"")</f>
         <v/>
       </c>
-      <c r="I23" s="12">
+      <c r="I23" s="14">
         <f>IFERROR(INDEX($B$5:$B$24,MATCH(G23,$D$5:$D$24,0)),"")</f>
         <v/>
       </c>
-      <c r="J23" s="9">
+      <c r="J23" s="11">
         <f>IF(I23="",NA(),SUM($I$5:I23)/SUM($I$5:$I$24))</f>
         <v/>
       </c>
-      <c r="K23" s="13">
+      <c r="K23" s="15">
         <f>IF(I23="",NA(),0.8)</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="14" t="n"/>
-      <c r="B24" s="14" t="n"/>
-      <c r="C24" s="9">
+      <c r="A24" s="16" t="n"/>
+      <c r="B24" s="16" t="n"/>
+      <c r="C24" s="11">
         <f>IF(OR(B24="",SUM($B$5:$B$24)=0),"",B24/SUM($B$5:$B$24))</f>
         <v/>
       </c>
-      <c r="D24" s="10">
+      <c r="D24" s="12">
         <f>IF(B24="","",RANK(B24,$B$5:$B$24,0)+COUNTIF($B$5:B24,B24)-1)</f>
         <v/>
       </c>
-      <c r="E24" s="14" t="n"/>
-      <c r="G24" s="5" t="n">
+      <c r="E24" s="16" t="n"/>
+      <c r="G24" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="H24" s="11">
+      <c r="H24" s="13">
         <f>IFERROR(INDEX($A$5:$A$24,MATCH(G24,$D$5:$D$24,0)),"")</f>
         <v/>
       </c>
-      <c r="I24" s="12">
+      <c r="I24" s="14">
         <f>IFERROR(INDEX($B$5:$B$24,MATCH(G24,$D$5:$D$24,0)),"")</f>
         <v/>
       </c>
-      <c r="J24" s="9">
+      <c r="J24" s="11">
         <f>IF(I24="",NA(),SUM($I$5:I24)/SUM($I$5:$I$24))</f>
         <v/>
       </c>
-      <c r="K24" s="13">
+      <c r="K24" s="15">
         <f>IF(I24="",NA(),0.8)</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="90" customHeight="1">
-      <c r="A25" s="15" t="inlineStr">
+      <c r="A25" s="17" t="inlineStr">
         <is>
           <t>How to answer the last column, and why it is the one that matters. Open 50 tickets at random from your top category and read them. Count how many are genuinely that category rather than the code an agent picked under time pressure. Answer Yes only if 40 or more of the 50 hold up; below that your Pareto is ranking your data-entry habits and not your problems, and the business case built on it will not survive contact with the process. Row 5 is the worked example: 50 read, 41 held up, so Yes.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="16" t="inlineStr">
+      <c r="A26" s="18" t="inlineStr">
         <is>
           <t>SUMMARY</t>
         </is>
       </c>
-      <c r="B26" s="17" t="n"/>
-      <c r="C26" s="17" t="n"/>
-      <c r="D26" s="17" t="n"/>
-      <c r="E26" s="17" t="n"/>
+      <c r="B26" s="19" t="n"/>
+      <c r="C26" s="19" t="n"/>
+      <c r="D26" s="19" t="n"/>
+      <c r="E26" s="19" t="n"/>
     </row>
     <row r="27" ht="77" customHeight="1">
-      <c r="A27" s="18" t="inlineStr">
+      <c r="A27" s="20" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C27" s="11">
+      <c r="C27" s="13">
         <f>SUM(B5:B24)</f>
         <v/>
       </c>
-      <c r="N27" s="19" t="inlineStr">
+      <c r="N27" s="4" t="inlineStr">
         <is>
           <t>HOW TO READ IT.  Bars ranked, line cumulative. The top category runs 42.7% and the top two reach 66.8%, so two of them carry two-thirds of the volume. Where the line crosses 80% is the set worth working on. A flat Pareto with no clear break means the categories are wrong, not that the problem is evenly spread.
 SO:  Scope the project to the categories left of the 80% crossing — two of them here — and leave the tail alone. If the bars are flat with no clear break, re-cut the categories before starting: a flat Pareto means the categories are wrong, not that the problem is evenly spread.</t>
@@ -1837,30 +1880,30 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="18" t="inlineStr">
+      <c r="A28" s="20" t="inlineStr">
         <is>
           <t>Categories</t>
         </is>
       </c>
-      <c r="C28" s="11">
+      <c r="C28" s="13">
         <f>COUNTA(A5:A24)</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="18" t="inlineStr">
+      <c r="A29" s="20" t="inlineStr">
         <is>
           <t>Share explained by the top three</t>
         </is>
       </c>
-      <c r="C29" s="9">
+      <c r="C29" s="11">
         <f>IFERROR(SUM(I5:I7)/SUM(I5:I24),"")</f>
         <v/>
       </c>
     </row>
     <row r="30"/>
     <row r="31">
-      <c r="A31" s="5" t="inlineStr">
+      <c r="A31" s="7" t="inlineStr">
         <is>
           <t>A Pareto inherits the quality of your categories. Disposition codes are chosen by agents under time pressure, so a Pareto of them ranks your data-entry habits as much as your problems. Read 50 tickets in the top bar before you size a business case on it — that is what the last column is for.</t>
         </is>
@@ -1916,17 +1959,17 @@
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Is this data the shape you assumed?</t>
         </is>
       </c>
-      <c r="B1" s="4" t="n"/>
-      <c r="C1" s="4" t="n"/>
-      <c r="D1" s="4" t="n"/>
+      <c r="B1" s="6" t="n"/>
+      <c r="C1" s="6" t="n"/>
+      <c r="D1" s="6" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>Normality assessment for support data. Support durations are right-skewed: the mean flatters you, the median and p90 do not. Read the skew before you pick a test — a two-sample t-test on data this shaped will mislead you, and the non-parametric equivalent will not.</t>
         </is>
@@ -1934,137 +1977,137 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>Paste your values into column B</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>Statistic</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr"/>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="C5" s="9" t="inlineStr"/>
+      <c r="D5" s="9" t="inlineStr">
         <is>
           <t>What it tells you</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="inlineStr">
+      <c r="A6" s="20" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
-      <c r="B6" s="20">
+      <c r="B6" s="21">
         <f>COUNT($B$20:$B$1000)</f>
         <v/>
       </c>
-      <c r="D6" s="21" t="inlineStr">
+      <c r="D6" s="22" t="inlineStr">
         <is>
           <t>How many values you pasted.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="inlineStr">
+      <c r="A7" s="20" t="inlineStr">
         <is>
           <t>Mean</t>
         </is>
       </c>
-      <c r="B7" s="20">
+      <c r="B7" s="21">
         <f>IFERROR(AVERAGE($B$20:$B$1000),"")</f>
         <v/>
       </c>
-      <c r="D7" s="21" t="inlineStr">
+      <c r="D7" s="22" t="inlineStr">
         <is>
           <t>Dragged upward by the long tail. Rarely the number to quote.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="inlineStr">
+      <c r="A8" s="20" t="inlineStr">
         <is>
           <t>Median (p50)</t>
         </is>
       </c>
-      <c r="B8" s="20">
+      <c r="B8" s="21">
         <f>IFERROR(MEDIAN($B$20:$B$1000),"")</f>
         <v/>
       </c>
-      <c r="D8" s="21" t="inlineStr">
+      <c r="D8" s="22" t="inlineStr">
         <is>
           <t>The typical experience. Quote this.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="inlineStr">
+      <c r="A9" s="20" t="inlineStr">
         <is>
           <t>p90</t>
         </is>
       </c>
-      <c r="B9" s="20">
+      <c r="B9" s="21">
         <f>IFERROR(PERCENTILE($B$20:$B$1000,0.9),"")</f>
         <v/>
       </c>
-      <c r="D9" s="21" t="inlineStr">
+      <c r="D9" s="22" t="inlineStr">
         <is>
           <t>What your worst-served customers get. This is what generates complaints.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="inlineStr">
+      <c r="A10" s="20" t="inlineStr">
         <is>
           <t>Standard deviation</t>
         </is>
       </c>
-      <c r="B10" s="20">
+      <c r="B10" s="21">
         <f>IFERROR(STDEV($B$20:$B$1000),"")</f>
         <v/>
       </c>
-      <c r="D10" s="21" t="inlineStr">
+      <c r="D10" s="22" t="inlineStr">
         <is>
           <t>Assumes symmetry, so it describes skewed data poorly.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="inlineStr">
+      <c r="A11" s="20" t="inlineStr">
         <is>
           <t>Interquartile range</t>
         </is>
       </c>
-      <c r="B11" s="20">
+      <c r="B11" s="21">
         <f>IFERROR(QUARTILE($B$20:$B$1000,3)-QUARTILE($B$20:$B$1000,1),"")</f>
         <v/>
       </c>
-      <c r="D11" s="21" t="inlineStr">
+      <c r="D11" s="22" t="inlineStr">
         <is>
           <t>The middle half. A better spread measure for this data.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="inlineStr">
+      <c r="A12" s="20" t="inlineStr">
         <is>
           <t>Mean ÷ median</t>
         </is>
       </c>
-      <c r="B12" s="20">
+      <c r="B12" s="21">
         <f>IFERROR(AVERAGE($B$20:$B$1000)/MEDIAN($B$20:$B$1000),"")</f>
         <v/>
       </c>
-      <c r="D12" s="21" t="inlineStr">
+      <c r="D12" s="22" t="inlineStr">
         <is>
           <t>Above about 1.2 means meaningful right skew — use non-parametric tests and quote percentiles.</t>
         </is>
@@ -2072,17 +2115,17 @@
     </row>
     <row r="13"/>
     <row r="14">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="A14" s="13" t="inlineStr">
         <is>
           <t>VERDICT</t>
         </is>
       </c>
-      <c r="B14" s="17" t="n"/>
-      <c r="C14" s="17" t="n"/>
-      <c r="D14" s="17" t="n"/>
+      <c r="B14" s="19" t="n"/>
+      <c r="C14" s="19" t="n"/>
+      <c r="D14" s="19" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="22">
+      <c r="A15" s="23">
         <f>IF(COUNT($B$20:$B$1000)=0,"Paste your data into column B below.",IF(AVERAGE($B$20:$B$1000)/MEDIAN($B$20:$B$1000)&gt;1.2,"RIGHT-SKEWED — quote the median and p90, and prefer non-parametric tests.","ROUGHLY SYMMETRIC — the mean and a parametric test are defensible."))</f>
         <v/>
       </c>
@@ -2090,156 +2133,156 @@
     <row r="16"/>
     <row r="17"/>
     <row r="18">
-      <c r="A18" s="18" t="inlineStr">
+      <c r="A18" s="20" t="inlineStr">
         <is>
           <t>Your data</t>
         </is>
       </c>
-      <c r="F18" s="18" t="inlineStr">
+      <c r="F18" s="20" t="inlineStr">
         <is>
           <t>What you would quote</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t>Values ↓</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="F19" s="7" t="inlineStr">
         <is>
           <t>Mean</t>
         </is>
       </c>
-      <c r="G19" s="12">
+      <c r="G19" s="14">
         <f>IFERROR(AVERAGE($B$20:$B$1000),"")</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="23" t="n">
+      <c r="B20" s="24" t="n">
         <v>182</v>
       </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="F20" s="7" t="inlineStr">
         <is>
           <t>Median (p50)</t>
         </is>
       </c>
-      <c r="G20" s="12">
+      <c r="G20" s="14">
         <f>IFERROR(MEDIAN($B$20:$B$1000),"")</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="23" t="n">
+      <c r="B21" s="24" t="n">
         <v>201</v>
       </c>
-      <c r="F21" s="5" t="inlineStr">
+      <c r="F21" s="7" t="inlineStr">
         <is>
           <t>p90</t>
         </is>
       </c>
-      <c r="G21" s="12">
+      <c r="G21" s="14">
         <f>IFERROR(PERCENTILE($B$20:$B$1000,0.9),"")</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="23" t="n">
+      <c r="B22" s="24" t="n">
         <v>214</v>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="23" t="n">
+      <c r="B23" s="24" t="n">
         <v>227</v>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="23" t="n">
+      <c r="B24" s="24" t="n">
         <v>236</v>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="23" t="n">
+      <c r="B25" s="24" t="n">
         <v>241</v>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="23" t="n">
+      <c r="B26" s="24" t="n">
         <v>248</v>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="23" t="n">
+      <c r="B27" s="24" t="n">
         <v>255</v>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="23" t="n">
+      <c r="B28" s="24" t="n">
         <v>259</v>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="23" t="n">
+      <c r="B29" s="24" t="n">
         <v>263</v>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="23" t="n">
+      <c r="B30" s="24" t="n">
         <v>268</v>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="23" t="n">
+      <c r="B31" s="24" t="n">
         <v>272</v>
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="23" t="n">
+      <c r="B32" s="24" t="n">
         <v>277</v>
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="23" t="n">
+      <c r="B33" s="24" t="n">
         <v>281</v>
       </c>
     </row>
     <row r="34">
-      <c r="B34" s="23" t="n">
+      <c r="B34" s="24" t="n">
         <v>286</v>
       </c>
     </row>
     <row r="35">
-      <c r="B35" s="23" t="n">
+      <c r="B35" s="24" t="n">
         <v>292</v>
       </c>
     </row>
     <row r="36">
-      <c r="B36" s="23" t="n">
+      <c r="B36" s="24" t="n">
         <v>298</v>
       </c>
     </row>
     <row r="37">
-      <c r="B37" s="23" t="n">
+      <c r="B37" s="24" t="n">
         <v>305</v>
       </c>
     </row>
     <row r="38">
-      <c r="B38" s="23" t="n">
+      <c r="B38" s="24" t="n">
         <v>311</v>
       </c>
     </row>
     <row r="39">
-      <c r="B39" s="23" t="n">
+      <c r="B39" s="24" t="n">
         <v>318</v>
       </c>
     </row>
     <row r="40" ht="66" customHeight="1">
-      <c r="B40" s="23" t="n">
+      <c r="B40" s="24" t="n">
         <v>326</v>
       </c>
-      <c r="F40" s="19" t="inlineStr">
+      <c r="F40" s="4" t="inlineStr">
         <is>
           <t>HOW TO READ IT.  Three markers on one axis. The gap between mean and median is the skew, and the distance out to p90 is what your customers actually feel. If the mean sits well below the median you are quoting a number almost nobody experiences — report the median and the p90 together, or report neither.
 SO:  Quote the median and the p90 together in every report, and retire the mean. If a target is written against the mean, renegotiate it — the tail is what customers escalate about.</t>
@@ -2247,97 +2290,97 @@
       </c>
     </row>
     <row r="41">
-      <c r="B41" s="23" t="n">
+      <c r="B41" s="24" t="n">
         <v>335</v>
       </c>
     </row>
     <row r="42">
-      <c r="B42" s="23" t="n">
+      <c r="B42" s="24" t="n">
         <v>346</v>
       </c>
     </row>
     <row r="43">
-      <c r="B43" s="23" t="n">
+      <c r="B43" s="24" t="n">
         <v>358</v>
       </c>
     </row>
     <row r="44">
-      <c r="B44" s="23" t="n">
+      <c r="B44" s="24" t="n">
         <v>372</v>
       </c>
     </row>
     <row r="45">
-      <c r="B45" s="23" t="n">
+      <c r="B45" s="24" t="n">
         <v>389</v>
       </c>
     </row>
     <row r="46">
-      <c r="B46" s="23" t="n">
+      <c r="B46" s="24" t="n">
         <v>408</v>
       </c>
     </row>
     <row r="47">
-      <c r="B47" s="23" t="n">
+      <c r="B47" s="24" t="n">
         <v>431</v>
       </c>
     </row>
     <row r="48">
-      <c r="B48" s="23" t="n">
+      <c r="B48" s="24" t="n">
         <v>459</v>
       </c>
     </row>
     <row r="49">
-      <c r="B49" s="23" t="n">
+      <c r="B49" s="24" t="n">
         <v>494</v>
       </c>
     </row>
     <row r="50">
-      <c r="B50" s="23" t="n">
+      <c r="B50" s="24" t="n">
         <v>538</v>
       </c>
     </row>
     <row r="51">
-      <c r="B51" s="23" t="n">
+      <c r="B51" s="24" t="n">
         <v>594</v>
       </c>
     </row>
     <row r="52">
-      <c r="B52" s="23" t="n">
+      <c r="B52" s="24" t="n">
         <v>668</v>
       </c>
     </row>
     <row r="53">
-      <c r="B53" s="23" t="n">
+      <c r="B53" s="24" t="n">
         <v>771</v>
       </c>
     </row>
     <row r="54">
-      <c r="B54" s="23" t="n">
+      <c r="B54" s="24" t="n">
         <v>918</v>
       </c>
     </row>
     <row r="55">
-      <c r="B55" s="23" t="n">
+      <c r="B55" s="24" t="n">
         <v>1140</v>
       </c>
     </row>
     <row r="56">
-      <c r="B56" s="23" t="n">
+      <c r="B56" s="24" t="n">
         <v>1502</v>
       </c>
     </row>
     <row r="57">
-      <c r="B57" s="23" t="n">
+      <c r="B57" s="24" t="n">
         <v>2160</v>
       </c>
     </row>
     <row r="58">
-      <c r="B58" s="23" t="n">
+      <c r="B58" s="24" t="n">
         <v>3480</v>
       </c>
     </row>
     <row r="59">
-      <c r="B59" s="23" t="n">
+      <c r="B59" s="24" t="n">
         <v>5220</v>
       </c>
     </row>

--- a/templates/25-pareto-and-distribution.xlsx
+++ b/templates/25-pareto-and-distribution.xlsx
@@ -1014,7 +1014,7 @@
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Rank = position by weighted total, 1 being highest. Ties are not broken, so two rows can share a rank. Read it with the totals beside it: rank 1 at 270 and rank 2 at 261 (H15, H16) is a photo finish, and a rank alone hides that</t>
+          <t>Rank = position by weighted total, 1 being highest. Ties are not broken, so two rows can share a rank. Always read it with the totals beside it: a rank on its own hides both a photo finish and an exact tie, and no amount of re-scoring separates two rows that scored the same</t>
         </is>
       </c>
     </row>

--- a/templates/25-pareto-and-distribution.xlsx
+++ b/templates/25-pareto-and-distribution.xlsx
@@ -1971,7 +1971,7 @@
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>Normality assessment for support data. Support durations are right-skewed: the mean flatters you, the median and p90 do not. Read the skew before you pick a test — a two-sample t-test on data this shaped will mislead you, and the non-parametric equivalent will not.</t>
+          <t>Normality assessment for support data. Support durations are right-skewed: the mean flatters you, the median and p90 do not. Read the skew before you pick a test — a two-sample t-test on data this shaped will mislead you, and the non-parametric equivalent will not. This tab gives you in numbers what a histogram or a boxplot would show you in a picture: where the middle sits, how far the tail runs, and whether the two disagree. It does not draw either one — plot those in your BI tool or notebook and read them beside this.</t>
         </is>
       </c>
     </row>
